--- a/pmu-admissions-audit/final_review/سجل_ملاحظات_صفحات_مكتب_القبول.xlsx
+++ b/pmu-admissions-audit/final_review/سجل_ملاحظات_صفحات_مكتب_القبول.xlsx
@@ -8441,7 +8441,7 @@
       </c>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve"> home</t>
+          <t>الصفحة الرئيسية للجامعة</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Study at PMU :: PMU :: Prince Mohammad Bin Fahd University</t>
+          <t>صفحة Study @ PMU (مكتب التسجيل)</t>
         </is>
       </c>
       <c r="C7" s="19" t="inlineStr">

--- a/pmu-admissions-audit/final_review/سجل_ملاحظات_صفحات_مكتب_القبول.xlsx
+++ b/pmu-admissions-audit/final_review/سجل_ملاحظات_صفحات_مكتب_القبول.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="نطاق الرصد" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'سجل الملاحظات'!$A$4:$L$131</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'سجل الملاحظات'!$A$4:$L$134</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'سجل الملاحظات'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'نطاق الرصد'!$A$4:$D$45</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'نطاق الرصد'!$4:$4</definedName>
@@ -572,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L131"/>
+  <dimension ref="A1:L134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -931,27 +931,27 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>صفحة مكتب القبول – قائمتا Graduate Admissions وUndergraduate Admissions</t>
+          <t>تذييل الصفحة – رابط «Academic Calendar»</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>Admissions to the MIBL … ../Admission/Admissions_Requirements_MIlBL_GDP.aspx … Admission to the College of Medicine … Admissions to the Preparatory Program … Admissions from Other Universities</t>
+          <t>Academic Calendar → ../Admission/academic_calendar_2021_2022_ro.aspx</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>الاتساق</t>
+          <t>دقة المعلومات</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>عدم اتساق تسميات القائمة</t>
+          <t>رابط إلى محتوى منتهي</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>يرد البند "Admissions to the MIBL" دون كلمة "Program" خلافًا لسائر بنود القائمة، ويتضمن رابطه خطأً في الحروف (MIlBL)، كما يرد البند "Admission to the College of Medicine" بصيغة المفرد في حين تستخدم البنود المجاورة "Admissions".</t>
+          <t>يفتح رابط «Academic Calendar» في تذييل صفحة مكتب القبول التقويم الأكاديمي للعام 2021/2022، لا تقويم العام الجاري، فيحصل المتقدم على مواعيد منتهية منذ أربع سنوات.</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -961,15 +961,19 @@
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>منخفضة</t>
+          <t>متوسطة</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>توحيد التسميات إلى "Admissions to the MIBL Program" و"Admissions to the College of Medicine"، وتصحيح الرابط إلى الصيغة السليمة مع إعادة توجيه دائمة من الرابط القديم.</t>
-        </is>
-      </c>
-      <c r="L9" s="6" t="inlineStr"/>
+          <t>توجيه الرابط إلى التقويم الأكاديمي المعتمد للعام الجاري (أو صفحة تقويم ثابتة تُحدَّث سنويًا)، مع إبقاء التقاويم السابقة في أرشيف مؤرخ.</t>
+        </is>
+      </c>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>تحقق مباشر من الصفحة الحية بتاريخ 13 أكتوبر 2026.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n">
@@ -987,27 +991,27 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>قائمة صفحة مكتب القبول؛ نموذج استفسار القبول؛ صفحتا اختبار SAT ومتطلبات تخصصات الحاسب والهندسة؛ صفحتا القبول في كلية الطب والقبول في البكالوريوس؛ عناوين صفحات متطلبات عدد من برامج الدراسات العليا</t>
+          <t>صفحة مكتب القبول – قائمتا Graduate Admissions وUndergraduate Admissions</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>Visting Students ; Enter Verifaction Code ; may wave one or more of the mathematics courses ; The PMU College of Medical curriculum ; MSEE ADMISSSIONS REQUIREMENTS ; MSME Admisssions Requirements</t>
+          <t>Admissions to the MIBL … ../Admission/Admissions_Requirements_MIlBL_GDP.aspx … Admission to the College of Medicine … Admissions to the Preparatory Program … Admissions from Other Universities</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>لغوي ونحوي</t>
+          <t>الاتساق</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>أخطاء إملائية متكررة</t>
+          <t>عدم اتساق تسميات القائمة</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>تتضمن صفحات القبول أخطاء إملائية ظاهرة في عناوين الروابط والنماذج، منها "Visting" بدل "Visiting" في رابط صفحة الطلاب الزائرين، و"Verifaction" بدل "Verification" في نموذج استفسار القبول.</t>
+          <t>يرد البند "Admissions to the MIBL" دون كلمة "Program" خلافًا لسائر بنود القائمة، ويتضمن رابطه خطأً في الحروف (MIlBL)، كما يرد البند "Admission to the College of Medicine" بصيغة المفرد في حين تستخدم البنود المجاورة "Admissions".</t>
         </is>
       </c>
       <c r="I10" s="8" t="inlineStr">
@@ -1022,7 +1026,7 @@
       </c>
       <c r="K10" s="9" t="inlineStr">
         <is>
-          <t>تصحيح الكلمتين إلى "Visiting" و"Verification"، وإجراء تدقيق لغوي شامل لعناوين الروابط والنماذج قبل النشر.</t>
+          <t>توحيد التسميات إلى "Admissions to the MIBL Program" و"Admissions to the College of Medicine"، وتصحيح الرابط إلى الصيغة السليمة مع إعادة توجيه دائمة من الرابط القديم.</t>
         </is>
       </c>
       <c r="L10" s="9" t="inlineStr"/>
@@ -1043,27 +1047,27 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>صفحة مكتب القبول – بنية الصفحة (شيفرة HTML)</t>
+          <t>قائمة صفحة مكتب القبول؛ نموذج استفسار القبول؛ صفحتا اختبار SAT ومتطلبات تخصصات الحاسب والهندسة؛ صفحتا القبول في كلية الطب والقبول في البكالوريوس؛ عناوين صفحات متطلبات عدد من برامج الدراسات العليا</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>href="#sidebar" (link with no text) ; landmarks: HEADER, NAV, HEADER, NAV, FOOTER, FOOTER (no MAIN)</t>
+          <t>Visting Students ; Enter Verifaction Code ; may wave one or more of the mathematics courses ; The PMU College of Medical curriculum ; MSEE ADMISSSIONS REQUIREMENTS ; MSME Admisssions Requirements</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>وظيفي وتقني</t>
+          <t>لغوي ونحوي</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>مشكلات وصولية في البنية</t>
+          <t>أخطاء إملائية متكررة</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>تخلو الصفحة من معلم المحتوى الرئيس (main)، وتتضمن رابطًا بلا نص يدل على وجهته، وإطار بحث مضمّنًا دون عنوان، مما يضعف التصفح بقارئات الشاشة.</t>
+          <t>تتضمن صفحات القبول أخطاء إملائية ظاهرة في عناوين الروابط والنماذج، منها "Visting" بدل "Visiting" في رابط صفحة الطلاب الزائرين، و"Verifaction" بدل "Verification" في نموذج استفسار القبول.</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -1078,14 +1082,10 @@
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>إضافة عنصر main للمحتوى الرئيس، ومنح الرابط الفارغ نصًا وصفيًا أو تسمية وصولية، وإضافة عنوان للإطار المضمّن، وتصحيح مسار صورة الشعار المحالة.</t>
-        </is>
-      </c>
-      <c r="L11" s="6" t="inlineStr">
-        <is>
-          <t>النص الحالي مقتطف من شيفرة الصفحة وليس نصًا ظاهرًا؛ غياب عنوان الإطار وإعادة توجيه مسار صورة الشعار مأخوذان من الفحص التقني الأصلي.</t>
-        </is>
-      </c>
+          <t>تصحيح الكلمتين إلى "Visiting" و"Verification"، وإجراء تدقيق لغوي شامل لعناوين الروابط والنماذج قبل النشر.</t>
+        </is>
+      </c>
+      <c r="L11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="8" t="n">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>صفحة مكتب القبول وسائر الصفحات – عناوين URL ووسوم الترويسة</t>
+          <t>صفحة مكتب القبول – بنية الصفحة (شيفرة HTML)</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>href="../Admission/Admission_Contact_GDP.aspx" ; meta description: none</t>
+          <t>href="#sidebar" (link with no text) ; landmarks: HEADER, NAV, HEADER, NAV, FOOTER, FOOTER (no MAIN)</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
@@ -1118,17 +1118,17 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>عناوين URL غير موحدة</t>
+          <t>مشكلات وصولية في البنية</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>تُقدَّم الصفحة ذاتها عبر أكثر من نطاق وصيغة عنوان (مثل pmu.edu.sa دون تحويل إلى www، وروابط بالصيغة القديمة .aspx وبحالة أحرف مختلفة)، ولا تتضمن الصفحات وسم وصف (meta description) ولا عنوانًا مرجعيًا (canonical).</t>
+          <t>تخلو الصفحة من معلم المحتوى الرئيس (main)، وتتضمن رابطًا بلا نص يدل على وجهته، وإطار بحث مضمّنًا دون عنوان، مما يضعف التصفح بقارئات الشاشة.</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>توصية تحسين</t>
+          <t>تصحيح مطلوب</t>
         </is>
       </c>
       <c r="J12" s="8" t="inlineStr">
@@ -1138,10 +1138,14 @@
       </c>
       <c r="K12" s="9" t="inlineStr">
         <is>
-          <t>اعتماد نطاق وصيغة عنوان واحدة لكل صفحة مع إعادة توجيه دائمة من الصيغ الأخرى، وإضافة وسم canonical ووصف موجز لكل صفحة.</t>
-        </is>
-      </c>
-      <c r="L12" s="9" t="inlineStr"/>
+          <t>إضافة عنصر main للمحتوى الرئيس، ومنح الرابط الفارغ نصًا وصفيًا أو تسمية وصولية، وإضافة عنوان للإطار المضمّن، وتصحيح مسار صورة الشعار المحالة.</t>
+        </is>
+      </c>
+      <c r="L12" s="9" t="inlineStr">
+        <is>
+          <t>النص الحالي مقتطف من شيفرة الصفحة وليس نصًا ظاهرًا؛ غياب عنوان الإطار وإعادة توجيه مسار صورة الشعار مأخوذان من الفحص التقني الأصلي.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
@@ -1149,42 +1153,42 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>نظرة عامة – الطلاب المستقبليون</t>
+          <t>صفحة مكتب القبول (الرئيسية)</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/future_students_ro</t>
+          <t>https://pmu.edu.sa/admission/admission</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>صفحة النظرة العامة – الفقرة الافتتاحية وجملة الإحالة إلى الروابط (والفقرة نفسها مكررة في بوابة التقديم)</t>
+          <t>صفحة مكتب القبول وسائر الصفحات – عناوين URL ووسوم الترويسة</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>When you are looking for an institution that not only provides you with a degree in a competent subject, … grooms you to be a leader wherever you go. … To explore the opportunities and the admission requirements more please visit the below links:</t>
+          <t>href="../Admission/Admission_Contact_GDP.aspx" ; meta description: none</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>لغوي ونحوي</t>
+          <t>وظيفي وتقني</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>جملة ناقصة وصياغة ركيكة</t>
+          <t>عناوين URL غير موحدة</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>الجملة الافتتاحية ناقصة؛ إذ تبدأ بشرط "When…" دون جواب، وتستخدم عبارة الإحالة صياغة غير سليمة "please visit the below links".</t>
+          <t>تُقدَّم الصفحة ذاتها عبر أكثر من نطاق وصيغة عنوان (مثل pmu.edu.sa دون تحويل إلى www، وروابط بالصيغة القديمة .aspx وبحالة أحرف مختلفة)، ولا تتضمن الصفحات وسم وصف (meta description) ولا عنوانًا مرجعيًا (canonical).</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>تصحيح مطلوب</t>
+          <t>توصية تحسين</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
@@ -1194,7 +1198,7 @@
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>إعادة صياغة الجملة الافتتاحية جملةً تامة (مثل: "If you are looking for an institution that…, PMU is the place for you.")، واستخدام "please visit the links below"، وتطبيق التصحيح نفسه على بوابة التقديم.</t>
+          <t>اعتماد نطاق وصيغة عنوان واحدة لكل صفحة مع إعادة توجيه دائمة من الصيغ الأخرى، وإضافة وسم canonical ووصف موجز لكل صفحة.</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr"/>
@@ -1215,32 +1219,32 @@
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>صفحة النظرة العامة – الفقرة التعريفية (ومكررة في بوابة التقديم)</t>
+          <t>صفحة النظرة العامة – الفقرة الافتتاحية وجملة الإحالة إلى الروابط (والفقرة نفسها مكررة في بوابة التقديم)</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>We offer different programs accredited by prestigious national and international organizations.</t>
+          <t>When you are looking for an institution that not only provides you with a degree in a competent subject, … grooms you to be a leader wherever you go. … To explore the opportunities and the admission requirements more please visit the below links:</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>دقة المعلومات</t>
+          <t>لغوي ونحوي</t>
         </is>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>ادعاء غير موثّق</t>
+          <t>جملة ناقصة وصياغة ركيكة</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>تذكر الصفحة أن البرامج معتمدة من جهات وطنية ودولية مرموقة دون تسمية هذه الجهات أو الإحالة إلى صفحة الاعتماد الأكاديمي.</t>
+          <t>الجملة الافتتاحية ناقصة؛ إذ تبدأ بشرط "When…" دون جواب، وتستخدم عبارة الإحالة صياغة غير سليمة "please visit the below links".</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>توصية تحسين</t>
+          <t>تصحيح مطلوب</t>
         </is>
       </c>
       <c r="J14" s="8" t="inlineStr">
@@ -1250,7 +1254,7 @@
       </c>
       <c r="K14" s="9" t="inlineStr">
         <is>
-          <t>تسمية جهات الاعتماد لكل برنامج أو إضافة رابط إلى صفحة الاعتماد الأكاديمي الرسمية.</t>
+          <t>إعادة صياغة الجملة الافتتاحية جملةً تامة (مثل: "If you are looking for an institution that…, PMU is the place for you.")، واستخدام "please visit the links below"، وتطبيق التصحيح نفسه على بوابة التقديم.</t>
         </is>
       </c>
       <c r="L14" s="9" t="inlineStr"/>
@@ -1261,22 +1265,22 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>الدرجات والبرامج</t>
+          <t>نظرة عامة – الطلاب المستقبليون</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/degrees_programs_fs_ro</t>
+          <t>https://pmu.edu.sa/admission/future_students_ro</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>صفحة الدرجات والبرامج – جدولا البرامج الجامعية وبرامج الدراسات العليا؛ مقارنةً بقائمة الدراسات العليا في صفحة مكتب القبول وصفحة برامج الدراسات العليا وصفحة رسوم الدراسات العليا</t>
+          <t>صفحة النظرة العامة – الفقرة التعريفية (ومكررة في بوابة التقديم)</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>College of Law … B.A. in Law … Graduate Programs ; Admissions to the EMGMS Program ; Master of Engineering in Innovation, Sustainability, and Entrepreneurship (33) | SAR 80,000 | SAR 80,000</t>
+          <t>We offer different programs accredited by prestigious national and international organizations.</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -1286,34 +1290,30 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>قائمة برامج غير مكتملة</t>
+          <t>ادعاء غير موثّق</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>لا تتضمن صفحة الدرجات والبرامج برنامج كلية الطب ولا ماجستير الإدارة الهندسية (EMGMS) مع أن لكليهما صفحة قبول، ولا ماجستير الهندسة في الابتكار والاستدامة وريادة الأعمال المدرج برسومه في صفحة رسوم الدراسات العليا دون أي مدخل له في قائمة القبول في الدراسات العليا. كما تختلف قوائم برامج الدراسات العليا بين صفحة مكتب القبول وصفحة برامج الدراسات العليا وصفحة الدرجات والبرامج.</t>
+          <t>تذكر الصفحة أن البرامج معتمدة من جهات وطنية ودولية مرموقة دون تسمية هذه الجهات أو الإحالة إلى صفحة الاعتماد الأكاديمي.</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>تصحيح مطلوب</t>
+          <t>توصية تحسين</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>متوسطة</t>
+          <t>منخفضة</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>اعتماد قائمة موحدة بالبرامج المفتوحة للقبول تُغذّي جميع الصفحات من مصدر واحد، بعد أن تؤكد الجهات الأكاديمية المالكة البرامج المتاحة فعليًا (بما فيها برنامج الطب مع بيان إتاحته للطلاب والطالبات، وبرنامج الابتكار والاستدامة وريادة الأعمال).</t>
-        </is>
-      </c>
-      <c r="L15" s="6" t="inlineStr">
-        <is>
-          <t>حالة ماجستير الهندسة في الابتكار والاستدامة وريادة الأعمال (مفتوح للقبول أم لا) تحتاج تأكيدًا من الجهة المالكة. أما اختلاف مسمى ماجستير التنمية البشرية فمعالج في ملاحظة مستقلة.</t>
-        </is>
-      </c>
+          <t>تسمية جهات الاعتماد لكل برنامج أو إضافة رابط إلى صفحة الاعتماد الأكاديمي الرسمية.</t>
+        </is>
+      </c>
+      <c r="L15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="8" t="n">
@@ -1331,27 +1331,27 @@
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>صفحة الدرجات والبرامج – جداول البرامج</t>
+          <t>صفحة الدرجات والبرامج – جدولا البرامج الجامعية وبرامج الدراسات العليا؛ مقارنةً بقائمة الدراسات العليا في صفحة مكتب القبول وصفحة برامج الدراسات العليا وصفحة رسوم الدراسات العليا</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>PhD. in Mechanical Engineering ; Masters in Business Administration (MBA) ; College of Computer Engineering and Science</t>
+          <t>College of Law … B.A. in Law … Graduate Programs ; Admissions to the EMGMS Program ; Master of Engineering in Innovation, Sustainability, and Entrepreneurship (33) | SAR 80,000 | SAR 80,000</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>الاتساق</t>
+          <t>دقة المعلومات</t>
         </is>
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>عدم اتساق مسميات الدرجات</t>
+          <t>قائمة برامج غير مكتملة</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>تُكتب الدرجة "PhD." بصيغة غير قياسية في حين تستخدم صفحة الرسوم "Ph.D."، ويرد "Masters in Business Administration" بدل الصيغة القياسية "Master of Business Administration"، ويختلف اسم الكلية عن صيغته في تذييل الموقع "College of Computer Engineering &amp; Sciences".</t>
+          <t>لا تتضمن صفحة الدرجات والبرامج برنامج كلية الطب ولا ماجستير الإدارة الهندسية (EMGMS) مع أن لكليهما صفحة قبول، ولا ماجستير الهندسة في الابتكار والاستدامة وريادة الأعمال المدرج برسومه في صفحة رسوم الدراسات العليا دون أي مدخل له في قائمة القبول في الدراسات العليا. كما تختلف قوائم برامج الدراسات العليا بين صفحة مكتب القبول وصفحة برامج الدراسات العليا وصفحة الدرجات والبرامج.</t>
         </is>
       </c>
       <c r="I16" s="8" t="inlineStr">
@@ -1361,15 +1361,19 @@
       </c>
       <c r="J16" s="8" t="inlineStr">
         <is>
-          <t>منخفضة</t>
+          <t>متوسطة</t>
         </is>
       </c>
       <c r="K16" s="9" t="inlineStr">
         <is>
-          <t>توحيد الصيغ إلى "Ph.D." (أو "PhD") و"Master of Business Administration (MBA)"، واعتماد الاسم الرسمي للكلية في جميع المواضع.</t>
-        </is>
-      </c>
-      <c r="L16" s="9" t="inlineStr"/>
+          <t>اعتماد قائمة موحدة بالبرامج المفتوحة للقبول تُغذّي جميع الصفحات من مصدر واحد، بعد أن تؤكد الجهات الأكاديمية المالكة البرامج المتاحة فعليًا (بما فيها برنامج الطب مع بيان إتاحته للطلاب والطالبات، وبرنامج الابتكار والاستدامة وريادة الأعمال).</t>
+        </is>
+      </c>
+      <c r="L16" s="9" t="inlineStr">
+        <is>
+          <t>حالة ماجستير الهندسة في الابتكار والاستدامة وريادة الأعمال (مفتوح للقبول أم لا) تحتاج تأكيدًا من الجهة المالكة. أما اختلاف مسمى ماجستير التنمية البشرية فمعالج في ملاحظة مستقلة.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
@@ -1377,37 +1381,37 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>تقويم القبول</t>
+          <t>الدرجات والبرامج</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/admission_calendar_fs_ro</t>
+          <t>https://pmu.edu.sa/admission/degrees_programs_fs_ro</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>صفحة تقويم القبول – تقويم القبول في البكالوريوس لخريف 2026-2027</t>
+          <t>صفحة الدرجات والبرامج – جداول البرامج</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>Fall 2026-2027 … Last day to submit IELTS or TOEFL iBT | 2026-07-20 … Last day for Transfer applicants to submit documents in person | 2026-07-20 … First day of classes | 2026-08-30 … Announcement of admission results through Qabool platform | From July 19 to July 21, 2026</t>
+          <t>PhD. in Mechanical Engineering ; Masters in Business Administration (MBA) ; College of Computer Engineering and Science</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>دقة المعلومات</t>
+          <t>الاتساق</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>معلومة قديمة وتسلسل غير منطقي</t>
+          <t>عدم اتساق مسميات الدرجات</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>يعرض تقويم القبول دورة خريف 2026-2027 وحدها، وجميع مواعيدها انقضت (آخرها بدء الدراسة في 30 أغسطس 2026)، دون إعلان عن الدورة التالية أو عن إغلاق القبول. كما يبدأ إعلان نتائج القبول (19–21 يوليو 2026) قبل يوم من آخر موعد لتقديم درجات IELTS/TOEFL ووثائق المتقدمين المحولين (20 يوليو 2026)، دون توضيح لكيفية التعامل مع ذلك.</t>
+          <t>تُكتب الدرجة "PhD." بصيغة غير قياسية في حين تستخدم صفحة الرسوم "Ph.D."، ويرد "Masters in Business Administration" بدل الصيغة القياسية "Master of Business Administration"، ويختلف اسم الكلية عن صيغته في تذييل الموقع "College of Computer Engineering &amp; Sciences".</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -1417,19 +1421,15 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>عالية</t>
+          <t>منخفضة</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>نشر تقويم الدورة القادمة أو عبارة صريحة بإغلاق القبول مع موعد فتح الدورة التالية، وترتيب البنود زمنيًا مع بيان الفئة التي ينطبق عليها كل موعد؛ ويتطلب ذلك اعتماد مواعيد الدورة القادمة من مكتب القبول.</t>
-        </is>
-      </c>
-      <c r="L17" s="6" t="inlineStr">
-        <is>
-          <t>قد يكون تداخل موعد النتائج مع آخر موعد للوثائق مقصودًا لفئات مختلفة من المتقدمين؛ يلزم تأكيد ذلك من مكتب القبول.</t>
-        </is>
-      </c>
+          <t>توحيد الصيغ إلى "Ph.D." (أو "PhD") و"Master of Business Administration (MBA)"، واعتماد الاسم الرسمي للكلية في جميع المواضع.</t>
+        </is>
+      </c>
+      <c r="L17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="n">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>صفحة تقويم القبول – بند اللقاء التعريفي في تقويم البكالوريوس</t>
+          <t>صفحة تقويم القبول – تقويم القبول في البكالوريوس لخريف 2026-2027</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>Orientation for new applicants | TBA</t>
+          <t>Fall 2026-2027 … Last day to submit IELTS or TOEFL iBT | 2026-07-20 … Last day for Transfer applicants to submit documents in person | 2026-07-20 … First day of classes | 2026-08-30 … Announcement of admission results through Qabool platform | From July 19 to July 21, 2026</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>معلومة غير مكتملة</t>
+          <t>معلومة قديمة وتسلسل غير منطقي</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>لا يزال موعد اللقاء التعريفي للمتقدمين الجدد "TBA" مع أن الدراسة بدأت في 30 أغسطس 2026، في حين يحدد التقويم الأكاديمي 2026-2027 اللقاء التعريفي للطلاب الجدد في 27 أغسطس 2026 و14 يناير 2027؛ ولا يتضمن تقويم القبول أي نافذة قبول لفصل الربيع.</t>
+          <t>يعرض تقويم القبول دورة خريف 2026-2027 وحدها، وجميع مواعيدها انقضت (آخرها بدء الدراسة في 30 أغسطس 2026)، دون إعلان عن الدورة التالية أو عن إغلاق القبول. كما يبدأ إعلان نتائج القبول (19–21 يوليو 2026) قبل يوم من آخر موعد لتقديم درجات IELTS/TOEFL ووثائق المتقدمين المحولين (20 يوليو 2026)، دون توضيح لكيفية التعامل مع ذلك.</t>
         </is>
       </c>
       <c r="I18" s="8" t="inlineStr">
@@ -1477,17 +1477,17 @@
       </c>
       <c r="J18" s="8" t="inlineStr">
         <is>
-          <t>متوسطة</t>
+          <t>عالية</t>
         </is>
       </c>
       <c r="K18" s="9" t="inlineStr">
         <is>
-          <t>استبدال "TBA" بالموعد الفعلي أو حذف البند، ونشر نافذة القبول التالية (ومنها الربيع إن كان القبول فيه متاحًا) بما يتسق مع التقويم الأكاديمي.</t>
+          <t>نشر تقويم الدورة القادمة أو عبارة صريحة بإغلاق القبول مع موعد فتح الدورة التالية، وترتيب البنود زمنيًا مع بيان الفئة التي ينطبق عليها كل موعد؛ ويتطلب ذلك اعتماد مواعيد الدورة القادمة من مكتب القبول.</t>
         </is>
       </c>
       <c r="L18" s="9" t="inlineStr">
         <is>
-          <t>إتاحة القبول في فصل الربيع قرار يعود إلى مكتب القبول ويلزم تأكيده.</t>
+          <t>قد يكون تداخل موعد النتائج مع آخر موعد للوثائق مقصودًا لفئات مختلفة من المتقدمين؛ يلزم تأكيد ذلك من مكتب القبول.</t>
         </is>
       </c>
     </row>
@@ -1507,12 +1507,12 @@
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>صفحة تقويم القبول – بندا التقديم للطلاب غير السعوديين وإعلان النتائج</t>
+          <t>صفحة تقويم القبول – بند اللقاء التعريفي في تقويم البكالوريوس</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>For non Saudi Students: Apply online through Study in Saudi platform: https://studyinsaudi.sa/ar | Closed … Announcement of admission results through Qabool platform | From July 19 to July 21, 2026</t>
+          <t>Orientation for new applicants | TBA</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -1522,30 +1522,34 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>معلومة ناقصة</t>
+          <t>معلومة غير مكتملة</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>يحدد التقويم منصة "قبول" وحدها قناةً لإعلان النتائج، ولا يذكر كيف أو متى يتلقى المتقدمون غير السعوديين الذين يتقدمون عبر منصة "ادرس في السعودية" نتائجهم.</t>
+          <t>لا يزال موعد اللقاء التعريفي للمتقدمين الجدد "TBA" مع أن الدراسة بدأت في 30 أغسطس 2026، في حين يحدد التقويم الأكاديمي 2026-2027 اللقاء التعريفي للطلاب الجدد في 27 أغسطس 2026 و14 يناير 2027؛ ولا يتضمن تقويم القبول أي نافذة قبول لفصل الربيع.</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>توصية تحسين</t>
+          <t>تصحيح مطلوب</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>منخفضة</t>
+          <t>متوسطة</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>بيان قناة إعلان النتائج وموعدها للمتقدمين غير السعوديين.</t>
-        </is>
-      </c>
-      <c r="L19" s="6" t="inlineStr"/>
+          <t>استبدال "TBA" بالموعد الفعلي أو حذف البند، ونشر نافذة القبول التالية (ومنها الربيع إن كان القبول فيه متاحًا) بما يتسق مع التقويم الأكاديمي.</t>
+        </is>
+      </c>
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>إتاحة القبول في فصل الربيع قرار يعود إلى مكتب القبول ويلزم تأكيده.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="n">
@@ -1563,32 +1567,32 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>صفحة تقويم القبول – شيفرة الصفحة (نسخة ثانية من جدولي التقويم)</t>
+          <t>صفحة تقويم القبول – بندا التقديم للطلاب غير السعوديين وإعلان النتائج</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>Fall 2026-2027 Undergraduate Admission Calendar … First day of classes 2026-08-30 … For non Saudi Students: Apply online through Study in Saudi platform … Closed</t>
+          <t>For non Saudi Students: Apply online through Study in Saudi platform: https://studyinsaudi.sa/ar | Closed … Announcement of admission results through Qabool platform | From July 19 to July 21, 2026</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>وظيفي وتقني</t>
+          <t>دقة المعلومات</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>محتوى مكرر</t>
+          <t>معلومة ناقصة</t>
         </is>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>تتضمن شيفرة صفحة تقويم القبول نسخة ثانية من جدولي تقويم البكالوريوس والدراسات العليا، يختلف فيها موضع بند الطلاب غير السعوديين، مما قد يُظهرها في بعض طرق العرض ويعرّض النسختين لعدم التطابق عند التحديث.</t>
+          <t>يحدد التقويم منصة "قبول" وحدها قناةً لإعلان النتائج، ولا يذكر كيف أو متى يتلقى المتقدمون غير السعوديين الذين يتقدمون عبر منصة "ادرس في السعودية" نتائجهم.</t>
         </is>
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>تصحيح مطلوب</t>
+          <t>توصية تحسين</t>
         </is>
       </c>
       <c r="J20" s="8" t="inlineStr">
@@ -1598,14 +1602,10 @@
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
-          <t>حذف الجداول المكررة والإبقاء على نسخة واحدة تُحدَّث.</t>
-        </is>
-      </c>
-      <c r="L20" s="9" t="inlineStr">
-        <is>
-          <t>العرض المرئي الذي جرى التقاطه يُظهر كل جدول مرة واحدة، والتكرار موجود في النص الكامل المستخرج من الصفحة.</t>
-        </is>
-      </c>
+          <t>بيان قناة إعلان النتائج وموعدها للمتقدمين غير السعوديين.</t>
+        </is>
+      </c>
+      <c r="L20" s="9" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
@@ -1623,27 +1623,27 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>صفحة تقويم القبول – بنود جدول البكالوريوس</t>
+          <t>صفحة تقويم القبول – شيفرة الصفحة (نسخة ثانية من جدولي التقويم)</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>For non Saudi Students: Apply online through Study in Saudi platform ; Start of English Placement Test and personal Interviews | 2026-05-17</t>
+          <t>Fall 2026-2027 Undergraduate Admission Calendar … First day of classes 2026-08-30 … For non Saudi Students: Apply online through Study in Saudi platform … Closed</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>لغوي ونحوي</t>
+          <t>وظيفي وتقني</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>أخطاء في الترقيم والأحرف الكبيرة</t>
+          <t>محتوى مكرر</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>ترد عبارة "non Saudi" دون الشرطة الواصلة، ويختلف استخدام الأحرف الكبيرة في عبارة "personal Interviews".</t>
+          <t>تتضمن شيفرة صفحة تقويم القبول نسخة ثانية من جدولي تقويم البكالوريوس والدراسات العليا، يختلف فيها موضع بند الطلاب غير السعوديين، مما قد يُظهرها في بعض طرق العرض ويعرّض النسختين لعدم التطابق عند التحديث.</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
@@ -1658,10 +1658,14 @@
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>التصحيح إلى "For non-Saudi Students:" و"Start of English Placement Test and Personal Interviews".</t>
-        </is>
-      </c>
-      <c r="L21" s="6" t="inlineStr"/>
+          <t>حذف الجداول المكررة والإبقاء على نسخة واحدة تُحدَّث.</t>
+        </is>
+      </c>
+      <c r="L21" s="6" t="inlineStr">
+        <is>
+          <t>العرض المرئي الذي جرى التقاطه يُظهر كل جدول مرة واحدة، والتكرار موجود في النص الكامل المستخرج من الصفحة.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="n">
@@ -1679,32 +1683,32 @@
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>صفحة تقويم القبول – زر "Apply Now" فوق جدولي التقويم</t>
+          <t>صفحة تقويم القبول – بنود جدول البكالوريوس</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>Apply Now</t>
+          <t>For non Saudi Students: Apply online through Study in Saudi platform ; Start of English Placement Test and personal Interviews | 2026-05-17</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>وظيفي وتقني</t>
+          <t>لغوي ونحوي</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>رابط غير قياسي</t>
+          <t>أخطاء في الترقيم والأحرف الكبيرة</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>يعمل زر "Apply Now" في صفحة التقويم عبر استدعاء برمجي للخادم (postback) بدل رابط عادي، فلا يمكن فتحه في تبويب جديد أو نسخه، وتصل عدة صيغ مختلفة للروابط إلى بوابة التقديم نفسها.</t>
+          <t>ترد عبارة "non Saudi" دون الشرطة الواصلة، ويختلف استخدام الأحرف الكبيرة في عبارة "personal Interviews".</t>
         </is>
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>متابعة وتحقق</t>
+          <t>تصحيح مطلوب</t>
         </is>
       </c>
       <c r="J22" s="8" t="inlineStr">
@@ -1714,14 +1718,10 @@
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
-          <t>استبدال الزر برابط قياسي مباشر إلى عنوان موحد لبوابة التقديم.</t>
-        </is>
-      </c>
-      <c r="L22" s="9" t="inlineStr">
-        <is>
-          <t>نص الزر موجود في الأدلة، أما شيفرة الرابط البرمجي فلم تُحفظ ضمن النصوص المستخرجة؛ يُتحقق منها في الصفحة الحية قبل التنفيذ.</t>
-        </is>
-      </c>
+          <t>التصحيح إلى "For non-Saudi Students:" و"Start of English Placement Test and Personal Interviews".</t>
+        </is>
+      </c>
+      <c r="L22" s="9" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
@@ -1729,57 +1729,57 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>استفسار القبول</t>
+          <t>تقويم القبول</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/admissions_queries</t>
+          <t>https://pmu.edu.sa/admission/admission_calendar_fs_ro</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>صفحة استفسار القبول – نموذج الاستفسار؛ وصفحة التواصل للدراسات العليا</t>
+          <t>صفحة تقويم القبول – زر "Apply Now" فوق جدولي التقويم</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>Welcome to PMU, the Admissions Office is glad to answer your inquiries. … Name [الأسم]: * … Email [البريد الإلكتروني]:* … Mobile number [رقم الجوال]:*</t>
+          <t>Apply Now</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>تنظيمي</t>
+          <t>وظيفي وتقني</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>غياب إشعار الخصوصية وقنوات التواصل</t>
+          <t>رابط غير قياسي</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>يجمع نموذج استفسار القبول الاسم والبريد الإلكتروني ورقم الجوال دون أي إشعار خصوصية ظاهر، ولا تقدم الصفحة بريدًا إلكترونيًا أو هاتفًا بديلًا لمكتب القبول ولا مدة متوقعة للرد؛ كما تقتصر صفحة التواصل للدراسات العليا على المكتب والبريد الإلكتروني دون هاتف.</t>
+          <t>يعمل زر "Apply Now" في صفحة التقويم عبر استدعاء برمجي للخادم (postback) بدل رابط عادي، فلا يمكن فتحه في تبويب جديد أو نسخه، وتصل عدة صيغ مختلفة للروابط إلى بوابة التقديم نفسها.</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>تصحيح مطلوب</t>
+          <t>متابعة وتحقق</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>متوسطة</t>
+          <t>منخفضة</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>إضافة إشعار خصوصية بعد مراجعته من الجهة المختصة بالامتثال، وإضافة البريد الإلكتروني الرسمي ورقم الهاتف لمكتب القبول ومدة الرد المتوقعة بجوار النموذج.</t>
+          <t>استبدال الزر برابط قياسي مباشر إلى عنوان موحد لبوابة التقديم.</t>
         </is>
       </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
-          <t>صياغة إشعار الخصوصية تتطلب اعتماد الجهة القانونية/جهة الامتثال.</t>
+          <t>نص الزر موجود في الأدلة، أما شيفرة الرابط البرمجي فلم تُحفظ ضمن النصوص المستخرجة؛ يُتحقق منها في الصفحة الحية قبل التنفيذ.</t>
         </is>
       </c>
     </row>
@@ -1799,27 +1799,27 @@
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>صفحة استفسار القبول – نص الترحيب وعناوين حقول التحقق</t>
+          <t>صفحة استفسار القبول – نموذج الاستفسار؛ وصفحة التواصل للدراسات العليا</t>
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>Please fill the below request: ; Verification Code[رمز التحقق]:* ; Enter Verifaction Code[أدخل رمز التحقق]:*</t>
+          <t>Welcome to PMU, the Admissions Office is glad to answer your inquiries. … Name [الأسم]: * … Email [البريد الإلكتروني]:* … Mobile number [رقم الجوال]:*</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>لغوي ونحوي</t>
+          <t>تنظيمي</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>صياغة ركيكة ومسافات ناقصة</t>
+          <t>غياب إشعار الخصوصية وقنوات التواصل</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>عبارة "Please fill the below request" ركيكة، ويفتقد عنوانا حقلي التحقق المسافة قبل القوس الذي يضم النص العربي.</t>
+          <t>يجمع نموذج استفسار القبول الاسم والبريد الإلكتروني ورقم الجوال دون أي إشعار خصوصية ظاهر، ولا تقدم الصفحة بريدًا إلكترونيًا أو هاتفًا بديلًا لمكتب القبول ولا مدة متوقعة للرد؛ كما تقتصر صفحة التواصل للدراسات العليا على المكتب والبريد الإلكتروني دون هاتف.</t>
         </is>
       </c>
       <c r="I24" s="8" t="inlineStr">
@@ -1829,15 +1829,19 @@
       </c>
       <c r="J24" s="8" t="inlineStr">
         <is>
-          <t>منخفضة</t>
+          <t>متوسطة</t>
         </is>
       </c>
       <c r="K24" s="9" t="inlineStr">
         <is>
-          <t>التصحيح إلى "Please fill in the form below:" وإضافة مسافة قبل القوس في العنوانين.</t>
-        </is>
-      </c>
-      <c r="L24" s="9" t="inlineStr"/>
+          <t>إضافة إشعار خصوصية بعد مراجعته من الجهة المختصة بالامتثال، وإضافة البريد الإلكتروني الرسمي ورقم الهاتف لمكتب القبول ومدة الرد المتوقعة بجوار النموذج.</t>
+        </is>
+      </c>
+      <c r="L24" s="9" t="inlineStr">
+        <is>
+          <t>صياغة إشعار الخصوصية تتطلب اعتماد الجهة القانونية/جهة الامتثال.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
@@ -1855,12 +1859,12 @@
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>صفحة استفسار القبول – النص العربي للترحيب وعناوين الحقول؛ وعنوان "نسب الموزونة" في صفحة التقديم /apply</t>
+          <t>صفحة استفسار القبول – نص الترحيب وعناوين حقول التحقق</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>:مرحباً بكم بجامعة الأمير محمد بن فهد، مكتب القبول يسعد بالإجابة على إستفساراتكم. … Name [الأسم] ; Query [الإستفسار] ; Email [البريد الإللكتروني] ; نسب الموزونة</t>
+          <t>Please fill the below request: ; Verification Code[رمز التحقق]:* ; Enter Verifaction Code[أدخل رمز التحقق]:*</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -1870,12 +1874,12 @@
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>أخطاء إملائية ونحوية عربية</t>
+          <t>صياغة ركيكة ومسافات ناقصة</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>يتضمن النص العربي أخطاء إملائية في همزة الوصل ("الأسم"، "الإستفسار"، "إستفساراتكم")، وتكرار حرف في "الإللكتروني"، وموضعًا خاطئًا للنقطتين في بداية جملة الترحيب، إضافة إلى خطأ نحوي في عنوان "نسب الموزونة" بصفحة التقديم (مكرر مرتين).</t>
+          <t>عبارة "Please fill the below request" ركيكة، ويفتقد عنوانا حقلي التحقق المسافة قبل القوس الذي يضم النص العربي.</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
@@ -1890,7 +1894,7 @@
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>التصحيح إلى "الاسم" و"الاستفسار" و"استفساراتكم" و"البريد الإلكتروني" و"النسب الموزونة"، ونقل النقطتين إلى نهاية الجملة العربية مع ضبط اتجاه السطر من اليمين إلى اليسار.</t>
+          <t>التصحيح إلى "Please fill in the form below:" وإضافة مسافة قبل القوس في العنوانين.</t>
         </is>
       </c>
       <c r="L25" s="6" t="inlineStr"/>
@@ -1901,37 +1905,37 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>صفحة التقديم /apply</t>
+          <t>استفسار القبول</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>https://www.pmu.edu.sa/apply</t>
+          <t>https://pmu.edu.sa/admission/admissions_queries</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>صفحة التقديم /apply – قسم متطلبات القبول في البكالوريوس (يُعاد التوجيه فورًا إلى بوابة التقديم)</t>
+          <t>صفحة استفسار القبول – النص العربي للترحيب وعناوين الحقول؛ وعنوان "نسب الموزونة" في صفحة التقديم /apply</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>Bachelor’s Programs — Admission Requirements … High school 80% or higher … Qudrat 60% or equivalent SAT 1 score … High school average: 85% or higher … Qudrat 65% or higher … Tahseely 65% or higher</t>
+          <t>:مرحباً بكم بجامعة الأمير محمد بن فهد، مكتب القبول يسعد بالإجابة على إستفساراتكم. … Name [الأسم] ; Query [الإستفسار] ; Email [البريد الإللكتروني] ; نسب الموزونة</t>
         </is>
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>وظيفي وتقني</t>
+          <t>لغوي ونحوي</t>
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>محتوى غير ظاهر للمتقدم</t>
+          <t>أخطاء إملائية ونحوية عربية</t>
         </is>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>تتضمن صفحة /apply باللغتين الحدود الدنيا والنسب الموزونة لبرامج البكالوريوس، لكنها تُعيد التوجيه فورًا إلى بوابة التقديم، فلا يراها المتقدم، ولا تعرض البوابة هذه المتطلبات. وتعادل الحدود الدنيا المنشورة نسبة موزونة قدرها 72% للتخصصات غير الهندسية و73% للهندسة والذكاء الاصطناعي وعلوم الحاسب والعمارة دون أن تُذكر صراحة.</t>
+          <t>يتضمن النص العربي أخطاء إملائية في همزة الوصل ("الأسم"، "الإستفسار"، "إستفساراتكم")، وتكرار حرف في "الإللكتروني"، وموضعًا خاطئًا للنقطتين في بداية جملة الترحيب، إضافة إلى خطأ نحوي في عنوان "نسب الموزونة" بصفحة التقديم (مكرر مرتين).</t>
         </is>
       </c>
       <c r="I26" s="8" t="inlineStr">
@@ -1941,19 +1945,15 @@
       </c>
       <c r="J26" s="8" t="inlineStr">
         <is>
-          <t>متوسطة</t>
+          <t>منخفضة</t>
         </is>
       </c>
       <c r="K26" s="9" t="inlineStr">
         <is>
-          <t>نشر متطلبات القبول في صفحة ظاهرة ومرتبطة بمسار التقديم، وأن يؤكد مكتب القبول الحد الأدنى المعتمد للنسبة الموزونة ويقرر بقاء المحتوى المخفي أو حذفه.</t>
-        </is>
-      </c>
-      <c r="L26" s="9" t="inlineStr">
-        <is>
-          <t>النسبتان 72% و73% محسوبتان من الحدود الدنيا والأوزان المنشورة، ويلزم تأكيد كونهما الحد الأدنى المعتمد.</t>
-        </is>
-      </c>
+          <t>التصحيح إلى "الاسم" و"الاستفسار" و"استفساراتكم" و"البريد الإلكتروني" و"النسب الموزونة"، ونقل النقطتين إلى نهاية الجملة العربية مع ضبط اتجاه السطر من اليمين إلى اليسار.</t>
+        </is>
+      </c>
+      <c r="L26" s="9" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
@@ -1971,27 +1971,27 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>صفحة التقديم /apply – تخصصات الهندسة والذكاء الاصطناعي؛ مقارنةً بصفحة اختبار SAT وصفحة متطلبات تخصصات الحاسب والهندسة</t>
+          <t>صفحة التقديم /apply – قسم متطلبات القبول في البكالوريوس (يُعاد التوجيه فورًا إلى بوابة التقديم)</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>/apply: "a SAT 1 total score of 1200 is accepted in place of both Qudrat and Tahseely" | SAT: "Students with international high school certificate might submit SAT with minimum score of 1200 instead of Qudrat and Tahseely tests" | CS/Eng: "(SAAT – Tahseely) or SAT 1 (1200)"</t>
+          <t>Bachelor’s Programs — Admission Requirements … High school 80% or higher … Qudrat 60% or equivalent SAT 1 score … High school average: 85% or higher … Qudrat 65% or higher … Tahseely 65% or higher</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>الاتساق</t>
+          <t>وظيفي وتقني</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>تعارض في شروط القبول</t>
+          <t>محتوى غير ظاهر للمتقدم</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>يُوصف بديل SAT 1 بدرجة 1200 بثلاث صيغ مختلفة: في /apply بديلًا عن القدرات والتحصيلي لجميع المتقدمين لتخصصات الهندسة والذكاء الاصطناعي والحاسب والعمارة، وفي صفحة SAT مقصورًا على حملة الشهادات الثانوية الدولية، وفي صفحة تخصصات الحاسب والهندسة بديلًا عن التحصيلي فقط.</t>
+          <t>تتضمن صفحة /apply باللغتين الحدود الدنيا والنسب الموزونة لبرامج البكالوريوس، لكنها تُعيد التوجيه فورًا إلى بوابة التقديم، فلا يراها المتقدم، ولا تعرض البوابة هذه المتطلبات. وتعادل الحدود الدنيا المنشورة نسبة موزونة قدرها 72% للتخصصات غير الهندسية و73% للهندسة والذكاء الاصطناعي وعلوم الحاسب والعمارة دون أن تُذكر صراحة.</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
@@ -2006,10 +2006,14 @@
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>أن يحدد مكتب القبول القاعدة المعتمدة لبديل SAT (الفئة المستفيدة والاختبارات التي يحل محلها)، ثم نشرها بصيغة واحدة في جميع الصفحات.</t>
-        </is>
-      </c>
-      <c r="L27" s="6" t="inlineStr"/>
+          <t>نشر متطلبات القبول في صفحة ظاهرة ومرتبطة بمسار التقديم، وأن يؤكد مكتب القبول الحد الأدنى المعتمد للنسبة الموزونة ويقرر بقاء المحتوى المخفي أو حذفه.</t>
+        </is>
+      </c>
+      <c r="L27" s="6" t="inlineStr">
+        <is>
+          <t>النسبتان 72% و73% محسوبتان من الحدود الدنيا والأوزان المنشورة، ويلزم تأكيد كونهما الحد الأدنى المعتمد.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="n">
@@ -2027,27 +2031,27 @@
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>صفحة التقديم /apply – الحد الأدنى للتخصصات غير الهندسية</t>
+          <t>صفحة التقديم /apply – تخصصات الهندسة والذكاء الاصطناعي؛ مقارنةً بصفحة اختبار SAT وصفحة متطلبات تخصصات الحاسب والهندسة</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>Qudrat 60% or equivalent SAT 1 score</t>
+          <t>/apply: "a SAT 1 total score of 1200 is accepted in place of both Qudrat and Tahseely" | SAT: "Students with international high school certificate might submit SAT with minimum score of 1200 instead of Qudrat and Tahseely tests" | CS/Eng: "(SAAT – Tahseely) or SAT 1 (1200)"</t>
         </is>
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>دقة المعلومات</t>
+          <t>الاتساق</t>
         </is>
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
-          <t>معلومة ناقصة</t>
+          <t>تعارض في شروط القبول</t>
         </is>
       </c>
       <c r="H28" s="9" t="inlineStr">
         <is>
-          <t>تشترط الصفحة للتخصصات غير الهندسية "القدرات 60% أو ما يعادلها من SAT 1" دون ذكر الدرجة المعادلة، في حين تُذكر درجة 1200 لمجموعة الهندسة والذكاء الاصطناعي.</t>
+          <t>يُوصف بديل SAT 1 بدرجة 1200 بثلاث صيغ مختلفة: في /apply بديلًا عن القدرات والتحصيلي لجميع المتقدمين لتخصصات الهندسة والذكاء الاصطناعي والحاسب والعمارة، وفي صفحة SAT مقصورًا على حملة الشهادات الثانوية الدولية، وفي صفحة تخصصات الحاسب والهندسة بديلًا عن التحصيلي فقط.</t>
         </is>
       </c>
       <c r="I28" s="8" t="inlineStr">
@@ -2057,12 +2061,12 @@
       </c>
       <c r="J28" s="8" t="inlineStr">
         <is>
-          <t>منخفضة</t>
+          <t>متوسطة</t>
         </is>
       </c>
       <c r="K28" s="9" t="inlineStr">
         <is>
-          <t>ذكر الحد الأدنى لدرجة SAT 1 للتخصصات غير الهندسية في /apply وصفحة القبول في البكالوريوس، بعد اعتماده من مكتب القبول.</t>
+          <t>أن يحدد مكتب القبول القاعدة المعتمدة لبديل SAT (الفئة المستفيدة والاختبارات التي يحل محلها)، ثم نشرها بصيغة واحدة في جميع الصفحات.</t>
         </is>
       </c>
       <c r="L28" s="9" t="inlineStr"/>
@@ -2083,12 +2087,12 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>صفحة التقديم /apply – قسم رسوم التقديم؛ مقارنةً بصفحات القبول في البكالوريوس وكلية الطب</t>
+          <t>صفحة التقديم /apply – الحد الأدنى للتخصصات غير الهندسية</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>A non-refundable application fee of SAR 950 must be paid to complete the admission process. ; other pages: "SAR 950 (incl. VAT)" ; College of Medicine: "SAR 1000 (incl. VAT)"</t>
+          <t>Qudrat 60% or equivalent SAT 1 score</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
@@ -2098,12 +2102,12 @@
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>معلومة رسوم ناقصة</t>
+          <t>معلومة ناقصة</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>تذكر الصفحة رسوم تقديم بقيمة 950 ريالًا دون بيان أنها شاملة ضريبة القيمة المضافة كما في صفحات البكالوريوس الأخرى، وتعرض رسومًا ومعايير عامة لجميع برامج البكالوريوس دون الإشارة إلى أن لكلية الطب رسوم تقديم قدرها 1000 ريال شاملة ضريبة القيمة المضافة ومعايير أعلى (منها SAT 1 بدرجة 1300).</t>
+          <t>تشترط الصفحة للتخصصات غير الهندسية "القدرات 60% أو ما يعادلها من SAT 1" دون ذكر الدرجة المعادلة، في حين تُذكر درجة 1200 لمجموعة الهندسة والذكاء الاصطناعي.</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
@@ -2118,7 +2122,7 @@
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>إضافة عبارة "شاملة ضريبة القيمة المضافة" إلى بيان الرسوم، وإضافة إشارة أو رابط إلى رسوم كلية الطب ومعاييرها الخاصة (أو عبارة "تختلف الرسوم حسب البرنامج").</t>
+          <t>ذكر الحد الأدنى لدرجة SAT 1 للتخصصات غير الهندسية في /apply وصفحة القبول في البكالوريوس، بعد اعتماده من مكتب القبول.</t>
         </is>
       </c>
       <c r="L29" s="6" t="inlineStr"/>
@@ -2139,27 +2143,27 @@
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>صفحة التقديم /apply – قسم التخصصات غير الهندسية؛ مقارنةً بصفحة القبول في البكالوريوس</t>
+          <t>صفحة التقديم /apply – قسم رسوم التقديم؛ مقارنةً بصفحات القبول في البكالوريوس وكلية الطب</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>* Students with a lower percentage can apply; however, acceptance will depend on the overall weight.</t>
+          <t>A non-refundable application fee of SAR 950 must be paid to complete the admission process. ; other pages: "SAR 950 (incl. VAT)" ; College of Medicine: "SAR 1000 (incl. VAT)"</t>
         </is>
       </c>
       <c r="F30" s="9" t="inlineStr">
         <is>
-          <t>الاتساق</t>
+          <t>دقة المعلومات</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>ملاحظة غير متسقة بين الصفحات</t>
+          <t>معلومة رسوم ناقصة</t>
         </is>
       </c>
       <c r="H30" s="9" t="inlineStr">
         <is>
-          <t>ترد ملاحظة إمكانية تقديم الحاصلين على نسب أقل في /apply تحت مجموعة الهندسة والذكاء الاصطناعي وحدها، في حين تطبقها صفحة القبول في البكالوريوس على القبول العام (غير الهندسي) أيضًا.</t>
+          <t>تذكر الصفحة رسوم تقديم بقيمة 950 ريالًا دون بيان أنها شاملة ضريبة القيمة المضافة كما في صفحات البكالوريوس الأخرى، وتعرض رسومًا ومعايير عامة لجميع برامج البكالوريوس دون الإشارة إلى أن لكلية الطب رسوم تقديم قدرها 1000 ريال شاملة ضريبة القيمة المضافة ومعايير أعلى (منها SAT 1 بدرجة 1300).</t>
         </is>
       </c>
       <c r="I30" s="8" t="inlineStr">
@@ -2174,7 +2178,7 @@
       </c>
       <c r="K30" s="9" t="inlineStr">
         <is>
-          <t>إضافة الملاحظة نفسها بالعربية والإنجليزية إلى قسم التخصصات غير الهندسية، بعد تأكيد مكتب القبول انطباقها عليه.</t>
+          <t>إضافة عبارة "شاملة ضريبة القيمة المضافة" إلى بيان الرسوم، وإضافة إشارة أو رابط إلى رسوم كلية الطب ومعاييرها الخاصة (أو عبارة "تختلف الرسوم حسب البرنامج").</t>
         </is>
       </c>
       <c r="L30" s="9" t="inlineStr"/>
@@ -2195,12 +2199,12 @@
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>صفحة التقديم /apply – النص العربي لجدول التخصصات غير الهندسية وملاحظة اختبار التوفل</t>
+          <t>صفحة التقديم /apply – قسم التخصصات غير الهندسية؛ مقارنةً بصفحة القبول في البكالوريوس</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>القدرات / 1 SAT ; ملاحظة: لا يُقبل اختبار النسخة المنزلية. (EN: "Note: TOEFL Home Edition is not accepted.")</t>
+          <t>* Students with a lower percentage can apply; however, acceptance will depend on the overall weight.</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
@@ -2210,12 +2214,12 @@
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>عدم تطابق النصين العربي والإنجليزي</t>
+          <t>ملاحظة غير متسقة بين الصفحات</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>يظهر اسم الاختبار في الجدول العربي "1 SAT" بدل "SAT 1"، وتذكر الملاحظة العربية عدم قبول "النسخة المنزلية" دون تسمية اختبار التوفل خلافًا للنص الإنجليزي.</t>
+          <t>ترد ملاحظة إمكانية تقديم الحاصلين على نسب أقل في /apply تحت مجموعة الهندسة والذكاء الاصطناعي وحدها، في حين تطبقها صفحة القبول في البكالوريوس على القبول العام (غير الهندسي) أيضًا.</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
@@ -2230,7 +2234,7 @@
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>التصحيح إلى "القدرات / SAT 1" و"لا يُقبل اختبار التوفل (النسخة المنزلية)".</t>
+          <t>إضافة الملاحظة نفسها بالعربية والإنجليزية إلى قسم التخصصات غير الهندسية، بعد تأكيد مكتب القبول انطباقها عليه.</t>
         </is>
       </c>
       <c r="L31" s="6" t="inlineStr"/>
@@ -2251,12 +2255,12 @@
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>صفحة التقديم /apply – قسم الشهادات الثانوية الدولية؛ مقارنةً بصفحتي القبول في البكالوريوس والطلاب الدوليين</t>
+          <t>صفحة التقديم /apply – النص العربي لجدول التخصصات غير الهندسية وملاحظة اختبار التوفل</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>/apply: "Have the certificate stamped by the Saudi Embassy in their country" | UG Admissions: "attested, in advance, by the Saudi Consulate and other authorized organizations" | International: "certified by the Saudi Cultural Mission and Saudi Embassy"</t>
+          <t>القدرات / 1 SAT ; ملاحظة: لا يُقبل اختبار النسخة المنزلية. (EN: "Note: TOEFL Home Edition is not accepted.")</t>
         </is>
       </c>
       <c r="F32" s="9" t="inlineStr">
@@ -2266,12 +2270,12 @@
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>صياغات متباينة لشرط التصديق</t>
+          <t>عدم تطابق النصين العربي والإنجليزي</t>
         </is>
       </c>
       <c r="H32" s="9" t="inlineStr">
         <is>
-          <t>يُصاغ شرط تصديق الشهادة الثانوية الدولية بثلاث صيغ مختلفة: السفارة السعودية في /apply، والقنصلية السعودية وجهات أخرى معتمدة في صفحة القبول في البكالوريوس، والملحقية الثقافية السعودية والسفارة في صفحة الطلاب الدوليين.</t>
+          <t>يظهر اسم الاختبار في الجدول العربي "1 SAT" بدل "SAT 1"، وتذكر الملاحظة العربية عدم قبول "النسخة المنزلية" دون تسمية اختبار التوفل خلافًا للنص الإنجليزي.</t>
         </is>
       </c>
       <c r="I32" s="8" t="inlineStr">
@@ -2286,7 +2290,7 @@
       </c>
       <c r="K32" s="9" t="inlineStr">
         <is>
-          <t>اعتماد صيغة واحدة لشرط التصديق (الجهة المصدِّقة في بلد الدراسة مع معادلة وزارة التعليم) بعد تأكيدها من مكتب القبول، وتطبيقها في جميع الصفحات.</t>
+          <t>التصحيح إلى "القدرات / SAT 1" و"لا يُقبل اختبار التوفل (النسخة المنزلية)".</t>
         </is>
       </c>
       <c r="L32" s="9" t="inlineStr"/>
@@ -2297,22 +2301,22 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>بوابة التقديم</t>
+          <t>صفحة التقديم /apply</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>https://admissions.pmu.edu.sa/welcome</t>
+          <t>https://www.pmu.edu.sa/apply</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>بوابة التقديم – قسم Admission Calendar؛ مقارنةً بصفحة تقويم القبول</t>
+          <t>صفحة التقديم /apply – قسم الشهادات الثانوية الدولية؛ مقارنةً بصفحتي القبول في البكالوريوس والطلاب الدوليين</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>Admission Calendar | No events are currently published. Please check back later. … 2022 © PMU ; Admissions Calendar page: "Fall 2026-2027 Undergraduate Admission Calendar"</t>
+          <t>/apply: "Have the certificate stamped by the Saudi Embassy in their country" | UG Admissions: "attested, in advance, by the Saudi Consulate and other authorized organizations" | International: "certified by the Saudi Cultural Mission and Saudi Embassy"</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
@@ -2322,12 +2326,12 @@
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>تعارض بين مصدرين للتقويم</t>
+          <t>صياغات متباينة لشرط التصديق</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>تعرض بوابة التقديم عبارة "لا توجد أحداث منشورة حاليًا"، في حين تنشر صفحة تقويم القبول في الموقع مواعيد دورة خريف 2026-2027؛ كما يحمل تذييل البوابة تاريخ 2022.</t>
+          <t>يُصاغ شرط تصديق الشهادة الثانوية الدولية بثلاث صيغ مختلفة: السفارة السعودية في /apply، والقنصلية السعودية وجهات أخرى معتمدة في صفحة القبول في البكالوريوس، والملحقية الثقافية السعودية والسفارة في صفحة الطلاب الدوليين.</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
@@ -2337,12 +2341,12 @@
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>متوسطة</t>
+          <t>منخفضة</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>اعتماد مصدر واحد لتقويم القبول تُعرض منه المواعيد في البوابة والموقع معًا، وتحديث سنة التذييل.</t>
+          <t>اعتماد صيغة واحدة لشرط التصديق (الجهة المصدِّقة في بلد الدراسة مع معادلة وزارة التعليم) بعد تأكيدها من مكتب القبول، وتطبيقها في جميع الصفحات.</t>
         </is>
       </c>
       <c r="L33" s="6" t="inlineStr"/>
@@ -2363,49 +2367,45 @@
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>بوابة التقديم – الصفحة الترحيبية</t>
+          <t>بوابة التقديم – قسم Admission Calendar؛ مقارنةً بصفحة تقويم القبول</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>Creative minds … Transform the world … Student Login … New Student? Register! … Contact Admissions</t>
+          <t>Admission Calendar | No events are currently published. Please check back later. … 2022 © PMU ; Admissions Calendar page: "Fall 2026-2027 Undergraduate Admission Calendar"</t>
         </is>
       </c>
       <c r="F34" s="9" t="inlineStr">
         <is>
-          <t>تجربة المستخدم</t>
+          <t>الاتساق</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>غياب العربية وإشعار الخصوصية</t>
+          <t>تعارض بين مصدرين للتقويم</t>
         </is>
       </c>
       <c r="H34" s="9" t="inlineStr">
         <is>
-          <t>بوابة التقديم متاحة باللغة الإنجليزية وحدها، ولا تتضمن رابطًا لإشعار الخصوصية مع أنها نقطة تسجيل المتقدمين.</t>
+          <t>تعرض بوابة التقديم عبارة "لا توجد أحداث منشورة حاليًا"، في حين تنشر صفحة تقويم القبول في الموقع مواعيد دورة خريف 2026-2027؛ كما يحمل تذييل البوابة تاريخ 2022.</t>
         </is>
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>توصية تحسين</t>
+          <t>تصحيح مطلوب</t>
         </is>
       </c>
       <c r="J34" s="8" t="inlineStr">
         <is>
-          <t>منخفضة</t>
+          <t>متوسطة</t>
         </is>
       </c>
       <c r="K34" s="9" t="inlineStr">
         <is>
-          <t>إضافة واجهة عربية للبوابة ورابط لإشعار الخصوصية بعد مراجعته من الجهة المختصة بالامتثال.</t>
-        </is>
-      </c>
-      <c r="L34" s="9" t="inlineStr">
-        <is>
-          <t>غياب التقويم في البوابة معالج في الملاحظة السابقة.</t>
-        </is>
-      </c>
+          <t>اعتماد مصدر واحد لتقويم القبول تُعرض منه المواعيد في البوابة والموقع معًا، وتحديث سنة التذييل.</t>
+        </is>
+      </c>
+      <c r="L34" s="9" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
@@ -2413,22 +2413,22 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>القائمة الجانبية لصفحات القبول</t>
+          <t>بوابة التقديم</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>(menu shown on admission pages)</t>
+          <t>https://admissions.pmu.edu.sa/welcome</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>القائمة الجانبية لصفحات القبول – رابط "Contact Info" (يظهر في صفحات النظرة العامة والدرجات والبرامج وتقويم القبول وصفحات البكالوريوس)</t>
+          <t>بوابة التقديم – الصفحة الترحيبية</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>Contact Info → CONTACT INFO | Graduate Study Admission Coordinator | Office: G-017 Admin Bld | Email: graduateadm@pmu.edu.sa</t>
+          <t>Creative minds … Transform the world … Student Login … New Student? Register! … Contact Admissions</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
@@ -2438,30 +2438,34 @@
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>رابط مضلل</t>
+          <t>غياب العربية وإشعار الخصوصية</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>يقود رابط "Contact Info" في القائمة الجانبية، بما فيها صفحات القبول في البكالوريوس، إلى صفحة تواصل الدراسات العليا التي لا تذكر إلا منسق القبول في الدراسات العليا، فلا يجد المتقدم للبكالوريوس جهة تواصل خاصة به.</t>
+          <t>بوابة التقديم متاحة باللغة الإنجليزية وحدها، ولا تتضمن رابطًا لإشعار الخصوصية مع أنها نقطة تسجيل المتقدمين.</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>تصحيح مطلوب</t>
+          <t>توصية تحسين</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>متوسطة</t>
+          <t>منخفضة</t>
         </is>
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>توجيه الرابط إلى صفحة تواصل عامة لمكتب القبول (بريد إلكتروني وهاتف) أو إضافة بيانات تواصل البكالوريوس إلى الصفحة المستهدفة، أو إعادة تسمية الرابط إلى "Graduate Admissions Contact" في صفحات الدراسات العليا.</t>
-        </is>
-      </c>
-      <c r="L35" s="6" t="inlineStr"/>
+          <t>إضافة واجهة عربية للبوابة ورابط لإشعار الخصوصية بعد مراجعته من الجهة المختصة بالامتثال.</t>
+        </is>
+      </c>
+      <c r="L35" s="6" t="inlineStr">
+        <is>
+          <t>غياب التقويم في البوابة معالج في الملاحظة السابقة.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="n">
@@ -2469,37 +2473,37 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>القائمة الجانبية لصفحات القبول</t>
+          <t>بوابة التقديم</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>(menu shown on admission pages)</t>
+          <t>https://admissions.pmu.edu.sa/student/login/register</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>القائمة الجانبية لصفحات القبول – قسم Financial Aid (المنح الدراسية) وحاسبة المعدل</t>
+          <t>بوابة التقديم – نموذج التسجيل، قائمة الأنشطة (Activities)</t>
         </is>
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
-          <t>Sponsored Scholarship Programs ; MOHE Scholarships ; International Students Scholarships → "404 - File or directory not found"</t>
+          <t>Coop or Intership Programs</t>
         </is>
       </c>
       <c r="F36" s="9" t="inlineStr">
         <is>
-          <t>وظيفي وتقني</t>
+          <t>لغوي ونحوي</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>روابط معطلة</t>
+          <t>خطأ إملائي</t>
         </is>
       </c>
       <c r="H36" s="9" t="inlineStr">
         <is>
-          <t>أربعة روابط في القائمة الجانبية (صفحات المنح الثلاث وحاسبة المعدل) تعيد خطأ 404، وصفحة المساعدات المالية خالية من المحتوى.</t>
+          <t>يرد خيار «Coop or Intership Programs» في قائمة الأنشطة بنموذج التسجيل في بوابة التقديم، وفيه خطأ إملائي (Intership) وصيغة غير قياسية (Coop).</t>
         </is>
       </c>
       <c r="I36" s="8" t="inlineStr">
@@ -2509,17 +2513,17 @@
       </c>
       <c r="J36" s="8" t="inlineStr">
         <is>
-          <t>متوسطة</t>
+          <t>منخفضة</t>
         </is>
       </c>
       <c r="K36" s="9" t="inlineStr">
         <is>
-          <t>إصلاح الروابط أو إزالتها من القائمة، واستكمال صفحة المساعدات المالية أو حذفها بعد تأكيد الجهة المالكة.</t>
+          <t>تصحيح الخيار إلى «Co-op or Internship Programs».</t>
         </is>
       </c>
       <c r="L36" s="9" t="inlineStr">
         <is>
-          <t>هذه الصفحات من الصفحات القديمة غير المرتبطة مباشرة بالصفحة الرئيسية لمكتب القبول، لكنها تظهر في القائمة الجانبية لصفحات النظرة العامة والدرجات والبرامج وتقويم القبول.</t>
+          <t>تحقق من النص في ملف البرمجة المنشور للبوابة (main.2b01aae0109ae974.js).</t>
         </is>
       </c>
     </row>
@@ -2529,57 +2533,57 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>القائمة الجانبية لصفحات القبول</t>
+          <t>بوابة التقديم</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>https://www.pmu.edu.sa/Attachments/Admission/Images/PDF/Web-Admission-Guide-v2-2_20-12-18.pdf</t>
+          <t>https://admissions.pmu.edu.sa/student/login/register</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>رابط «Web Admission Guide» في القائمة الجانبية لصفحات مكتب القبول (ملف PDF)</t>
+          <t>بوابة التقديم – نموذج التسجيل، تسميات الحقول وقوائم الدول</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>PMU WEB ADMISSION GUIDE … Copyright © 2011 … For assistance please contact it@pmu.edu.sa … TOEFL Paper valid range is from 001 to 999 … TOEFL Computer valid range is from 040 to 300 … SAT valid range is from 50.00 to 99.99</t>
+          <t>الأسم الأول … أسم الأب … East Afrcia … Columbia</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>دقة المعلومات</t>
+          <t>لغوي ونحوي</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>دليل قديم</t>
+          <t>أخطاء إملائية محتملة</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>يفتح الرابط دليل تقديم إلكتروني مؤرخًا في ديسمبر 2018 ويحمل حقوق نشر 2011، يشرح الدخول باسم مستخدم ورقم سري (Login ID وPIN)، ويقتصر على نوعي طلب (مستجد ومحوّل)، ويتضمن جدول درجات يشمل اختبارات متوقفة (TOEFL Paper وTOEFL Computer) ونطاقًا لدرجة SAT لا يتوافق مع مقياسه (50.00–99.99)، ويحيل للمساعدة إلى بريد تقنية المعلومات، كما تتضمن صفحته الأخيرة أسماء وأرقامًا مباشرة لموظفين (2018). أما بوابة التقديم الحالية فتعتمد واجهة مختلفة («Student Login» و«New Student? Register!»).</t>
+          <t>رُصدت في حزمة المعالجة المرفقة أخطاء إملائية في تسميات حقول نموذج التسجيل (همزة القطع في «الأسم» و«أسم») وفي أسماء دول («East Afrcia» و«Columbia» بدل Colombia). لم يمكن التحقق منها في الملف المنشور للبوابة لأنها تُحمَّل ديناميكيًا من الخادم.</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>تصحيح مطلوب</t>
+          <t>متابعة وتحقق</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>متوسطة</t>
+          <t>منخفضة</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>سحب الدليل من القائمة أو استبداله بدليل محدَّث يشرح بوابة التقديم الحالية، مع إزالة بيانات التواصل الشخصية القديمة.</t>
+          <t>فتح نموذج التسجيل يدويًا والتحقق من التسميات، ثم تصحيحها إلى «الاسم الأول» و«اسم الأب» و«East Africa» و«Colombia» إن ثبت وجودها.</t>
         </is>
       </c>
       <c r="L37" s="6" t="inlineStr">
         <is>
-          <t>تاريخ ديسمبر 2018 مأخوذ من رابط الملف.</t>
+          <t>غير مُتحقَّق منه مباشرة؛ مصدره الحزمة المرفقة.</t>
         </is>
       </c>
     </row>
@@ -2599,42 +2603,42 @@
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>القائمة الجانبية لصفحات القبول – بندا "Admission Calendar" و"Home" تحت Undergraduate Admissions</t>
+          <t>القائمة الجانبية لصفحات القبول – رابط "Contact Info" (يظهر في صفحات النظرة العامة والدرجات والبرامج وتقويم القبول وصفحات البكالوريوس)</t>
         </is>
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
-          <t>Admission Calendar (sidebar) ; Admissions Calendar (page title) ; Undergraduate Admissions … Home … New Applicant … Freshman</t>
+          <t>Contact Info → CONTACT INFO | Graduate Study Admission Coordinator | Office: G-017 Admin Bld | Email: graduateadm@pmu.edu.sa</t>
         </is>
       </c>
       <c r="F38" s="9" t="inlineStr">
         <is>
-          <t>الاتساق</t>
+          <t>تجربة المستخدم</t>
         </is>
       </c>
       <c r="G38" s="9" t="inlineStr">
         <is>
-          <t>تسميات غير متسقة في القائمة</t>
+          <t>رابط مضلل</t>
         </is>
       </c>
       <c r="H38" s="9" t="inlineStr">
         <is>
-          <t>تُسمى صفحة التقويم "Admission Calendar" في القائمة الجانبية و"Admissions Calendar" في القائمة الرئيسية وعنوان الصفحة، ويحمل البند المؤدي إلى صفحة القبول في البكالوريوس اسم "Home" فيلتبس برابط الصفحة الرئيسية للموقع في مسار التصفح.</t>
+          <t>يقود رابط "Contact Info" في القائمة الجانبية، بما فيها صفحات القبول في البكالوريوس، إلى صفحة تواصل الدراسات العليا التي لا تذكر إلا منسق القبول في الدراسات العليا، فلا يجد المتقدم للبكالوريوس جهة تواصل خاصة به.</t>
         </is>
       </c>
       <c r="I38" s="8" t="inlineStr">
         <is>
-          <t>توصية تحسين</t>
+          <t>تصحيح مطلوب</t>
         </is>
       </c>
       <c r="J38" s="8" t="inlineStr">
         <is>
-          <t>منخفضة</t>
+          <t>متوسطة</t>
         </is>
       </c>
       <c r="K38" s="9" t="inlineStr">
         <is>
-          <t>اعتماد "Admissions Calendar" في جميع المواضع، وإعادة تسمية البند "Home" إلى "Undergraduate Admissions Overview".</t>
+          <t>توجيه الرابط إلى صفحة تواصل عامة لمكتب القبول (بريد إلكتروني وهاتف) أو إضافة بيانات تواصل البكالوريوس إلى الصفحة المستهدفة، أو إعادة تسمية الرابط إلى "Graduate Admissions Contact" في صفحات الدراسات العليا.</t>
         </is>
       </c>
       <c r="L38" s="9" t="inlineStr"/>
@@ -2655,12 +2659,12 @@
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>القائمة الجانبية لصفحات الدراسات العليا – رابط "Tuition &amp; Fees"</t>
+          <t>القائمة الجانبية لصفحات القبول – قسم Financial Aid (المنح الدراسية) وحاسبة المعدل</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>Tuition &amp; Fees</t>
+          <t>Sponsored Scholarship Programs ; MOHE Scholarships ; International Students Scholarships → "404 - File or directory not found"</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
@@ -2670,12 +2674,12 @@
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>رابط غير دقيق</t>
+          <t>روابط معطلة</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>يفتح رابط "Tuition &amp; Fees" في القائمة الجانبية لبرامج الدراسات العليا صفحة الرسوم الدراسية العامة، في حين يفتح الرابط نفسه في قائمة الدراسات العليا بصفحة مكتب القبول صفحة رسوم الدراسات العليا مباشرة.</t>
+          <t>أربعة روابط في القائمة الجانبية (صفحات المنح الثلاث وحاسبة المعدل) تعيد خطأ 404، وصفحة المساعدات المالية خالية من المحتوى.</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
@@ -2685,15 +2689,19 @@
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>منخفضة</t>
+          <t>متوسطة</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>توجيه الرابط في القائمة الجانبية للدراسات العليا إلى صفحة رسوم الدراسات العليا.</t>
-        </is>
-      </c>
-      <c r="L39" s="6" t="inlineStr"/>
+          <t>إصلاح الروابط أو إزالتها من القائمة، واستكمال صفحة المساعدات المالية أو حذفها بعد تأكيد الجهة المالكة.</t>
+        </is>
+      </c>
+      <c r="L39" s="6" t="inlineStr">
+        <is>
+          <t>هذه الصفحات من الصفحات القديمة غير المرتبطة مباشرة بالصفحة الرئيسية لمكتب القبول، لكنها تظهر في القائمة الجانبية لصفحات النظرة العامة والدرجات والبرامج وتقويم القبول.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="n">
@@ -2701,22 +2709,22 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>الطلاب الدوليون دون إقامة سعودية</t>
+          <t>القائمة الجانبية لصفحات القبول</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/international_students</t>
+          <t>https://www.pmu.edu.sa/Attachments/Admission/Images/PDF/Web-Admission-Guide-v2-2_20-12-18.pdf</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>قسما Transfer Students وVisitor Students – قائمة How to Apply (مقارنةً بصفحة القبول بالتحويل وصفحة الطلاب الزائرين وصفحة الرسوم الرسمية)</t>
+          <t>رابط «Web Admission Guide» في القائمة الجانبية لصفحات مكتب القبول (ملف PDF)</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
-          <t>[الطلاب الدوليون] Pay a non-refundable application fee of SAR 500 (excl. VAT) upon submission of documents | [التحويل, الطلاب الزائرون] Pay a non-refundable application fee of SAR 950 (incl. VAT) upon submission of documents | [Other Fees] Admission Application Fees- Undergraduate Programs … Non-refundable SAR 950</t>
+          <t>PMU WEB ADMISSION GUIDE … Copyright © 2011 … For assistance please contact it@pmu.edu.sa … TOEFL Paper valid range is from 001 to 999 … TOEFL Computer valid range is from 040 to 300 … SAT valid range is from 50.00 to 99.99 … Application Fee SR 500.00 (non refundable)</t>
         </is>
       </c>
       <c r="F40" s="9" t="inlineStr">
@@ -2726,12 +2734,12 @@
       </c>
       <c r="G40" s="9" t="inlineStr">
         <is>
-          <t>تعارض في رسوم التقديم</t>
+          <t>دليل قديم</t>
         </is>
       </c>
       <c r="H40" s="9" t="inlineStr">
         <is>
-          <t>تذكر صفحة الطلاب الدوليين أن رسوم التقديم للطلاب المحوَّلين والزائرين 500 ريال غير شاملة ضريبة القيمة المضافة، في حين تذكر صفحتا القبول بالتحويل والطلاب الزائرين وصفحة الرسوم الرسمية أن رسوم التقديم لمرحلة البكالوريوس 950 ريالًا شاملة ضريبة القيمة المضافة. كما تذكر الصفحة نفسها في قسم الطلاب المستجدين مبلغ 950 ريالًا شاملة ضريبة القيمة المضافة.</t>
+          <t>يفتح الرابط دليل تقديم إلكتروني مؤرخًا في ديسمبر 2018 ويحمل حقوق نشر 2011، يشرح الدخول باسم مستخدم ورقم سري (Login ID وPIN)، ويقتصر على نوعي طلب (مستجد ومحوّل)، ويتضمن جدول درجات يشمل اختبارات متوقفة (TOEFL Paper وTOEFL Computer) ونطاقًا لدرجة SAT لا يتوافق مع مقياسه (50.00–99.99)، ويعرض في صفحة الدفع (ص 20) رسم طلب «SR 500.00 (non refundable)» دون إشارة إلى ضريبة القيمة المضافة أو سنة السريان، بما يتعارض مع الرسوم المنشورة حاليًا لبعض الفئات (950 ريالًا للمحولين والزائرين الدوليين، و1,150 ريالًا لكلية الطب)، ويحيل للمساعدة إلى بريد تقنية المعلومات، كما تتضمن صفحته الأخيرة أسماء وأرقامًا مباشرة لموظفين (2018). أما بوابة التقديم الحالية فتعتمد واجهة مختلفة («Student Login» و«New Student? Register!»).</t>
         </is>
       </c>
       <c r="I40" s="8" t="inlineStr">
@@ -2741,17 +2749,17 @@
       </c>
       <c r="J40" s="8" t="inlineStr">
         <is>
-          <t>عالية</t>
+          <t>متوسطة</t>
         </is>
       </c>
       <c r="K40" s="9" t="inlineStr">
         <is>
-          <t>اعتماد مبلغ واحد لرسوم التقديم ومعالجة واحدة لضريبة القيمة المضافة لكل فئة من المتقدمين بقرار من الإدارة المالية ومكتب القبول، ثم توحيده في جميع الصفحات بما فيها صفحة الطلاب الدوليين.</t>
+          <t>سحب الدليل من القائمة أو استبداله بدليل محدَّث يشرح بوابة التقديم الحالية، مع إزالة بيانات التواصل الشخصية القديمة.</t>
         </is>
       </c>
       <c r="L40" s="9" t="inlineStr">
         <is>
-          <t>إن كانت هناك رسوم مختلفة معتمدة للطلاب الدوليين فيلزم توثيقها في صفحة الرسوم الرسمية.</t>
+          <t>تاريخ ديسمبر 2018 مأخوذ من رابط الملف.</t>
         </is>
       </c>
     </row>
@@ -2761,59 +2769,55 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>الطلاب الدوليون دون إقامة سعودية</t>
+          <t>القائمة الجانبية لصفحات القبول</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/international_students</t>
+          <t>(menu shown on admission pages)</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>قسم Freshman Students – معايير القبول والأوزان النسبية لتخصصات الحاسب والهندسة (مقارنةً بصفحة متطلبات تخصصات الحاسب والهندسة وصفحة اختبار SAT)</t>
+          <t>القائمة الجانبية لصفحات القبول – بندا "Admission Calendar" و"Home" تحت Undergraduate Admissions</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>[الطلاب الدوليون] Acceptable secondary school GPA *80% or equivalent … Computer Science &amp; Engineering Majors: Secondary School 40% SAT I 30% SAT II 30% | [الحاسب والهندسة] HS GPA out of 100 | ≥ 85 | 40% | [SAT] might submit SAT with minimum score of 1200 instead of Qudrat and Tahseely tests</t>
+          <t>Admission Calendar (sidebar) ; Admissions Calendar (page title) ; Undergraduate Admissions … Home … New Applicant … Freshman</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>دقة المعلومات</t>
+          <t>الاتساق</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>معيار قبول متقادم</t>
+          <t>تسميات غير متسقة في القائمة</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>تشترط صفحة الطلاب الدوليين لتخصصات الحاسب والهندسة اختبار SAT II بوزن 30%، وهو اختبار أوقفته الجهة المنظمة له (College Board) عام 2021، كما لا تذكر الحد الأدنى الأعلى لمعدل الثانوية (85%) ولا بديل SAT بدرجة 1200 المنشورَين في صفحتي متطلبات تخصصات الحاسب والهندسة واختبار SAT.</t>
+          <t>تُسمى صفحة التقويم "Admission Calendar" في القائمة الجانبية و"Admissions Calendar" في القائمة الرئيسية وعنوان الصفحة، ويحمل البند المؤدي إلى صفحة القبول في البكالوريوس اسم "Home" فيلتبس برابط الصفحة الرئيسية للموقع في مسار التصفح.</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>تصحيح مطلوب</t>
+          <t>توصية تحسين</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>عالية</t>
+          <t>منخفضة</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>حذف SAT II واستبداله بالبديل المعتمد (مثل SAT بدرجة 1200 بديلًا عن القدرات والتحصيلي)، وإضافة الحدود الدنيا الخاصة بهذه التخصصات أو الإحالة إلى صفحة متطلبات تخصصات الحاسب والهندسة، بعد اعتماد ذلك من مكتب القبول والكليات المعنية.</t>
-        </is>
-      </c>
-      <c r="L41" s="6" t="inlineStr">
-        <is>
-          <t>إيقاف اختبارات SAT Subject Tests معلومة خارجية معروفة وليست مأخوذة من صفحات الجامعة.</t>
-        </is>
-      </c>
+          <t>اعتماد "Admissions Calendar" في جميع المواضع، وإعادة تسمية البند "Home" إلى "Undergraduate Admissions Overview".</t>
+        </is>
+      </c>
+      <c r="L41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="8" t="n">
@@ -2821,37 +2825,37 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>الطلاب الدوليون دون إقامة سعودية</t>
+          <t>القائمة الجانبية لصفحات القبول</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/international_students</t>
+          <t>(menu shown on admission pages)</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>قسم Apply في صفحة الطلاب الدوليين (مقارنةً بتقويم القبول)</t>
+          <t>القائمة الجانبية لصفحات الدراسات العليا – رابط "Tuition &amp; Fees"</t>
         </is>
       </c>
       <c r="E42" s="10" t="inlineStr">
         <is>
-          <t>[الطلاب الدوليون] The application process can be completed entirely online. | [تقويم القبول] For non Saudi Students: Apply online through Study in Saudi platform: https://studyinsaudi.sa/ar … Closed</t>
+          <t>Tuition &amp; Fees</t>
         </is>
       </c>
       <c r="F42" s="9" t="inlineStr">
         <is>
-          <t>دقة المعلومات</t>
+          <t>وظيفي وتقني</t>
         </is>
       </c>
       <c r="G42" s="9" t="inlineStr">
         <is>
-          <t>مسار تقديم وموعد غير منشورين</t>
+          <t>رابط غير دقيق</t>
         </is>
       </c>
       <c r="H42" s="9" t="inlineStr">
         <is>
-          <t>يُظهر تقويم القبول مسار التقديم للمتقدمين من غير السعوديين عبر منصة «ادرس في السعودية» بحالة «Closed» دون أي تاريخ، ولا تذكر صفحة الطلاب الدوليين مسار التقديم ولا موعده النهائي، مكتفية بأن التقديم يتم إلكترونيًا بالكامل.</t>
+          <t>يفتح رابط "Tuition &amp; Fees" في القائمة الجانبية لبرامج الدراسات العليا صفحة الرسوم الدراسية العامة، في حين يفتح الرابط نفسه في قائمة الدراسات العليا بصفحة مكتب القبول صفحة رسوم الدراسات العليا مباشرة.</t>
         </is>
       </c>
       <c r="I42" s="8" t="inlineStr">
@@ -2861,12 +2865,12 @@
       </c>
       <c r="J42" s="8" t="inlineStr">
         <is>
-          <t>عالية</t>
+          <t>منخفضة</t>
         </is>
       </c>
       <c r="K42" s="9" t="inlineStr">
         <is>
-          <t>نشر مسار التقديم المعتمد للمتقدمين من غير السعوديين وموعد فتحه وإغلاقه للدورة القادمة في صفحة الطلاب الدوليين وتقويم القبول معًا.</t>
+          <t>توجيه الرابط في القائمة الجانبية للدراسات العليا إلى صفحة رسوم الدراسات العليا.</t>
         </is>
       </c>
       <c r="L42" s="9" t="inlineStr"/>
@@ -2887,12 +2891,12 @@
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>قسم Freshman Students – Admission Criteria؛ وقسم Transportation</t>
+          <t>قسما Transfer Students وVisitor Students – قائمة How to Apply (مقارنةً بصفحة القبول بالتحويل وصفحة الطلاب الزائرين وصفحة الرسوم الرسمية)</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>[الطلاب الدوليون] Acceptable SAT I … Transportation Transportation Campus Life | [SAT] might submit SAT with minimum score of 1200</t>
+          <t>[الطلاب الدوليون] Pay a non-refundable application fee of SAR 500 (excl. VAT) upon submission of documents | [التحويل, الطلاب الزائرون] Pay a non-refundable application fee of SAR 950 (incl. VAT) upon submission of documents | [Other Fees] Admission Application Fees- Undergraduate Programs … Non-refundable SAR 950</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
@@ -2902,12 +2906,12 @@
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>معلومة ناقصة</t>
+          <t>تعارض في رسوم التقديم</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>تشترط صفحة الطلاب الدوليين «SAT I مقبولًا» دون تحديد حد أدنى، بينما تحدد صفحة اختبار SAT حدًّا أدنى قدره 1200 لحملة الشهادات الثانوية الدولية. كما يظهر قسم Transportation بعنوانه فقط دون أي محتوى.</t>
+          <t>تذكر صفحة الطلاب الدوليين أن رسوم التقديم للطلاب المحوَّلين والزائرين 500 ريال غير شاملة ضريبة القيمة المضافة، في حين تذكر صفحتا القبول بالتحويل والطلاب الزائرين وصفحة الرسوم الرسمية أن رسوم التقديم لمرحلة البكالوريوس 950 ريالًا شاملة ضريبة القيمة المضافة. كما تذكر الصفحة نفسها في قسم الطلاب المستجدين مبلغ 950 ريالًا شاملة ضريبة القيمة المضافة.</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
@@ -2917,17 +2921,17 @@
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>متوسطة</t>
+          <t>عالية</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>ذكر الحد الأدنى المعتمد لدرجة SAT في الصفحة (1200 إذا أكده مكتب القبول)، واستكمال قسم المواصلات بمعلومات فعلية أو حذفه.</t>
+          <t>اعتماد مبلغ واحد لرسوم التقديم ومعالجة واحدة لضريبة القيمة المضافة لكل فئة من المتقدمين بقرار من الإدارة المالية ومكتب القبول، ثم توحيده في جميع الصفحات بما فيها صفحة الطلاب الدوليين.</t>
         </is>
       </c>
       <c r="L43" s="6" t="inlineStr">
         <is>
-          <t>رُفعت الأولوية إلى متوسطة لأن بعض الملاحظات المدمجة مصنفة بأولوية متوسطة.</t>
+          <t>إن كانت هناك رسوم مختلفة معتمدة للطلاب الدوليين فيلزم توثيقها في صفحة الرسوم الرسمية.</t>
         </is>
       </c>
     </row>
@@ -2947,12 +2951,12 @@
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>تبويب Graduate Studies في صفحة الطلاب الدوليين</t>
+          <t>قسم Freshman Students – معايير القبول والأوزان النسبية لتخصصات الحاسب والهندسة (مقارنةً بصفحة متطلبات تخصصات الحاسب والهندسة وصفحة اختبار SAT)</t>
         </is>
       </c>
       <c r="E44" s="10" t="inlineStr">
         <is>
-          <t>[الطلاب الدوليون] Graduate Studies MBA MSHD MSME</t>
+          <t>[الطلاب الدوليون] Acceptable secondary school GPA *80% or equivalent … Computer Science &amp; Engineering Majors: Secondary School 40% SAT I 30% SAT II 30% | [الحاسب والهندسة] HS GPA out of 100 | ≥ 85 | 40% | [SAT] might submit SAT with minimum score of 1200 instead of Qudrat and Tahseely tests</t>
         </is>
       </c>
       <c r="F44" s="9" t="inlineStr">
@@ -2962,12 +2966,12 @@
       </c>
       <c r="G44" s="9" t="inlineStr">
         <is>
-          <t>قائمة برامج ناقصة</t>
+          <t>معيار قبول متقادم</t>
         </is>
       </c>
       <c r="H44" s="9" t="inlineStr">
         <is>
-          <t>يعرض تبويب الدراسات العليا في صفحة الطلاب الدوليين ثلاثة برامج فقط (MBA وMSHD وMSME)، في حين تعرض صفحة مكتب القبول برامج أخرى للدراسات العليا لا تظهر في هذا التبويب (منها دكتوراه إدارة الأعمال، وEMBA، ودكتوراه الهندسة الميكانيكية، وMSEE، وMSCE، وMSID، وEMGMS، وMIBL).</t>
+          <t>تشترط صفحة الطلاب الدوليين لتخصصات الحاسب والهندسة اختبار SAT II بوزن 30%، وهو اختبار أوقفته الجهة المنظمة له (College Board) عام 2021، كما لا تذكر الحد الأدنى الأعلى لمعدل الثانوية (85%) ولا بديل SAT بدرجة 1200 المنشورَين في صفحتي متطلبات تخصصات الحاسب والهندسة واختبار SAT.</t>
         </is>
       </c>
       <c r="I44" s="8" t="inlineStr">
@@ -2977,15 +2981,19 @@
       </c>
       <c r="J44" s="8" t="inlineStr">
         <is>
-          <t>متوسطة</t>
+          <t>عالية</t>
         </is>
       </c>
       <c r="K44" s="9" t="inlineStr">
         <is>
-          <t>إضافة البرامج الناقصة أو الإحالة إلى صفحة برامج الدراسات العليا الكاملة، بعد تأكيد البرامج المتاحة للطلاب الدوليين من عمادة الدراسات العليا.</t>
-        </is>
-      </c>
-      <c r="L44" s="9" t="inlineStr"/>
+          <t>حذف SAT II واستبداله بالبديل المعتمد (مثل SAT بدرجة 1200 بديلًا عن القدرات والتحصيلي)، وإضافة الحدود الدنيا الخاصة بهذه التخصصات أو الإحالة إلى صفحة متطلبات تخصصات الحاسب والهندسة، بعد اعتماد ذلك من مكتب القبول والكليات المعنية.</t>
+        </is>
+      </c>
+      <c r="L44" s="9" t="inlineStr">
+        <is>
+          <t>إيقاف اختبارات SAT Subject Tests معلومة خارجية معروفة وليست مأخوذة من صفحات الجامعة.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n">
@@ -3003,42 +3011,42 @@
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>صفحة الطلاب الدوليين – قسم International Admissions Office (بيانات التواصل)</t>
+          <t>قسم Apply في صفحة الطلاب الدوليين (مقارنةً بتقويم القبول)</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>[الطلاب الدوليون] PMU’s International Admissions Office staff will be there for you.</t>
+          <t>[الطلاب الدوليون] The application process can be completed entirely online. | [تقويم القبول] For non Saudi Students: Apply online through Study in Saudi platform: https://studyinsaudi.sa/ar … Closed</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>تجربة المستخدم</t>
+          <t>دقة المعلومات</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>بيانات تواصل غير متوفرة</t>
+          <t>مسار تقديم وموعد غير منشورين</t>
         </is>
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>لا تتضمن صفحة الطلاب الدوليين بريدًا إلكترونيًا أو رقم هاتف أو موقعًا لمكتب القبول الدولي، ويقتصر التواصل على رابط عام لصفحة «اتصل بنا» في الجامعة.</t>
+          <t>يُظهر تقويم القبول مسار التقديم للمتقدمين من غير السعوديين عبر منصة «ادرس في السعودية» بحالة «Closed» دون أي تاريخ، ولا تذكر صفحة الطلاب الدوليين مسار التقديم ولا موعده النهائي، مكتفية بأن التقديم يتم إلكترونيًا بالكامل.</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>توصية تحسين</t>
+          <t>تصحيح مطلوب</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>متوسطة</t>
+          <t>عالية</t>
         </is>
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>إضافة البريد الإلكتروني ورقم الهاتف وموقع مكتب القبول الدولي، أو رابط مباشر لصفحة التواصل الخاصة به.</t>
+          <t>نشر مسار التقديم المعتمد للمتقدمين من غير السعوديين وموعد فتحه وإغلاقه للدورة القادمة في صفحة الطلاب الدوليين وتقويم القبول معًا.</t>
         </is>
       </c>
       <c r="L45" s="6" t="inlineStr"/>
@@ -3059,27 +3067,27 @@
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>صفحة الطلاب الدوليين – الفقرة التعريفية، ومسار التنقل، وقوائم المستندات، وقائمة International Students Services Office</t>
+          <t>قسم Freshman Students – Admission Criteria؛ وقسم Transportation</t>
         </is>
       </c>
       <c r="E46" s="10" t="inlineStr">
         <is>
-          <t>[الطلاب الدوليون] From choosing a program to applying to accept Admission Offer to issuing student visa to housing to start the study … International Students without Saudi residence … Copy of SAT 1 - if available … Issuing IQAMA … All registration’s functions</t>
+          <t>[الطلاب الدوليون] Acceptable SAT I … Transportation Transportation Campus Life | [SAT] might submit SAT with minimum score of 1200</t>
         </is>
       </c>
       <c r="F46" s="9" t="inlineStr">
         <is>
-          <t>لغوي ونحوي</t>
+          <t>دقة المعلومات</t>
         </is>
       </c>
       <c r="G46" s="9" t="inlineStr">
         <is>
-          <t>أخطاء لغوية وتحريرية</t>
+          <t>معلومة ناقصة</t>
         </is>
       </c>
       <c r="H46" s="9" t="inlineStr">
         <is>
-          <t>تتضمن الصفحة جملة تعريفية مضطربة التركيب، واختلافًا في كتابة الأحرف الكبيرة بين مسار التنقل («Saudi residence») وعنوان الصفحة («Saudi Residence»)، وتسمية الاختبار نفسه «SAT I» و«SAT 1»، وكتابة «IQAMA» بأحرف كبيرة، واستخدامًا خاطئًا لعلامة الملكية في «registration’s».</t>
+          <t>تشترط صفحة الطلاب الدوليين «SAT I مقبولًا» دون تحديد حد أدنى، بينما تحدد صفحة اختبار SAT حدًّا أدنى قدره 1200 لحملة الشهادات الثانوية الدولية. كما يظهر قسم Transportation بعنوانه فقط دون أي محتوى.</t>
         </is>
       </c>
       <c r="I46" s="8" t="inlineStr">
@@ -3089,15 +3097,19 @@
       </c>
       <c r="J46" s="8" t="inlineStr">
         <is>
-          <t>منخفضة</t>
+          <t>متوسطة</t>
         </is>
       </c>
       <c r="K46" s="9" t="inlineStr">
         <is>
-          <t>إعادة صياغة الجملة التعريفية في صورة قائمة واضحة (اختيار البرنامج، التقديم، قبول العرض، التأشيرة، السكن، بدء الدراسة)، وتوحيد «Saudi Residence» و«SAT»، وتصحيح العبارتين إلى «Issuing Iqama» و«All registration functions».</t>
-        </is>
-      </c>
-      <c r="L46" s="9" t="inlineStr"/>
+          <t>ذكر الحد الأدنى المعتمد لدرجة SAT في الصفحة (1200 إذا أكده مكتب القبول)، واستكمال قسم المواصلات بمعلومات فعلية أو حذفه.</t>
+        </is>
+      </c>
+      <c r="L46" s="9" t="inlineStr">
+        <is>
+          <t>رُفعت الأولوية إلى متوسطة لأن بعض الملاحظات المدمجة مصنفة بأولوية متوسطة.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n">
@@ -3115,42 +3127,42 @@
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>صفحة الطلاب الدوليين – قسم Why PMU (تسميات الروابط)</t>
+          <t>تبويب Graduate Studies في صفحة الطلاب الدوليين</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>[الطلاب الدوليون] Curriculum (TIEC) … Life @ pmu</t>
+          <t>[الطلاب الدوليون] Graduate Studies MBA MSHD MSME</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>تجربة المستخدم</t>
+          <t>دقة المعلومات</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>تسمية روابط غير واضحة</t>
+          <t>قائمة برامج ناقصة</t>
         </is>
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>يتضمن قسم Why PMU رابطًا بعنوان «Curriculum (TIEC)» باختصار غير مُعرَّف، ورابطًا بعنوان «Life @ pmu» يُكتب فيه اختصار الجامعة بأحرف صغيرة.</t>
+          <t>يعرض تبويب الدراسات العليا في صفحة الطلاب الدوليين ثلاثة برامج فقط (MBA وMSHD وMSME)، في حين تعرض صفحة مكتب القبول برامج أخرى للدراسات العليا لا تظهر في هذا التبويب (منها دكتوراه إدارة الأعمال، وEMBA، ودكتوراه الهندسة الميكانيكية، وMSEE، وMSCE، وMSID، وEMGMS، وMIBL).</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>توصية تحسين</t>
+          <t>تصحيح مطلوب</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>منخفضة</t>
+          <t>متوسطة</t>
         </is>
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>كتابة الاختصار كاملًا أو إعادة تسمية الرابط بما يصف وجهته، وتصحيح التسمية الثانية إلى «Life @ PMU» مع حذفها إن كانت تكرر رابطًا آخر في القسم.</t>
+          <t>إضافة البرامج الناقصة أو الإحالة إلى صفحة برامج الدراسات العليا الكاملة، بعد تأكيد البرامج المتاحة للطلاب الدوليين من عمادة الدراسات العليا.</t>
         </is>
       </c>
       <c r="L47" s="6" t="inlineStr"/>
@@ -3171,27 +3183,27 @@
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>صفحة الطلاب الدوليين – قسم Housing</t>
+          <t>صفحة الطلاب الدوليين – قسم International Admissions Office (بيانات التواصل)</t>
         </is>
       </c>
       <c r="E48" s="10" t="inlineStr">
         <is>
-          <t>[الطلاب الدوليون] various academic support elements will be located in the residence halls for the convenience of students.</t>
+          <t>[الطلاب الدوليون] PMU’s International Admissions Office staff will be there for you.</t>
         </is>
       </c>
       <c r="F48" s="9" t="inlineStr">
         <is>
-          <t>دقة المعلومات</t>
+          <t>تجربة المستخدم</t>
         </is>
       </c>
       <c r="G48" s="9" t="inlineStr">
         <is>
-          <t>نص قديم بصيغة المستقبل</t>
+          <t>بيانات تواصل غير متوفرة</t>
         </is>
       </c>
       <c r="H48" s="9" t="inlineStr">
         <is>
-          <t>يصف قسم السكن عناصر الدعم الأكاديمي في السكن الطلابي بصيغة المستقبل («will be located»)، مما يوحي بأنه نص من مرحلة التأسيس ولم يُحدَّث.</t>
+          <t>لا تتضمن صفحة الطلاب الدوليين بريدًا إلكترونيًا أو رقم هاتف أو موقعًا لمكتب القبول الدولي، ويقتصر التواصل على رابط عام لصفحة «اتصل بنا» في الجامعة.</t>
         </is>
       </c>
       <c r="I48" s="8" t="inlineStr">
@@ -3201,12 +3213,12 @@
       </c>
       <c r="J48" s="8" t="inlineStr">
         <is>
-          <t>منخفضة</t>
+          <t>متوسطة</t>
         </is>
       </c>
       <c r="K48" s="9" t="inlineStr">
         <is>
-          <t>تحديث النص بصيغة الحاضر وبمعلومات السكن الحالية بالتنسيق مع الجهة المسؤولة عن السكن الطلابي.</t>
+          <t>إضافة البريد الإلكتروني ورقم الهاتف وموقع مكتب القبول الدولي، أو رابط مباشر لصفحة التواصل الخاصة به.</t>
         </is>
       </c>
       <c r="L48" s="9" t="inlineStr"/>
@@ -3217,37 +3229,37 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>القبول في البكالوريوس</t>
+          <t>الطلاب الدوليون دون إقامة سعودية</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/undergraduate_programs_admission</t>
+          <t>https://pmu.edu.sa/admission/international_students</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>صفحة القبول في البكالوريوس – قسم Undergraduate Program</t>
+          <t>صفحة الطلاب الدوليين – الفقرة التعريفية، ومسار التنقل، وقوائم المستندات، وقائمة International Students Services Office</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>[القبول في البكالوريوس] PMU offers various degrees under the College of Architecture and Design, College of Computer Engineering and Science, College of Business Administration, College of Law and College of Engineering.</t>
+          <t>[الطلاب الدوليون] From choosing a program to applying to accept Admission Offer to issuing student visa to housing to start the study … International Students without Saudi residence … Copy of SAT 1 - if available … Issuing IQAMA … All registration’s functions</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>دقة المعلومات</t>
+          <t>لغوي ونحوي</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>قائمة كليات ناقصة</t>
+          <t>أخطاء لغوية وتحريرية</t>
         </is>
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>يعدد قسم Undergraduate Program خمس كليات ولا يذكر كلية الطب، مع أن الصفحة نفسها تتضمن قسمًا للقبول في كلية الطب.</t>
+          <t>تتضمن الصفحة جملة تعريفية مضطربة التركيب، واختلافًا في كتابة الأحرف الكبيرة بين مسار التنقل («Saudi residence») وعنوان الصفحة («Saudi Residence»)، وتسمية الاختبار نفسه «SAT I» و«SAT 1»، وكتابة «IQAMA» بأحرف كبيرة، واستخدامًا خاطئًا لعلامة الملكية في «registration’s».</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
@@ -3257,19 +3269,15 @@
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>متوسطة</t>
+          <t>منخفضة</t>
         </is>
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>إضافة كلية الطب إلى القائمة، وإضافة كلية العلوم والدراسات الإنسانية إن كانت تقدم برامج بكالوريوس.</t>
-        </is>
-      </c>
-      <c r="L49" s="6" t="inlineStr">
-        <is>
-          <t>طرح البكالوريوس في كلية العلوم والدراسات الإنسانية يحتاج إلى تأكيد.</t>
-        </is>
-      </c>
+          <t>إعادة صياغة الجملة التعريفية في صورة قائمة واضحة (اختيار البرنامج، التقديم، قبول العرض، التأشيرة، السكن، بدء الدراسة)، وتوحيد «Saudi Residence» و«SAT»، وتصحيح العبارتين إلى «Issuing Iqama» و«All registration functions».</t>
+        </is>
+      </c>
+      <c r="L49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="8" t="n">
@@ -3277,42 +3285,42 @@
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>القبول في البكالوريوس</t>
+          <t>الطلاب الدوليون دون إقامة سعودية</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/undergraduate_programs_admission</t>
+          <t>https://pmu.edu.sa/admission/international_students</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>صفحة القبول في البكالوريوس – قسم New Applicant</t>
+          <t>صفحة الطلاب الدوليين – قسم Why PMU (تسميات الروابط)</t>
         </is>
       </c>
       <c r="E50" s="10" t="inlineStr">
         <is>
-          <t>[القبول في البكالوريوس] Admission to each of the undergraduate program is based on different criteria.</t>
+          <t>[الطلاب الدوليون] Curriculum (TIEC) … Life @ pmu</t>
         </is>
       </c>
       <c r="F50" s="9" t="inlineStr">
         <is>
-          <t>لغوي ونحوي</t>
+          <t>تجربة المستخدم</t>
         </is>
       </c>
       <c r="G50" s="9" t="inlineStr">
         <is>
-          <t>خطأ نحوي</t>
+          <t>تسمية روابط غير واضحة</t>
         </is>
       </c>
       <c r="H50" s="9" t="inlineStr">
         <is>
-          <t>ترد عبارة «each of the undergraduate program» بصيغة المفرد، والصواب «each of the undergraduate programs».</t>
+          <t>يتضمن قسم Why PMU رابطًا بعنوان «Curriculum (TIEC)» باختصار غير مُعرَّف، ورابطًا بعنوان «Life @ pmu» يُكتب فيه اختصار الجامعة بأحرف صغيرة.</t>
         </is>
       </c>
       <c r="I50" s="8" t="inlineStr">
         <is>
-          <t>تصحيح مطلوب</t>
+          <t>توصية تحسين</t>
         </is>
       </c>
       <c r="J50" s="8" t="inlineStr">
@@ -3322,7 +3330,7 @@
       </c>
       <c r="K50" s="9" t="inlineStr">
         <is>
-          <t>تصحيح العبارة إلى «Admission to each of the undergraduate programs is based on different criteria».</t>
+          <t>كتابة الاختصار كاملًا أو إعادة تسمية الرابط بما يصف وجهته، وتصحيح التسمية الثانية إلى «Life @ PMU» مع حذفها إن كانت تكرر رابطًا آخر في القسم.</t>
         </is>
       </c>
       <c r="L50" s="9" t="inlineStr"/>
@@ -3333,42 +3341,42 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>القبول في البكالوريوس</t>
+          <t>الطلاب الدوليون دون إقامة سعودية</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/undergraduate_programs_admission</t>
+          <t>https://pmu.edu.sa/admission/international_students</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>صفحة القبول في البكالوريوس – قسم New Applicant (مقارنةً بصفحة التقديم وصفحة الطلاب الدوليين)</t>
+          <t>صفحة الطلاب الدوليين – قسم Housing</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>[القبول في البكالوريوس] attested, in advance, by the Saudi Consulate and other authorized organizations | [/apply] Have the certificate stamped by the Saudi Embassy in their country | [الطلاب الدوليون] certified by the Saudi Cultural Mission and Saudi Embassy</t>
+          <t>[الطلاب الدوليون] various academic support elements will be located in the residence halls for the convenience of students.</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>الاتساق</t>
+          <t>دقة المعلومات</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>تعارض في جهة التصديق</t>
+          <t>نص قديم بصيغة المستقبل</t>
         </is>
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>تشترط صفحة القبول في البكالوريوس تصديق الشهادات من «القنصلية السعودية»، بينما تذكر صفحة التقديم «السفارة السعودية»، وتذكر صفحة الطلاب الدوليين «الملحقية الثقافية السعودية والسفارة السعودية».</t>
+          <t>يصف قسم السكن عناصر الدعم الأكاديمي في السكن الطلابي بصيغة المستقبل («will be located»)، مما يوحي بأنه نص من مرحلة التأسيس ولم يُحدَّث.</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>تصحيح مطلوب</t>
+          <t>توصية تحسين</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
@@ -3378,7 +3386,7 @@
       </c>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>اعتماد صيغة واحدة لجهة التصديق المطلوبة (مثل «Saudi Embassy or Consulate» إن كانت معتمدة) بقرار من مكتب القبول، وتوحيدها في جميع الصفحات.</t>
+          <t>تحديث النص بصيغة الحاضر وبمعلومات السكن الحالية بالتنسيق مع الجهة المسؤولة عن السكن الطلابي.</t>
         </is>
       </c>
       <c r="L51" s="6" t="inlineStr"/>
@@ -3399,27 +3407,27 @@
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>عناوين الصفحة (مستويات H) في صفحة القبول في البكالوريوس وصفحة الطلاب الدوليين وصفحة تقويم القبول</t>
+          <t>صفحة القبول في البكالوريوس – قسم Undergraduate Program</t>
         </is>
       </c>
       <c r="E52" s="10" t="inlineStr">
         <is>
-          <t>[القبول في البكالوريوس] UNDERGRADUATE ADMISSIONS … New Applicant: … Computer Science and Engineering Majors Admission Requirements | [الطلاب الدوليون] International Admissions Office … Apply | [تقويم القبول] ADMISSIONS CALENDARS</t>
+          <t>[القبول في البكالوريوس] PMU offers various degrees under the College of Architecture and Design, College of Computer Engineering and Science, College of Business Administration, College of Law and College of Engineering.</t>
         </is>
       </c>
       <c r="F52" s="9" t="inlineStr">
         <is>
-          <t>وظيفي وتقني</t>
+          <t>دقة المعلومات</t>
         </is>
       </c>
       <c r="G52" s="9" t="inlineStr">
         <is>
-          <t>ترتيب عناوين غير سليم</t>
+          <t>قائمة كليات ناقصة</t>
         </is>
       </c>
       <c r="H52" s="9" t="inlineStr">
         <is>
-          <t>لا تتبع مستويات العناوين تسلسلًا سليمًا: في صفحة البكالوريوس ينتقل العنوان من H1 إلى H3 ثم H4 ثم يعود إلى H3، وفي صفحة الطلاب الدوليين لا يوجد H1 وتنتقل العناوين من H2 إلى H4، وفي صفحة التقويم يسبق H2 عنوان H1.</t>
+          <t>يعدد قسم Undergraduate Program خمس كليات ولا يذكر كلية الطب، مع أن الصفحة نفسها تتضمن قسمًا للقبول في كلية الطب.</t>
         </is>
       </c>
       <c r="I52" s="8" t="inlineStr">
@@ -3429,15 +3437,19 @@
       </c>
       <c r="J52" s="8" t="inlineStr">
         <is>
-          <t>منخفضة</t>
+          <t>متوسطة</t>
         </is>
       </c>
       <c r="K52" s="9" t="inlineStr">
         <is>
-          <t>تصحيح تسلسل العناوين في القوالب (H1 واحد ثم H2 فـH3) بما يدعم سهولة الوصول ومحركات البحث.</t>
-        </is>
-      </c>
-      <c r="L52" s="9" t="inlineStr"/>
+          <t>إضافة كلية الطب إلى القائمة، وإضافة كلية العلوم والدراسات الإنسانية إن كانت تقدم برامج بكالوريوس.</t>
+        </is>
+      </c>
+      <c r="L52" s="9" t="inlineStr">
+        <is>
+          <t>طرح البكالوريوس في كلية العلوم والدراسات الإنسانية يحتاج إلى تأكيد.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="n">
@@ -3445,37 +3457,37 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>القبول في كلية الطب</t>
+          <t>القبول في البكالوريوس</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/college_of_medicine_admission</t>
+          <t>https://pmu.edu.sa/admission/undergraduate_programs_admission</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>صفحة القبول في كلية الطب – How to Apply (مقارنةً بصفحة رسوم البرنامج الطبي وبقية صفحات البكالوريوس وصفحة التقديم)</t>
+          <t>صفحة القبول في البكالوريوس – قسم New Applicant</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>[كلية الطب] Pay a non-refundable application fee of SAR 1000 (incl. VAT) upon submission of documents | [Medical fees] SAR 1,150 (VAT inclusive) | [القبول في البكالوريوس, البرنامج التحضيري–الحاسب والهندسة] SAR 950 (incl. VAT)</t>
+          <t>[القبول في البكالوريوس] Admission to each of the undergraduate program is based on different criteria.</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>دقة المعلومات</t>
+          <t>لغوي ونحوي</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>تعارض في رسوم التقديم</t>
+          <t>خطأ نحوي</t>
         </is>
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>تذكر صفحة كلية الطب أن رسوم التقديم 1000 ريال شاملة ضريبة القيمة المضافة، بينما تذكر صفحة رسوم البرنامج الطبي 1,150 ريالًا شاملة ضريبة القيمة المضافة (وهو ما يساوي 1000 ريال مضافًا إليها 15%)، ولا توضح صفحات البكالوريوس الأخرى وصفحة التقديم، التي تذكر 950 ريالًا، أن لكلية الطب رسومًا مختلفة.</t>
+          <t>ترد عبارة «each of the undergraduate program» بصيغة المفرد، والصواب «each of the undergraduate programs».</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
@@ -3485,12 +3497,12 @@
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>عالية</t>
+          <t>منخفضة</t>
         </is>
       </c>
       <c r="K53" s="6" t="inlineStr">
         <is>
-          <t>تأكيد المبلغ المعتمد ومعالجة الضريبة من الإدارة المالية وكلية الطب، وتوحيده في الصفحتين، والإشارة في صفحات البكالوريوس وصفحة التقديم إلى أن الرسوم المختلفة خاصة بمتقدمي كلية الطب.</t>
+          <t>تصحيح العبارة إلى «Admission to each of the undergraduate programs is based on different criteria».</t>
         </is>
       </c>
       <c r="L53" s="6" t="inlineStr"/>
@@ -3501,22 +3513,22 @@
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>القبول في كلية الطب</t>
+          <t>القبول في البكالوريوس</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/college_of_medicine_admission</t>
+          <t>https://pmu.edu.sa/admission/undergraduate_programs_admission</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>صفحة القبول في كلية الطب – رابط التقديم (مقارنةً بتقويم القبول وبقية صفحات البكالوريوس)</t>
+          <t>صفحة القبول في البكالوريوس – قسم New Applicant (مقارنةً بصفحة التقديم وصفحة الطلاب الدوليين)</t>
         </is>
       </c>
       <c r="E54" s="10" t="inlineStr">
         <is>
-          <t>[تقويم القبول] For Saudi Students: Apply online through Qabool platform: https://www.uap.sa/ | [القبول في البكالوريوس] Apply online based on the admissions calendar (Apply Now)</t>
+          <t>[القبول في البكالوريوس] attested, in advance, by the Saudi Consulate and other authorized organizations | [/apply] Have the certificate stamped by the Saudi Embassy in their country | [الطلاب الدوليون] certified by the Saudi Cultural Mission and Saudi Embassy</t>
         </is>
       </c>
       <c r="F54" s="9" t="inlineStr">
@@ -3526,34 +3538,30 @@
       </c>
       <c r="G54" s="9" t="inlineStr">
         <is>
-          <t>قناة تقديم غير موحدة</t>
+          <t>تعارض في جهة التصديق</t>
         </is>
       </c>
       <c r="H54" s="9" t="inlineStr">
         <is>
-          <t>تحيل صفحة كلية الطب إلى منصة «قبول» الوطنية (uap.sa) بما يتفق مع تقويم القبول، بينما تحيل بقية صفحات البكالوريوس إلى رابط «Apply Now» الخاص بالجامعة، فلا تتضح القناة المعتمدة لكل فئة من المتقدمين.</t>
+          <t>تشترط صفحة القبول في البكالوريوس تصديق الشهادات من «القنصلية السعودية»، بينما تذكر صفحة التقديم «السفارة السعودية»، وتذكر صفحة الطلاب الدوليين «الملحقية الثقافية السعودية والسفارة السعودية».</t>
         </is>
       </c>
       <c r="I54" s="8" t="inlineStr">
         <is>
-          <t>متابعة وتحقق</t>
+          <t>تصحيح مطلوب</t>
         </is>
       </c>
       <c r="J54" s="8" t="inlineStr">
         <is>
-          <t>متوسطة</t>
+          <t>منخفضة</t>
         </is>
       </c>
       <c r="K54" s="9" t="inlineStr">
         <is>
-          <t>تحديد قناة التقديم المعتمدة لكل فئة (السعوديون، وغير السعوديين) بقرار من مكتب القبول، وذكرها بصيغة موحدة في جميع صفحات البكالوريوس.</t>
-        </is>
-      </c>
-      <c r="L54" s="9" t="inlineStr">
-        <is>
-          <t>وجود رابط uap.sa في صفحة كلية الطب ثابت في سجل الروابط، ولم يُلتقط نص الرابط نفسه في النص المستخرج.</t>
-        </is>
-      </c>
+          <t>اعتماد صيغة واحدة لجهة التصديق المطلوبة (مثل «Saudi Embassy or Consulate» إن كانت معتمدة) بقرار من مكتب القبول، وتوحيدها في جميع الصفحات.</t>
+        </is>
+      </c>
+      <c r="L54" s="9" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n">
@@ -3561,37 +3569,37 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>القبول في كلية الطب</t>
+          <t>القبول في البكالوريوس</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/college_of_medicine_admission</t>
+          <t>https://pmu.edu.sa/admission/undergraduate_programs_admission</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>صفحة القبول في كلية الطب – Admission Criteria وHow to Apply (الحدود الدنيا ومعادلة النسبة الموزونة)</t>
+          <t>عناوين الصفحة (مستويات H) في صفحة القبول في البكالوريوس وصفحة الطلاب الدوليين وصفحة تقويم القبول</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>[كلية الطب] Copy of secondary school certificate or equivalent (95%) … (Qudrat) (80) or equivalent (SAT 1) … (SAAT – Tahseely) (80) or equivalent (SAT 1) 1300 … *20% high school + 40% Qudrat + 40% Tahseely were 86 is the minimum acceptable score</t>
+          <t>[القبول في البكالوريوس] UNDERGRADUATE ADMISSIONS … New Applicant: … Computer Science and Engineering Majors Admission Requirements | [الطلاب الدوليون] International Admissions Office … Apply | [تقويم القبول] ADMISSIONS CALENDARS</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>دقة المعلومات</t>
+          <t>وظيفي وتقني</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>تعارض في معايير القبول</t>
+          <t>ترتيب عناوين غير سليم</t>
         </is>
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>الحدود الدنيا المنشورة (الثانوية 95% والقدرات 80 والتحصيلي 80) تعطي وفق المعادلة المنشورة نسبة موزونة قدرها 83 فقط، وهي أقل من الحد الأدنى المذكور (86). كما لا يتضح أي درجة يُشترط أن تبلغ 86، ولا ما إذا كانت درجة SAT 1 واحدة (1300) تُغني عن القدرات والتحصيلي معًا، إذ لا يُذكر حد أدنى لـSAT 1 بديلًا عن القدرات.</t>
+          <t>لا تتبع مستويات العناوين تسلسلًا سليمًا: في صفحة البكالوريوس ينتقل العنوان من H1 إلى H3 ثم H4 ثم يعود إلى H3، وفي صفحة الطلاب الدوليين لا يوجد H1 وتنتقل العناوين من H2 إلى H4، وفي صفحة التقويم يسبق H2 عنوان H1.</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
@@ -3601,12 +3609,12 @@
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>متوسطة</t>
+          <t>منخفضة</t>
         </is>
       </c>
       <c r="K55" s="6" t="inlineStr">
         <is>
-          <t>تحديد الحدود الدنيا والمعادلة المعتمدة من كلية الطب ومكتب القبول، وإعادة صياغة الملاحظة إلى «where 86 is the minimum acceptable total weighted score»، وتوضيح شروط استخدام SAT 1 بديلًا.</t>
+          <t>تصحيح تسلسل العناوين في القوالب (H1 واحد ثم H2 فـH3) بما يدعم سهولة الوصول ومحركات البحث.</t>
         </is>
       </c>
       <c r="L55" s="6" t="inlineStr"/>
@@ -3627,12 +3635,12 @@
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>صفحة القبول في كلية الطب – Admission Criteria وقائمة How to Apply</t>
+          <t>صفحة القبول في كلية الطب – How to Apply (مقارنةً بصفحة رسوم البرنامج الطبي وبقية صفحات البكالوريوس وصفحة التقديم)</t>
         </is>
       </c>
       <c r="E56" s="10" t="inlineStr">
         <is>
-          <t>[كلية الطب] the process typically involves understanding the weighting and criteria that the medical college uses to evaluate applicants. Here’s how each factor can contribute to the overall acceptance percentage:</t>
+          <t>[كلية الطب] Pay a non-refundable application fee of SAR 1000 (incl. VAT) upon submission of documents | [Medical fees] SAR 1,150 (VAT inclusive) | [القبول في البكالوريوس, البرنامج التحضيري–الحاسب والهندسة] SAR 950 (incl. VAT)</t>
         </is>
       </c>
       <c r="F56" s="9" t="inlineStr">
@@ -3642,12 +3650,12 @@
       </c>
       <c r="G56" s="9" t="inlineStr">
         <is>
-          <t>صياغة غير رسمية ومتطلبات ناقصة</t>
+          <t>تعارض في رسوم التقديم</t>
         </is>
       </c>
       <c r="H56" s="9" t="inlineStr">
         <is>
-          <t>تصف فقرة معايير القبول الإجراء بلغة عامة وغير رسمية بدل النص على قاعدة المفاضلة صراحة. ولا تذكر قائمة التقديم أي متطلب للغة الإنجليزية أو للّياقة الطبية، وتخلو من مستندات تطلبها صفحات البكالوريوس الأخرى (الصور الشخصية، وسجل الأسرة، وخطاب عدم الممانعة من جهة العمل).</t>
+          <t>تذكر صفحة كلية الطب أن رسوم التقديم 1000 ريال شاملة ضريبة القيمة المضافة، بينما تذكر صفحة رسوم البرنامج الطبي 1,150 ريالًا شاملة ضريبة القيمة المضافة (وهو ما يساوي 1000 ريال مضافًا إليها 15%)، ولا توضح صفحات البكالوريوس الأخرى وصفحة التقديم، التي تذكر 950 ريالًا، أن لكلية الطب رسومًا مختلفة.</t>
         </is>
       </c>
       <c r="I56" s="8" t="inlineStr">
@@ -3657,19 +3665,15 @@
       </c>
       <c r="J56" s="8" t="inlineStr">
         <is>
-          <t>متوسطة</t>
+          <t>عالية</t>
         </is>
       </c>
       <c r="K56" s="9" t="inlineStr">
         <is>
-          <t>استبدال الفقرة بنص رسمي معتمد مثل: «يُرتَّب المتقدمون وفق النسبة الموزونة (60%) والمقابلة الشخصية (40%)»، وإضافة متطلب اللغة الإنجليزية وأي متطلبات أخرى معتمدة، ومواءمة قائمة المستندات أو النص على اختلافها، بقرار من كلية الطب.</t>
-        </is>
-      </c>
-      <c r="L56" s="9" t="inlineStr">
-        <is>
-          <t>وجود متطلب للغة الإنجليزية أو للّياقة الطبية لكلية الطب قرار يعود للكلية ويحتاج إلى تأكيد.</t>
-        </is>
-      </c>
+          <t>تأكيد المبلغ المعتمد ومعالجة الضريبة من الإدارة المالية وكلية الطب، وتوحيده في الصفحتين، والإشارة في صفحات البكالوريوس وصفحة التقديم إلى أن الرسوم المختلفة خاصة بمتقدمي كلية الطب.</t>
+        </is>
+      </c>
+      <c r="L56" s="9" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="n">
@@ -3687,45 +3691,49 @@
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>صفحة القبول في كلية الطب (المقدمة، ومعايير القبول، وخطة السنتين الخامسة والسادسة)، وقسم College of Medical Admissions في صفحة القبول في البكالوريوس</t>
+          <t>صفحة القبول في كلية الطب – رابط التقديم (مقارنةً بتقويم القبول وبقية صفحات البكالوريوس)</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>[القبول في البكالوريوس, كلية الطب] The PMU College of Medical curriculum … combines a variety of course-type: | [القبول في البكالوريوس] College of Medical Admissions | [كلية الطب] College of Medical major … were 86 is the minimum acceptable score … Population Health (to be developed in launch phase)</t>
+          <t>[تقويم القبول] For Saudi Students: Apply online through Qabool platform: https://www.uap.sa/ | [القبول في البكالوريوس] Apply online based on the admissions calendar (Apply Now)</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>لغوي ونحوي</t>
+          <t>الاتساق</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>أخطاء لغوية ونص غير محدث</t>
+          <t>قناة تقديم غير موحدة</t>
         </is>
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>تُسمى الكلية «College of Medical» بدلًا من «College of Medicine» في الصفحتين، وتنتهي جملة «combines a variety of course-type:» بنقطتين دون قائمة، وترد «were» بدلًا من «where»، ويتكرر مقرر «Population Health (to be developed in launch phase)» مرتين بعبارة تخطيطية داخلية.</t>
+          <t>تحيل صفحة كلية الطب إلى منصة «قبول» الوطنية (uap.sa) بما يتفق مع تقويم القبول، بينما تحيل بقية صفحات البكالوريوس إلى رابط «Apply Now» الخاص بالجامعة، فلا تتضح القناة المعتمدة لكل فئة من المتقدمين.</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>تصحيح مطلوب</t>
+          <t>متابعة وتحقق</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>منخفضة</t>
+          <t>متوسطة</t>
         </is>
       </c>
       <c r="K57" s="6" t="inlineStr">
         <is>
-          <t>تصحيح التسمية إلى «College of Medicine»، وإعادة صياغة الجملة إلى «combines a variety of course types»، وتصحيح «were» إلى «where»، وحذف العبارة التخطيطية أو بيان الوضع الحالي للمقرر بعد مراجعة كلية الطب.</t>
-        </is>
-      </c>
-      <c r="L57" s="6" t="inlineStr"/>
+          <t>تحديد قناة التقديم المعتمدة لكل فئة (السعوديون، وغير السعوديين) بقرار من مكتب القبول، وذكرها بصيغة موحدة في جميع صفحات البكالوريوس.</t>
+        </is>
+      </c>
+      <c r="L57" s="6" t="inlineStr">
+        <is>
+          <t>وجود رابط uap.sa في صفحة كلية الطب ثابت في سجل الروابط، ولم يُلتقط نص الرابط نفسه في النص المستخرج.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="n">
@@ -3743,27 +3751,27 @@
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>صفحة القبول في كلية الطب – خطة السنوات 3–4 (Block 9) وخطة السنة السادسة</t>
+          <t>صفحة القبول في كلية الطب – Admission Criteria وHow to Apply (الحدود الدنيا ومعادلة النسبة الموزونة)</t>
         </is>
       </c>
       <c r="E58" s="10" t="inlineStr">
         <is>
-          <t>[كلية الطب] Block 9: Transition to Clerkship (Part 1 of CCC – see section below for explanation of CCC) … Surgery 8 weeks (Two 4-week electives) … Vascular Surgery (2-week elective)</t>
+          <t>[كلية الطب] Copy of secondary school certificate or equivalent (95%) … (Qudrat) (80) or equivalent (SAT 1) … (SAAT – Tahseely) (80) or equivalent (SAT 1) 1300 … *20% high school + 40% Qudrat + 40% Tahseely were 86 is the minimum acceptable score</t>
         </is>
       </c>
       <c r="F58" s="9" t="inlineStr">
         <is>
-          <t>تجربة المستخدم</t>
+          <t>دقة المعلومات</t>
         </is>
       </c>
       <c r="G58" s="9" t="inlineStr">
         <is>
-          <t>إحالة مفقودة وعرض مربك</t>
+          <t>تعارض في معايير القبول</t>
         </is>
       </c>
       <c r="H58" s="9" t="inlineStr">
         <is>
-          <t>يحيل Block 9 القارئ إلى «القسم أدناه» لشرح اختصار CCC، ولا يوجد هذا القسم ولا يُعرَّف الاختصار في الصفحة. كما تتناوب عناوين «Elective Rotations» و«Required Rotations» في خطة السنة السادسة بصورة غير متسقة، وتُوصف بعض الخيارات بأنها اختيارية لأسبوعين ضمن كتل موصوفة بمقررين اختياريين من أربعة أسابيع.</t>
+          <t>الحدود الدنيا المنشورة (الثانوية 95% والقدرات 80 والتحصيلي 80) تعطي وفق المعادلة المنشورة نسبة موزونة قدرها 83 فقط، وهي أقل من الحد الأدنى المذكور (86). كما لا يتضح أي درجة يُشترط أن تبلغ 86، ولا ما إذا كانت درجة SAT 1 واحدة (1300) تُغني عن القدرات والتحصيلي معًا، إذ لا يُذكر حد أدنى لـSAT 1 بديلًا عن القدرات.</t>
         </is>
       </c>
       <c r="I58" s="8" t="inlineStr">
@@ -3773,12 +3781,12 @@
       </c>
       <c r="J58" s="8" t="inlineStr">
         <is>
-          <t>منخفضة</t>
+          <t>متوسطة</t>
         </is>
       </c>
       <c r="K58" s="9" t="inlineStr">
         <is>
-          <t>كتابة الاختصار CCC كاملًا وإضافة الشرح أو حذف الإحالة، وإعادة عرض خطة السنة السادسة في جدول (الدورة، عدد الأسابيع، الإجباري والاختياري) بعد مراجعة كلية الطب.</t>
+          <t>تحديد الحدود الدنيا والمعادلة المعتمدة من كلية الطب ومكتب القبول، وإعادة صياغة الملاحظة إلى «where 86 is the minimum acceptable total weighted score»، وتوضيح شروط استخدام SAT 1 بديلًا.</t>
         </is>
       </c>
       <c r="L58" s="9" t="inlineStr"/>
@@ -3789,37 +3797,37 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>القبول في البرنامج التحضيري</t>
+          <t>القبول في كلية الطب</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/admission-to-the-preparatory-program</t>
+          <t>https://pmu.edu.sa/admission/college_of_medicine_admission</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>صفحة القبول في البرنامج التحضيري – الفقرة التعريفية والحاشية وقائمة How to Apply</t>
+          <t>صفحة القبول في كلية الطب – Admission Criteria وقائمة How to Apply</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>[البرنامج التحضيري] mathematics and learning skills** … the following study skills courses are required: … How to Apply: Completed online application</t>
+          <t>[كلية الطب] the process typically involves understanding the weighting and criteria that the medical college uses to evaluate applicants. Here’s how each factor can contribute to the overall acceptance percentage:</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>لغوي ونحوي</t>
+          <t>دقة المعلومات</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>عدم اتساق المصطلحات وصيغة الأمر</t>
+          <t>صياغة غير رسمية ومتطلبات ناقصة</t>
         </is>
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>تستخدم الصفحة مصطلحين للمكوّن نفسه («learning skills» و«study skills»)، ويرد البند الأول في قائمة التقديم بصيغة «Completed online application» بدلًا من صيغة الأمر «Complete online application» المستخدمة في الصفحات الأخرى.</t>
+          <t>تصف فقرة معايير القبول الإجراء بلغة عامة وغير رسمية بدل النص على قاعدة المفاضلة صراحة. ولا تذكر قائمة التقديم أي متطلب للغة الإنجليزية أو للّياقة الطبية، وتخلو من مستندات تطلبها صفحات البكالوريوس الأخرى (الصور الشخصية، وسجل الأسرة، وخطاب عدم الممانعة من جهة العمل).</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
@@ -3829,15 +3837,19 @@
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>منخفضة</t>
+          <t>متوسطة</t>
         </is>
       </c>
       <c r="K59" s="6" t="inlineStr">
         <is>
-          <t>توحيد المصطلح إلى «study skills»، وتصحيح البند إلى «Complete online application».</t>
-        </is>
-      </c>
-      <c r="L59" s="6" t="inlineStr"/>
+          <t>استبدال الفقرة بنص رسمي معتمد مثل: «يُرتَّب المتقدمون وفق النسبة الموزونة (60%) والمقابلة الشخصية (40%)»، وإضافة متطلب اللغة الإنجليزية وأي متطلبات أخرى معتمدة، ومواءمة قائمة المستندات أو النص على اختلافها، بقرار من كلية الطب.</t>
+        </is>
+      </c>
+      <c r="L59" s="6" t="inlineStr">
+        <is>
+          <t>وجود متطلب للغة الإنجليزية أو للّياقة الطبية لكلية الطب قرار يعود للكلية ويحتاج إلى تأكيد.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="n">
@@ -3845,37 +3857,37 @@
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>القبول المباشر من الثانوية</t>
+          <t>القبول في كلية الطب</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/direct-admissions-from-secondary-school</t>
+          <t>https://pmu.edu.sa/admission/college_of_medicine_admission</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>صفحة القبول المباشر – Admission Criteria وHow to Apply (والنص المماثل في صفحات الطلاب الدوليين والقبول بالتحويل والطلاب الزائرين ومتطلبات الحاسب والهندسة)</t>
+          <t>صفحة القبول في كلية الطب (المقدمة، ومعايير القبول، وخطة السنتين الخامسة والسادسة)، وقسم College of Medical Admissions في صفحة القبول في البكالوريوس</t>
         </is>
       </c>
       <c r="E60" s="10" t="inlineStr">
         <is>
-          <t>[القبول المباشر] or equivalent TOEFL iBT (Learn more) | [التحويل] or equivalent TOEFL iBT with acceptable scores (read more...) | [الطلاب الزائرون] or equivalent to TOEFL iBT (learn more...), if the medium of instruction at the home institute is other than English | [/apply] TOEFL iBT: Overall 83, Writing 19</t>
+          <t>[القبول في البكالوريوس, كلية الطب] The PMU College of Medical curriculum … combines a variety of course-type: | [القبول في البكالوريوس] College of Medical Admissions | [كلية الطب] College of Medical major … were 86 is the minimum acceptable score … Population Health (to be developed in launch phase)</t>
         </is>
       </c>
       <c r="F60" s="9" t="inlineStr">
         <is>
-          <t>دقة المعلومات</t>
+          <t>لغوي ونحوي</t>
         </is>
       </c>
       <c r="G60" s="9" t="inlineStr">
         <is>
-          <t>حد أدنى غير منشور</t>
+          <t>أخطاء لغوية ونص غير محدث</t>
         </is>
       </c>
       <c r="H60" s="9" t="inlineStr">
         <is>
-          <t>تقبل صفحات البكالوريوس «ما يعادل TOEFL iBT» أو «درجات مقبولة» دون ذكر الحد الأدنى، بينما تحدد صفحة التقديم وصفحات الدراسات العليا 83 درجة إجمالية و19 في الكتابة. كما تقتصر معايير القبول في صفحة القبول المباشر على IELTS، وتتناوب صفحة الطلاب الزائرين بين «home institute» و«home institution».</t>
+          <t>تُسمى الكلية «College of Medical» بدلًا من «College of Medicine» في الصفحتين، وتنتهي جملة «combines a variety of course-type:» بنقطتين دون قائمة، وترد «were» بدلًا من «where»، ويتكرر مقرر «Population Health (to be developed in launch phase)» مرتين بعبارة تخطيطية داخلية.</t>
         </is>
       </c>
       <c r="I60" s="8" t="inlineStr">
@@ -3885,12 +3897,12 @@
       </c>
       <c r="J60" s="8" t="inlineStr">
         <is>
-          <t>متوسطة</t>
+          <t>منخفضة</t>
         </is>
       </c>
       <c r="K60" s="9" t="inlineStr">
         <is>
-          <t>نشر الحد الأدنى المعتمد لاختبار TOEFL iBT (83 إجمالًا و19 في الكتابة إن أكده مكتب القبول ومركز الاختبارات) في جميع صفحات البكالوريوس أو ربطها بجدول معادلة واحد، واستخدام «home institution» بصورة موحدة.</t>
+          <t>تصحيح التسمية إلى «College of Medicine»، وإعادة صياغة الجملة إلى «combines a variety of course types»، وتصحيح «were» إلى «where»، وحذف العبارة التخطيطية أو بيان الوضع الحالي للمقرر بعد مراجعة كلية الطب.</t>
         </is>
       </c>
       <c r="L60" s="9" t="inlineStr"/>
@@ -3901,59 +3913,55 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>القبول المباشر من الثانوية</t>
+          <t>القبول في كلية الطب</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/direct-admissions-from-secondary-school</t>
+          <t>https://pmu.edu.sa/admission/college_of_medicine_admission</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>شرط اختبار اللغة الإنجليزية في صفحة القبول المباشر (مقارنةً بصفحة التقديم وصفحات الدراسات العليا)</t>
+          <t>صفحة القبول في كلية الطب – خطة السنوات 3–4 (Block 9) وخطة السنة السادسة</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>[القبول المباشر] minimum scores of 6.0 overall and 5.5 in writing or equivalent TOEFL iBT | [/apply] IELTS Academic: Overall 6.0, Writing 5.5 … TOEFL iBT: Overall 83, Writing 19</t>
+          <t>[كلية الطب] Block 9: Transition to Clerkship (Part 1 of CCC – see section below for explanation of CCC) … Surgery 8 weeks (Two 4-week electives) … Vascular Surgery (2-week elective)</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>دقة المعلومات</t>
+          <t>تجربة المستخدم</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>معادلة درجات تحتاج مراجعة</t>
+          <t>إحالة مفقودة وعرض مربك</t>
         </is>
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>تعامل الصفحات درجة IELTS 6.0 ودرجة TOEFL iBT 83 بوصفهما متعادلتين، في حين تشير جداول المقارنة المنشورة من الجهة المالكة لاختبار TOEFL إلى أن 6.0 تقابل نطاقًا أدنى وأن 83 تقابل نحو 6.5.</t>
+          <t>يحيل Block 9 القارئ إلى «القسم أدناه» لشرح اختصار CCC، ولا يوجد هذا القسم ولا يُعرَّف الاختصار في الصفحة. كما تتناوب عناوين «Elective Rotations» و«Required Rotations» في خطة السنة السادسة بصورة غير متسقة، وتُوصف بعض الخيارات بأنها اختيارية لأسبوعين ضمن كتل موصوفة بمقررين اختياريين من أربعة أسابيع.</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>متابعة وتحقق</t>
+          <t>تصحيح مطلوب</t>
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>متوسطة</t>
+          <t>منخفضة</t>
         </is>
       </c>
       <c r="K61" s="6" t="inlineStr">
         <is>
-          <t>مراجعة جدول المعادلة بين IELTS وTOEFL iBT من قبل مكتب القبول ومركز الاختبارات واعتماد درجات متكافئة، ثم نشرها موحدة في جميع الصفحات.</t>
-        </is>
-      </c>
-      <c r="L61" s="6" t="inlineStr">
-        <is>
-          <t>جداول المعادلة مصدر خارجي لم يُتحقق منه من صفحات الجامعة؛ يلزم تأكيده من الجهة المختصة.</t>
-        </is>
-      </c>
+          <t>كتابة الاختصار CCC كاملًا وإضافة الشرح أو حذف الإحالة، وإعادة عرض خطة السنة السادسة في جدول (الدورة، عدد الأسابيع، الإجباري والاختياري) بعد مراجعة كلية الطب.</t>
+        </is>
+      </c>
+      <c r="L61" s="6" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="8" t="n">
@@ -3961,37 +3969,37 @@
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>القبول المباشر من الثانوية</t>
+          <t>القبول في البرنامج التحضيري</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/direct-admissions-from-secondary-school</t>
+          <t>https://pmu.edu.sa/admission/admission-to-the-preparatory-program</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>قائمة How to Apply في صفحة القبول المباشر وصفحة متطلبات الحاسب والهندسة (مقارنةً بصفحات البرنامج التحضيري والتحويل والزائرين والطلاب الدوليين)</t>
+          <t>صفحة القبول في البرنامج التحضيري – الفقرة التعريفية والحاشية وقائمة How to Apply</t>
         </is>
       </c>
       <c r="E62" s="10" t="inlineStr">
         <is>
-          <t>[القبول المباشر, الحاسب والهندسة] Copy of Saudi ID | [البرنامج التحضيري, التحويل, الطلاب الزائرون] Copy of Saudi ID or “Iqama” (for Non-Saudis) | [الطلاب الدوليون] Copy of National ID</t>
+          <t>[البرنامج التحضيري] mathematics and learning skills** … the following study skills courses are required: … How to Apply: Completed online application</t>
         </is>
       </c>
       <c r="F62" s="9" t="inlineStr">
         <is>
-          <t>الاتساق</t>
+          <t>لغوي ونحوي</t>
         </is>
       </c>
       <c r="G62" s="9" t="inlineStr">
         <is>
-          <t>عدم اتساق قوائم المستندات</t>
+          <t>عدم اتساق المصطلحات وصيغة الأمر</t>
         </is>
       </c>
       <c r="H62" s="9" t="inlineStr">
         <is>
-          <t>تطلب صفحتا القبول المباشر ومتطلبات الحاسب والهندسة «صورة الهوية السعودية» فقط دون خيار الإقامة لغير السعوديين، بينما تذكر صفحات أخرى «الهوية السعودية أو الإقامة»، وتطلب صفحة الطلاب الدوليين «صورة الهوية الوطنية» دون توضيح أنها هوية بلد المتقدم.</t>
+          <t>تستخدم الصفحة مصطلحين للمكوّن نفسه («learning skills» و«study skills»)، ويرد البند الأول في قائمة التقديم بصيغة «Completed online application» بدلًا من صيغة الأمر «Complete online application» المستخدمة في الصفحات الأخرى.</t>
         </is>
       </c>
       <c r="I62" s="8" t="inlineStr">
@@ -4001,12 +4009,12 @@
       </c>
       <c r="J62" s="8" t="inlineStr">
         <is>
-          <t>متوسطة</t>
+          <t>منخفضة</t>
         </is>
       </c>
       <c r="K62" s="9" t="inlineStr">
         <is>
-          <t>اعتماد قائمة مستندات واحدة لكل فئة من المتقدمين، وتعديل الصفحتين إلى «Copy of Saudi ID or Iqama (for non-Saudis)»، وتوضيح عبارة صفحة الطلاب الدوليين إلى «Copy of national ID from home country (if applicable)».</t>
+          <t>توحيد المصطلح إلى «study skills»، وتصحيح البند إلى «Complete online application».</t>
         </is>
       </c>
       <c r="L62" s="9" t="inlineStr"/>
@@ -4017,37 +4025,37 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>القبول بالتحويل من جامعات أخرى</t>
+          <t>القبول المباشر من الثانوية</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/admission-from-other-universities</t>
+          <t>https://pmu.edu.sa/admission/direct-admissions-from-secondary-school</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>صفحة القبول بالتحويل – Admission Criteria وEligibility (والنص نفسه في قسم Transfer Students بصفحة الطلاب الدوليين)</t>
+          <t>صفحة القبول المباشر – Admission Criteria وHow to Apply (والنص المماثل في صفحات الطلاب الدوليين والقبول بالتحويل والطلاب الزائرين ومتطلبات الحاسب والهندسة)</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>[التحويل, الطلاب الدوليون] In order to be consider as a transfer candidate … The total GPA is 2.0 out of 4.0 from the previous institution</t>
+          <t>[القبول المباشر] or equivalent TOEFL iBT (Learn more) | [التحويل] or equivalent TOEFL iBT with acceptable scores (read more...) | [الطلاب الزائرون] or equivalent to TOEFL iBT (learn more...), if the medium of instruction at the home institute is other than English | [/apply] TOEFL iBT: Overall 83, Writing 19</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>لغوي ونحوي</t>
+          <t>دقة المعلومات</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>خطأ نحوي وصياغة ملتبسة</t>
+          <t>حد أدنى غير منشور</t>
         </is>
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>ترد في الصفحتين عبارة «to be consider» والصواب «to be considered»، ويرد شرط المعدل بصيغة تقريرية («The total GPA is 2.0») توحي بقيمة ثابتة لا بحدٍّ أدنى.</t>
+          <t>تقبل صفحات البكالوريوس «ما يعادل TOEFL iBT» أو «درجات مقبولة» دون ذكر الحد الأدنى، بينما تحدد صفحة التقديم وصفحات الدراسات العليا 83 درجة إجمالية و19 في الكتابة. كما تقتصر معايير القبول في صفحة القبول المباشر على IELTS، وتتناوب صفحة الطلاب الزائرين بين «home institute» و«home institution».</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr">
@@ -4057,12 +4065,12 @@
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>منخفضة</t>
+          <t>متوسطة</t>
         </is>
       </c>
       <c r="K63" s="6" t="inlineStr">
         <is>
-          <t>تصحيح العبارة إلى «To be considered as a transfer candidate» وإعادة صياغة الشرط إلى «Minimum cumulative GPA of 2.0 out of 4.0 at the previous institution» بعد تأكيد مكتب القبول.</t>
+          <t>نشر الحد الأدنى المعتمد لاختبار TOEFL iBT (83 إجمالًا و19 في الكتابة إن أكده مكتب القبول ومركز الاختبارات) في جميع صفحات البكالوريوس أو ربطها بجدول معادلة واحد، واستخدام «home institution» بصورة موحدة.</t>
         </is>
       </c>
       <c r="L63" s="6" t="inlineStr"/>
@@ -4073,22 +4081,22 @@
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>القبول بالتحويل من جامعات أخرى</t>
+          <t>القبول المباشر من الثانوية</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/admission-from-other-universities</t>
+          <t>https://pmu.edu.sa/admission/direct-admissions-from-secondary-school</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>صفحة القبول بالتحويل – Eligibility (والنص المماثل في صفحة الطلاب الدوليين)</t>
+          <t>شرط اختبار اللغة الإنجليزية في صفحة القبول المباشر (مقارنةً بصفحة التقديم وصفحات الدراسات العليا)</t>
         </is>
       </c>
       <c r="E64" s="10" t="inlineStr">
         <is>
-          <t>[التحويل] international university or can be a college/community college in a Western country (Associate Degree or above)</t>
+          <t>[القبول المباشر] minimum scores of 6.0 overall and 5.5 in writing or equivalent TOEFL iBT | [/apply] IELTS Academic: Overall 6.0, Writing 5.5 … TOEFL iBT: Overall 83, Writing 19</t>
         </is>
       </c>
       <c r="F64" s="9" t="inlineStr">
@@ -4098,30 +4106,34 @@
       </c>
       <c r="G64" s="9" t="inlineStr">
         <is>
-          <t>معيار غير محدد</t>
+          <t>معادلة درجات تحتاج مراجعة</t>
         </is>
       </c>
       <c r="H64" s="9" t="inlineStr">
         <is>
-          <t>يشير شرط الأهلية إلى كليات أو كليات مجتمع «في دولة غربية» دون تعريف موضوعي لهذا الوصف، فلا يتضح للمتقدم أي المؤسسات مقبولة.</t>
+          <t>تعامل الصفحات درجة IELTS 6.0 ودرجة TOEFL iBT 83 بوصفهما متعادلتين، في حين تشير جداول المقارنة المنشورة من الجهة المالكة لاختبار TOEFL إلى أن 6.0 تقابل نطاقًا أدنى وأن 83 تقابل نحو 6.5.</t>
         </is>
       </c>
       <c r="I64" s="8" t="inlineStr">
         <is>
-          <t>توصية تحسين</t>
+          <t>متابعة وتحقق</t>
         </is>
       </c>
       <c r="J64" s="8" t="inlineStr">
         <is>
-          <t>منخفضة</t>
+          <t>متوسطة</t>
         </is>
       </c>
       <c r="K64" s="9" t="inlineStr">
         <is>
-          <t>تعريف المؤسسات المقبولة بمعيار موضوعي (مثل المؤسسات المعتمدة والمعترف بها من وزارة التعليم)، بقرار من مكتب القبول.</t>
-        </is>
-      </c>
-      <c r="L64" s="9" t="inlineStr"/>
+          <t>مراجعة جدول المعادلة بين IELTS وTOEFL iBT من قبل مكتب القبول ومركز الاختبارات واعتماد درجات متكافئة، ثم نشرها موحدة في جميع الصفحات.</t>
+        </is>
+      </c>
+      <c r="L64" s="9" t="inlineStr">
+        <is>
+          <t>جداول المعادلة مصدر خارجي لم يُتحقق منه من صفحات الجامعة؛ يلزم تأكيده من الجهة المختصة.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="n">
@@ -4129,22 +4141,22 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>الطلاب الزائرون</t>
+          <t>القبول المباشر من الثانوية</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/visiting-student-admission</t>
+          <t>https://pmu.edu.sa/admission/direct-admissions-from-secondary-school</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>عنوان الصفحة في المتصفح ومسار التنقل في صفحة الطلاب الزائرين؛ ومسار التنقل والعنوان في صفحة الانتقال من البرنامج التحضيري إلى البكالوريوس</t>
+          <t>قائمة How to Apply في صفحة القبول المباشر وصفحة متطلبات الحاسب والهندسة (مقارنةً بصفحات البرنامج التحضيري والتحويل والزائرين والطلاب الدوليين)</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>[الطلاب الزائرون] Visiting Student Admission :: Undergraduate :: Admission Office … Admission Office &gt; Undergraduate &gt; Visiting Student Admissions | [الانتقال من التحضيري] Preparatory Program to Undergraduate Programs … ADMISSIONS FROM THE PREPARATORY PROGRAM … Admission from the Preparatory Program</t>
+          <t>[القبول المباشر, الحاسب والهندسة] Copy of Saudi ID | [البرنامج التحضيري, التحويل, الطلاب الزائرون] Copy of Saudi ID or “Iqama” (for Non-Saudis) | [الطلاب الدوليون] Copy of National ID</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
@@ -4154,12 +4166,12 @@
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>عدم اتساق التسمية</t>
+          <t>عدم اتساق قوائم المستندات</t>
         </is>
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>تستخدم صفحة الطلاب الزائرين «Admission Office» و«Undergraduate» بدلًا من «Admissions Office» و«Undergraduate Admissions» المستخدمة في بقية الصفحات، وتختلف تسمية صفحة الانتقال من البرنامج التحضيري بين مسار التنقل والعنوان الرئيسي وعنوان المتصفح.</t>
+          <t>تطلب صفحتا القبول المباشر ومتطلبات الحاسب والهندسة «صورة الهوية السعودية» فقط دون خيار الإقامة لغير السعوديين، بينما تذكر صفحات أخرى «الهوية السعودية أو الإقامة»، وتطلب صفحة الطلاب الدوليين «صورة الهوية الوطنية» دون توضيح أنها هوية بلد المتقدم.</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr">
@@ -4169,12 +4181,12 @@
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>منخفضة</t>
+          <t>متوسطة</t>
         </is>
       </c>
       <c r="K65" s="6" t="inlineStr">
         <is>
-          <t>توحيد التسمية في مسار التنقل والعناوين وعنوان المتصفح وفق التسمية المعتمدة («Admissions Office &gt; Undergraduate Admissions»)، واعتماد اسم واحد لكل صفحة.</t>
+          <t>اعتماد قائمة مستندات واحدة لكل فئة من المتقدمين، وتعديل الصفحتين إلى «Copy of Saudi ID or Iqama (for non-Saudis)»، وتوضيح عبارة صفحة الطلاب الدوليين إلى «Copy of national ID from home country (if applicable)».</t>
         </is>
       </c>
       <c r="L65" s="6" t="inlineStr"/>
@@ -4185,37 +4197,37 @@
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>الانتقال من التحضيري إلى البكالوريوس</t>
+          <t>القبول بالتحويل من جامعات أخرى</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/admission-from-the-prep-to-ug-programs</t>
+          <t>https://pmu.edu.sa/admission/admission-from-other-universities</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>صفحة الانتقال من البرنامج التحضيري إلى البكالوريوس – جدول مقررات الرياضيات وحواشيه (مقارنةً بصفحة الخطة الدراسية للبرنامج التحضيري)</t>
+          <t>صفحة القبول بالتحويل – Admission Criteria وEligibility (والنص نفسه في قسم Transfer Students بصفحة الطلاب الدوليين)</t>
         </is>
       </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
-          <t>[الانتقال من التحضيري] College of Computer Engineering &amp; Science** … College of Architecture &amp; Design* … * Department of Information Technology is excluded from PRPM 0022 ** Department of Architecture is excluded from PRPM 0012 | [Study plan] * Department of Interior Design is excluded from PRPM 0022</t>
+          <t>[التحويل, الطلاب الدوليون] In order to be consider as a transfer candidate … The total GPA is 2.0 out of 4.0 from the previous institution</t>
         </is>
       </c>
       <c r="F66" s="9" t="inlineStr">
         <is>
-          <t>دقة المعلومات</t>
+          <t>لغوي ونحوي</t>
         </is>
       </c>
       <c r="G66" s="9" t="inlineStr">
         <is>
-          <t>تعارض في جدول المتطلبات</t>
+          <t>خطأ نحوي وصياغة ملتبسة</t>
         </is>
       </c>
       <c r="H66" s="9" t="inlineStr">
         <is>
-          <t>لا تطابق علامات الحواشي في جدول الرياضيات الصفوف الصحيحة: حاشية تقنية المعلومات مرتبطة بكليتي الهندسة والعمارة والتصميم، وحاشية العمارة مرتبطة بكلية هندسة وعلوم الحاسب. ويُظهر الجدول مقرر PRPM 0012 مطلوبًا للعمارة والتصميم مع أن الحاشية تستثني قسم العمارة منه، كما تختلف الحواشي عن جدول صفحة الخطة الدراسية للبرنامج التحضيري.</t>
+          <t>ترد في الصفحتين عبارة «to be consider» والصواب «to be considered»، ويرد شرط المعدل بصيغة تقريرية («The total GPA is 2.0») توحي بقيمة ثابتة لا بحدٍّ أدنى.</t>
         </is>
       </c>
       <c r="I66" s="8" t="inlineStr">
@@ -4225,12 +4237,12 @@
       </c>
       <c r="J66" s="8" t="inlineStr">
         <is>
-          <t>متوسطة</t>
+          <t>منخفضة</t>
         </is>
       </c>
       <c r="K66" s="9" t="inlineStr">
         <is>
-          <t>اعتماد جدول واحد لمتطلبات الرياضيات من البرنامج التحضيري بعد تأكيد مقررات العمارة، وتصحيح علامات الحواشي وقيم الجدول، ونشره بالصيغة نفسها في الصفحتين.</t>
+          <t>تصحيح العبارة إلى «To be considered as a transfer candidate» وإعادة صياغة الشرط إلى «Minimum cumulative GPA of 2.0 out of 4.0 at the previous institution» بعد تأكيد مكتب القبول.</t>
         </is>
       </c>
       <c r="L66" s="9" t="inlineStr"/>
@@ -4241,22 +4253,22 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>الانتقال من التحضيري إلى البكالوريوس</t>
+          <t>القبول بالتحويل من جامعات أخرى</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/admission-from-the-prep-to-ug-programs</t>
+          <t>https://pmu.edu.sa/admission/admission-from-other-universities</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>صفحة الانتقال من البرنامج التحضيري إلى البكالوريوس – Criteria and Procedure</t>
+          <t>صفحة القبول بالتحويل – Eligibility (والنص المماثل في صفحة الطلاب الدوليين)</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>[الانتقال من التحضيري] Successfully pass the EXIT exam</t>
+          <t>[التحويل] international university or can be a college/community college in a Western country (Associate Degree or above)</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
@@ -4266,12 +4278,12 @@
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>معلومة ناقصة</t>
+          <t>معيار غير محدد</t>
         </is>
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>يشترط للانتقال إلى البكالوريوس اجتياز «اختبار EXIT» دون وصف للاختبار أو درجة النجاح فيه أو رابط لمعلوماته.</t>
+          <t>يشير شرط الأهلية إلى كليات أو كليات مجتمع «في دولة غربية» دون تعريف موضوعي لهذا الوصف، فلا يتضح للمتقدم أي المؤسسات مقبولة.</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr">
@@ -4281,12 +4293,12 @@
       </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>متوسطة</t>
+          <t>منخفضة</t>
         </is>
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
-          <t>إضافة وصف موجز للاختبار ودرجة النجاح المعتمدة، أو رابط لصفحة توضحه، بالتنسيق مع البرنامج التحضيري.</t>
+          <t>تعريف المؤسسات المقبولة بمعيار موضوعي (مثل المؤسسات المعتمدة والمعترف بها من وزارة التعليم)، بقرار من مكتب القبول.</t>
         </is>
       </c>
       <c r="L67" s="6" t="inlineStr"/>
@@ -4297,42 +4309,42 @@
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>الانتقال من التحضيري إلى البكالوريوس</t>
+          <t>الطلاب الزائرون</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/admission-from-the-prep-to-ug-programs</t>
+          <t>https://pmu.edu.sa/admission/visiting-student-admission</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>صفحة الانتقال من البرنامج التحضيري إلى البكالوريوس – جدول مقررات الرياضيات</t>
+          <t>عنوان الصفحة في المتصفح ومسار التنقل في صفحة الطلاب الزائرين؛ ومسار التنقل والعنوان في صفحة الانتقال من البرنامج التحضيري إلى البكالوريوس</t>
         </is>
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>[الانتقال من التحضيري] College of Sciences &amp; Human Studies … Department of Interior Design</t>
+          <t>[الطلاب الزائرون] Visiting Student Admission :: Undergraduate :: Admission Office … Admission Office &gt; Undergraduate &gt; Visiting Student Admissions | [الانتقال من التحضيري] Preparatory Program to Undergraduate Programs … ADMISSIONS FROM THE PREPARATORY PROGRAM … Admission from the Preparatory Program</t>
         </is>
       </c>
       <c r="F68" s="9" t="inlineStr">
         <is>
-          <t>دقة المعلومات</t>
+          <t>الاتساق</t>
         </is>
       </c>
       <c r="G68" s="9" t="inlineStr">
         <is>
-          <t>معلومة ناقصة</t>
+          <t>عدم اتساق التسمية</t>
         </is>
       </c>
       <c r="H68" s="9" t="inlineStr">
         <is>
-          <t>لا يتضمن جدول متطلبات الرياضيات صفًا لكلية الطب، ولا يوضح ما إذا كان تخصص الذكاء الاصطناعي يتبع متطلبات كلية هندسة وعلوم الحاسب.</t>
+          <t>تستخدم صفحة الطلاب الزائرين «Admission Office» و«Undergraduate» بدلًا من «Admissions Office» و«Undergraduate Admissions» المستخدمة في بقية الصفحات، وتختلف تسمية صفحة الانتقال من البرنامج التحضيري بين مسار التنقل والعنوان الرئيسي وعنوان المتصفح.</t>
         </is>
       </c>
       <c r="I68" s="8" t="inlineStr">
         <is>
-          <t>متابعة وتحقق</t>
+          <t>تصحيح مطلوب</t>
         </is>
       </c>
       <c r="J68" s="8" t="inlineStr">
@@ -4342,14 +4354,10 @@
       </c>
       <c r="K68" s="9" t="inlineStr">
         <is>
-          <t>تأكيد متطلبات كلية الطب وتخصص الذكاء الاصطناعي من البرنامج التحضيري، ثم إضافة صف لكلية الطب (أو النص على استثنائها) وتوضيح متطلب الذكاء الاصطناعي.</t>
-        </is>
-      </c>
-      <c r="L68" s="9" t="inlineStr">
-        <is>
-          <t>لم يُتحقق مما إذا كان طلاب كلية الطب يمرون بالبرنامج التحضيري.</t>
-        </is>
-      </c>
+          <t>توحيد التسمية في مسار التنقل والعناوين وعنوان المتصفح وفق التسمية المعتمدة («Admissions Office &gt; Undergraduate Admissions»)، واعتماد اسم واحد لكل صفحة.</t>
+        </is>
+      </c>
+      <c r="L68" s="9" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="n">
@@ -4367,27 +4375,27 @@
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>صفحة الانتقال من البرنامج التحضيري إلى البكالوريوس – فقرة مقررات الرياضيات وعنوان الجدول</t>
+          <t>صفحة الانتقال من البرنامج التحضيري إلى البكالوريوس – جدول مقررات الرياضيات وحواشيه (مقارنةً بصفحة الخطة الدراسية للبرنامج التحضيري)</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>[الانتقال من التحضيري] Depending on students desired major at the university … PRPM 0012 | PRPM0022</t>
+          <t>[الانتقال من التحضيري] College of Computer Engineering &amp; Science** … College of Architecture &amp; Design* … * Department of Information Technology is excluded from PRPM 0022 ** Department of Architecture is excluded from PRPM 0012 | [Study plan] * Department of Interior Design is excluded from PRPM 0022</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>لغوي ونحوي</t>
+          <t>دقة المعلومات</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>أخطاء تحريرية</t>
+          <t>تعارض في جدول المتطلبات</t>
         </is>
       </c>
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>تفتقد عبارة «students desired major» علامة الملكية، ويُكتب رمز المقرر في عنوان الجدول «PRPM0022» دون مسافة خلافًا لكتابته «PRPM 0022» في بقية الصفحة.</t>
+          <t>لا تطابق علامات الحواشي في جدول الرياضيات الصفوف الصحيحة: حاشية تقنية المعلومات مرتبطة بكليتي الهندسة والعمارة والتصميم، وحاشية العمارة مرتبطة بكلية هندسة وعلوم الحاسب. ويُظهر الجدول مقرر PRPM 0012 مطلوبًا للعمارة والتصميم مع أن الحاشية تستثني قسم العمارة منه، كما تختلف الحواشي عن جدول صفحة الخطة الدراسية للبرنامج التحضيري.</t>
         </is>
       </c>
       <c r="I69" s="5" t="inlineStr">
@@ -4397,12 +4405,12 @@
       </c>
       <c r="J69" s="5" t="inlineStr">
         <is>
-          <t>منخفضة</t>
+          <t>متوسطة</t>
         </is>
       </c>
       <c r="K69" s="6" t="inlineStr">
         <is>
-          <t>تصحيح العبارة إلى «Depending on students’ desired major» وتوحيد رمز المقرر إلى «PRPM 0022».</t>
+          <t>اعتماد جدول واحد لمتطلبات الرياضيات من البرنامج التحضيري بعد تأكيد مقررات العمارة، وتصحيح علامات الحواشي وقيم الجدول، ونشره بالصيغة نفسها في الصفحتين.</t>
         </is>
       </c>
       <c r="L69" s="6" t="inlineStr"/>
@@ -4418,54 +4426,50 @@
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>https://www.pmu.edu.sa/admission/admission-from-the-prep-to-ug-programs ; https://www.pmu.edu.sa/admission/aptis-placement-test</t>
+          <t>https://pmu.edu.sa/admission/admission-from-the-prep-to-ug-programs</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>عرض الصفحة على الجوال (عرض 390 بكسل)</t>
+          <t>صفحة الانتقال من البرنامج التحضيري إلى البكالوريوس – Criteria and Procedure</t>
         </is>
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>(فحص عرض) عرض محتوى الصفحتين أكبر من عرض شاشة الجوال</t>
+          <t>[الانتقال من التحضيري] Successfully pass the EXIT exam</t>
         </is>
       </c>
       <c r="F70" s="9" t="inlineStr">
         <is>
-          <t>تجربة المستخدم</t>
+          <t>دقة المعلومات</t>
         </is>
       </c>
       <c r="G70" s="9" t="inlineStr">
         <is>
-          <t>تمرير أفقي على الجوال</t>
+          <t>معلومة ناقصة</t>
         </is>
       </c>
       <c r="H70" s="9" t="inlineStr">
         <is>
-          <t>يتجاوز عرض المحتوى عرض شاشة الجوال في صفحتي الانتقال من البرنامج التحضيري إلى البكالوريوس واختبار Aptis، فيضطر المستخدم إلى التمرير أفقيًا.</t>
+          <t>يشترط للانتقال إلى البكالوريوس اجتياز «اختبار EXIT» دون وصف للاختبار أو درجة النجاح فيه أو رابط لمعلوماته.</t>
         </is>
       </c>
       <c r="I70" s="8" t="inlineStr">
         <is>
-          <t>تصحيح مطلوب</t>
+          <t>توصية تحسين</t>
         </is>
       </c>
       <c r="J70" s="8" t="inlineStr">
         <is>
-          <t>منخفضة</t>
+          <t>متوسطة</t>
         </is>
       </c>
       <c r="K70" s="9" t="inlineStr">
         <is>
-          <t>جعل الجداول والروابط الطويلة متجاوبة (التفاف النص، أو جداول قابلة للتمرير داخل إطارها).</t>
-        </is>
-      </c>
-      <c r="L70" s="9" t="inlineStr">
-        <is>
-          <t>فحص بمتصفح محمول بتاريخ 11 أكتوبر 2026.</t>
-        </is>
-      </c>
+          <t>إضافة وصف موجز للاختبار ودرجة النجاح المعتمدة، أو رابط لصفحة توضحه، بالتنسيق مع البرنامج التحضيري.</t>
+        </is>
+      </c>
+      <c r="L70" s="9" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n">
@@ -4473,55 +4477,59 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>متطلبات تخصصات الحاسب والهندسة</t>
+          <t>الانتقال من التحضيري إلى البكالوريوس</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/admissions_requirements_cs_eng_majors</t>
+          <t>https://pmu.edu.sa/admission/admission-from-the-prep-to-ug-programs</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>صفحة متطلبات تخصصات الحاسب والهندسة – المقدمة وAdmission Criteria (مقارنةً بصفحة SAT وصفحة القبول في البكالوريوس وصفحة الطلاب الدوليين)</t>
+          <t>صفحة الانتقال من البرنامج التحضيري إلى البكالوريوس – جدول مقررات الرياضيات</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>[الحاسب والهندسة] These majors are Architecture, Computer Science, Computer Engineering, Software Engineering … to Computer Science or Engineering majors | [SAT] Software Engineering, Artificial Intelligence | [القبول في البكالوريوس] Computer Science and Engineering Majors Admission Requirements | [الطلاب الدوليون] Non-Engineering Majors:</t>
+          <t>[الانتقال من التحضيري] College of Sciences &amp; Human Studies … Department of Interior Design</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>الاتساق</t>
+          <t>دقة المعلومات</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>قائمة تخصصات غير موحدة</t>
+          <t>معلومة ناقصة</t>
         </is>
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>لا تتضمن قائمة التخصصات ذات المتطلبات الخاصة في صفحة متطلبات الحاسب والهندسة تخصص الذكاء الاصطناعي، بينما تتضمنه صفحة SAT وصفحة التقديم. كما تقتصر جملة معايير القبول وعنوان الرابط في صفحة البكالوريوس على «الحاسب والهندسة» رغم شمول العمارة، وتقسم صفحة الطلاب الدوليين التخصصات إلى «غير هندسية» و«حاسب وهندسة» دون تعدادها.</t>
+          <t>لا يتضمن جدول متطلبات الرياضيات صفًا لكلية الطب، ولا يوضح ما إذا كان تخصص الذكاء الاصطناعي يتبع متطلبات كلية هندسة وعلوم الحاسب.</t>
         </is>
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>تصحيح مطلوب</t>
+          <t>متابعة وتحقق</t>
         </is>
       </c>
       <c r="J71" s="5" t="inlineStr">
         <is>
-          <t>متوسطة</t>
+          <t>منخفضة</t>
         </is>
       </c>
       <c r="K71" s="6" t="inlineStr">
         <is>
-          <t>اعتماد قائمة نهائية واحدة بالتخصصات ذات المتطلبات الخاصة من مكتب القبول، وتوحيدها وتسمية المجموعة في صفحة متطلبات الحاسب والهندسة وصفحة SAT وصفحة التقديم وصفحة البكالوريوس وصفحة الطلاب الدوليين، مع تعداد التخصصات في كل مجموعة.</t>
-        </is>
-      </c>
-      <c r="L71" s="6" t="inlineStr"/>
+          <t>تأكيد متطلبات كلية الطب وتخصص الذكاء الاصطناعي من البرنامج التحضيري، ثم إضافة صف لكلية الطب (أو النص على استثنائها) وتوضيح متطلب الذكاء الاصطناعي.</t>
+        </is>
+      </c>
+      <c r="L71" s="6" t="inlineStr">
+        <is>
+          <t>لم يُتحقق مما إذا كان طلاب كلية الطب يمرون بالبرنامج التحضيري.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="8" t="n">
@@ -4529,59 +4537,55 @@
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>متطلبات تخصصات الحاسب والهندسة</t>
+          <t>الانتقال من التحضيري إلى البكالوريوس</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/admissions_requirements_cs_eng_majors</t>
+          <t>https://pmu.edu.sa/admission/admission-from-the-prep-to-ug-programs</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>صفحة متطلبات تخصصات الحاسب والهندسة – الحاشية أسفل جدول المتطلبات</t>
+          <t>صفحة الانتقال من البرنامج التحضيري إلى البكالوريوس – فقرة مقررات الرياضيات وعنوان الجدول</t>
         </is>
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>[الحاسب والهندسة] *Students with lower marks may apply, however, the minimum weighted total, defined by the Admissions Office, should be met.</t>
+          <t>[الانتقال من التحضيري] Depending on students desired major at the university … PRPM 0012 | PRPM0022</t>
         </is>
       </c>
       <c r="F72" s="9" t="inlineStr">
         <is>
-          <t>دقة المعلومات</t>
+          <t>لغوي ونحوي</t>
         </is>
       </c>
       <c r="G72" s="9" t="inlineStr">
         <is>
-          <t>حد أدنى غير منشور</t>
+          <t>أخطاء تحريرية</t>
         </is>
       </c>
       <c r="H72" s="9" t="inlineStr">
         <is>
-          <t>تشترط الصفحة استيفاء حد أدنى للنسبة الموزونة «يحدده مكتب القبول» دون ذكر قيمته، في حين تنشر صفحة كلية الطب حدها الأدنى.</t>
+          <t>تفتقد عبارة «students desired major» علامة الملكية، ويُكتب رمز المقرر في عنوان الجدول «PRPM0022» دون مسافة خلافًا لكتابته «PRPM 0022» في بقية الصفحة.</t>
         </is>
       </c>
       <c r="I72" s="8" t="inlineStr">
         <is>
-          <t>متابعة وتحقق</t>
+          <t>تصحيح مطلوب</t>
         </is>
       </c>
       <c r="J72" s="8" t="inlineStr">
         <is>
-          <t>متوسطة</t>
+          <t>منخفضة</t>
         </is>
       </c>
       <c r="K72" s="9" t="inlineStr">
         <is>
-          <t>يقرر مكتب القبول نشر الحد الأدنى للنسبة الموزونة لكل مجموعة تخصصات، أو بيان آلية تحديده، وتوحيد ذلك في صفحات البكالوريوس.</t>
-        </is>
-      </c>
-      <c r="L72" s="9" t="inlineStr">
-        <is>
-          <t>قرار نشر الحد الأدنى يعود إلى الجهة المالكة لسياسة القبول.</t>
-        </is>
-      </c>
+          <t>تصحيح العبارة إلى «Depending on students’ desired major» وتوحيد رمز المقرر إلى «PRPM 0022».</t>
+        </is>
+      </c>
+      <c r="L72" s="9" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="n">
@@ -4589,22 +4593,22 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>متطلبات تخصصات الحاسب والهندسة</t>
+          <t>الانتقال من التحضيري إلى البكالوريوس</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/admissions_requirements_cs_eng_majors</t>
+          <t>https://www.pmu.edu.sa/admission/admission-from-the-prep-to-ug-programs ; https://www.pmu.edu.sa/admission/aptis-placement-test</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>صفحة متطلبات تخصصات الحاسب والهندسة – How to Apply (والنص نفسه في قسمي Transfer Students وVisitor Students بصفحة الطلاب الدوليين)</t>
+          <t>عرض الصفحة على الجوال (عرض 390 بكسل)</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>[الحاسب والهندسة, الطلاب الدوليون] Submit original IELTS (Academic version) certificate or equivalent TOEFL iBT with acceptable scores (if available) or For direct entry, submit original IELTS (Academic version) certificate with minimum scores of 6.0 overall and 5.5 in writing</t>
+          <t>(فحص عرض) عرض محتوى الصفحتين أكبر من عرض شاشة الجوال</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
@@ -4614,12 +4618,12 @@
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>صياغة ملتبسة</t>
+          <t>تمرير أفقي على الجوال</t>
         </is>
       </c>
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>يتوزع شرط اختبار اللغة الإنجليزية على بندين متداخلين يربطهما «or» في نهاية الأول مع حرف كبير زائد في «For»، فلا يتضح الفرق بين خيار تقديم الدرجة لتحديد المستوى وخيار القبول المباشر.</t>
+          <t>يتجاوز عرض المحتوى عرض شاشة الجوال في صفحتي الانتقال من البرنامج التحضيري إلى البكالوريوس واختبار Aptis، فيضطر المستخدم إلى التمرير أفقيًا.</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr">
@@ -4634,10 +4638,14 @@
       </c>
       <c r="K73" s="6" t="inlineStr">
         <is>
-          <t>دمج الشرط في بند واحد واضح يفصل بين الخيارين: (أ) دون شهادة يُحدد موعد لاختبار تحديد المستوى، (ب) للقبول المباشر تُقدم شهادة IELTS أو TOEFL iBT بالحد الأدنى المعتمد.</t>
-        </is>
-      </c>
-      <c r="L73" s="6" t="inlineStr"/>
+          <t>جعل الجداول والروابط الطويلة متجاوبة (التفاف النص، أو جداول قابلة للتمرير داخل إطارها).</t>
+        </is>
+      </c>
+      <c r="L73" s="6" t="inlineStr">
+        <is>
+          <t>فحص بمتصفح محمول بتاريخ 11 أكتوبر 2026.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="8" t="n">
@@ -4645,37 +4653,37 @@
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>برامج الدراسات العليا</t>
+          <t>متطلبات تخصصات الحاسب والهندسة</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t>https://www.pmu.edu.sa/admission/admission_graduate_degree_programs</t>
+          <t>https://pmu.edu.sa/admission/admissions_requirements_cs_eng_majors</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>روابط «Application Form» لبرامج دكتوراه الهندسة الميكانيكية وماجستير الهندسة المدنية والكهربائية والتصميم الداخلي</t>
+          <t>صفحة متطلبات تخصصات الحاسب والهندسة – المقدمة وAdmission Criteria (مقارنةً بصفحة SAT وصفحة القبول في البكالوريوس وصفحة الطلاب الدوليين)</t>
         </is>
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>[برامج الدراسات العليا] "Application Form" → application_form_gr | [نموذج التقديم العام] "minimum scores of 6.5 overall and 5.5 in each skill" | [صفحات متطلبات البرامج الأربعة] "minimum scores of 6.0 overall and 5.5 in each skill"</t>
+          <t>[الحاسب والهندسة] These majors are Architecture, Computer Science, Computer Engineering, Software Engineering … to Computer Science or Engineering majors | [SAT] Software Engineering, Artificial Intelligence | [القبول في البكالوريوس] Computer Science and Engineering Majors Admission Requirements | [الطلاب الدوليون] Non-Engineering Majors:</t>
         </is>
       </c>
       <c r="F74" s="9" t="inlineStr">
         <is>
-          <t>دقة المعلومات</t>
+          <t>الاتساق</t>
         </is>
       </c>
       <c r="G74" s="9" t="inlineStr">
         <is>
-          <t>تعارض في متطلب اللغة</t>
+          <t>قائمة تخصصات غير موحدة</t>
         </is>
       </c>
       <c r="H74" s="9" t="inlineStr">
         <is>
-          <t>تحيل روابط «Application Form» لأربعة برامج (دكتوراه الهندسة الميكانيكية، وماجستير الهندسة المدنية، وماجستير الهندسة الكهربائية، وماجستير التصميم الداخلي) إلى نموذج تقديم عام يشترط IELTS بدرجة 6.5، في حين تشترط صفحات متطلبات هذه البرامج نفسها درجة 6.0.</t>
+          <t>لا تتضمن قائمة التخصصات ذات المتطلبات الخاصة في صفحة متطلبات الحاسب والهندسة تخصص الذكاء الاصطناعي، بينما تتضمنه صفحة SAT وصفحة التقديم. كما تقتصر جملة معايير القبول وعنوان الرابط في صفحة البكالوريوس على «الحاسب والهندسة» رغم شمول العمارة، وتقسم صفحة الطلاب الدوليين التخصصات إلى «غير هندسية» و«حاسب وهندسة» دون تعدادها.</t>
         </is>
       </c>
       <c r="I74" s="8" t="inlineStr">
@@ -4685,19 +4693,15 @@
       </c>
       <c r="J74" s="8" t="inlineStr">
         <is>
-          <t>عالية</t>
+          <t>متوسطة</t>
         </is>
       </c>
       <c r="K74" s="9" t="inlineStr">
         <is>
-          <t>ربط كل برنامج بنموذج تقديم خاص به، أو توحيد درجة IELTS في النموذج العام وفق قرار عمادة الدراسات العليا.</t>
-        </is>
-      </c>
-      <c r="L74" s="9" t="inlineStr">
-        <is>
-          <t>تحقق مباشر من روابط الصفحة بتاريخ 11 أكتوبر 2026.</t>
-        </is>
-      </c>
+          <t>اعتماد قائمة نهائية واحدة بالتخصصات ذات المتطلبات الخاصة من مكتب القبول، وتوحيدها وتسمية المجموعة في صفحة متطلبات الحاسب والهندسة وصفحة SAT وصفحة التقديم وصفحة البكالوريوس وصفحة الطلاب الدوليين، مع تعداد التخصصات في كل مجموعة.</t>
+        </is>
+      </c>
+      <c r="L74" s="9" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n">
@@ -4705,37 +4709,37 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>برامج الدراسات العليا</t>
+          <t>متطلبات تخصصات الحاسب والهندسة</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/admission_graduate_degree_programs</t>
+          <t>https://pmu.edu.sa/admission/admissions_requirements_cs_eng_majors</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>صفحة برامج الدراسات العليا: قائمة البرامج؛ وصفحة مكتب القبول (الرئيسية): رابط «Admissions to the EMGMS Program»؛ والقائمة الجانبية لصفحات الدراسات العليا</t>
+          <t>صفحة متطلبات تخصصات الحاسب والهندسة – الحاشية أسفل جدول المتطلبات</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>[Admissions Office page] Admissions to the EMGMS Program … [Graduate Admissions] Admissions to the Master of Arts (MA) in International Business Law Program … [Sidebar] Apply for EMBA … Apply for MBA … Apply for MSHD … Apply for MSME</t>
+          <t>[الحاسب والهندسة] *Students with lower marks may apply, however, the minimum weighted total, defined by the Admissions Office, should be met.</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
         <is>
-          <t>تنظيمي</t>
+          <t>دقة المعلومات</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>برنامج دون مسار تقديم</t>
+          <t>حد أدنى غير منشور</t>
         </is>
       </c>
       <c r="H75" s="6" t="inlineStr">
         <is>
-          <t>يظهر برنامج ماجستير الإدارة الهندسية في صفحة مكتب القبول الرئيسية وله صفحة متطلبات ورسوم منشورة، لكنه غير مدرج في صفحة برامج الدراسات العليا، ولا يوجد له رابط تقديم أو نموذج طلب.</t>
+          <t>تشترط الصفحة استيفاء حد أدنى للنسبة الموزونة «يحدده مكتب القبول» دون ذكر قيمته، في حين تنشر صفحة كلية الطب حدها الأدنى.</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr">
@@ -4750,12 +4754,12 @@
       </c>
       <c r="K75" s="6" t="inlineStr">
         <is>
-          <t>تحديد حالة طرح البرنامج من قِبل عمادة الدراسات العليا: فإن كان مطروحًا يُضاف إلى صفحة برامج الدراسات العليا مع رابط تقديم، وإلا يُزال من صفحة مكتب القبول ومن جدول الرسوم.</t>
+          <t>يقرر مكتب القبول نشر الحد الأدنى للنسبة الموزونة لكل مجموعة تخصصات، أو بيان آلية تحديده، وتوحيد ذلك في صفحات البكالوريوس.</t>
         </is>
       </c>
       <c r="L75" s="6" t="inlineStr">
         <is>
-          <t>الجزء من الملاحظة المتعلق ببرنامج ماجستير الهندسة في الابتكار والاستدامة وريادة الأعمال مدرج في صف البرامج المسعّرة دون صفحة قبول.</t>
+          <t>قرار نشر الحد الأدنى يعود إلى الجهة المالكة لسياسة القبول.</t>
         </is>
       </c>
     </row>
@@ -4765,22 +4769,22 @@
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>برامج الدراسات العليا</t>
+          <t>متطلبات تخصصات الحاسب والهندسة</t>
         </is>
       </c>
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/admission_graduate_degree_programs</t>
+          <t>https://pmu.edu.sa/admission/admissions_requirements_cs_eng_majors</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>صفحة برامج الدراسات العليا: روابط «Application Form» و«Admissions Requirements» لبرامج دكتوراه الهندسة الميكانيكية وماجستير الهندسة المدنية والكهربائية والتصميم الداخلي والقانون التجاري الدولي؛ وصفحة مكتب القبول: روابط «Home» و«Tuition &amp; Fees»</t>
+          <t>صفحة متطلبات تخصصات الحاسب والهندسة – How to Apply (والنص نفسه في قسمي Transfer Students وVisitor Students بصفحة الطلاب الدوليين)</t>
         </is>
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t>Admissions to the Doctorate in Mechanical Engineering Program … Application Form … Admissions Requirements … Admissions to the Master of Science in Civil Engineering (MSCE) Program … Application Form … Admissions Requirements … [Admissions Office page] Home … Tuition &amp; Fees</t>
+          <t>[الحاسب والهندسة, الطلاب الدوليون] Submit original IELTS (Academic version) certificate or equivalent TOEFL iBT with acceptable scores (if available) or For direct entry, submit original IELTS (Academic version) certificate with minimum scores of 6.0 overall and 5.5 in writing</t>
         </is>
       </c>
       <c r="F76" s="9" t="inlineStr">
@@ -4790,34 +4794,30 @@
       </c>
       <c r="G76" s="9" t="inlineStr">
         <is>
-          <t>روابط بعناوين غير مميزة</t>
+          <t>صياغة ملتبسة</t>
         </is>
       </c>
       <c r="H76" s="9" t="inlineStr">
         <is>
-          <t>تتكرر عناوين روابط «Application Form» و«Admissions Requirements» دون اسم البرنامج لخمسة برامج، وتقود روابط التقديم لدكتوراه الهندسة الميكانيكية وماجستير الهندسة المدنية والكهربائية والتصميم الداخلي إلى صفحة تقديم عامة واحدة لا تسمي البرنامج، كما تتكرر عناوين «Home» و«Tuition &amp; Fees» في صفحة مكتب القبول مع اختلاف وجهاتها.</t>
+          <t>يتوزع شرط اختبار اللغة الإنجليزية على بندين متداخلين يربطهما «or» في نهاية الأول مع حرف كبير زائد في «For»، فلا يتضح الفرق بين خيار تقديم الدرجة لتحديد المستوى وخيار القبول المباشر.</t>
         </is>
       </c>
       <c r="I76" s="8" t="inlineStr">
         <is>
-          <t>توصية تحسين</t>
+          <t>تصحيح مطلوب</t>
         </is>
       </c>
       <c r="J76" s="8" t="inlineStr">
         <is>
-          <t>متوسطة</t>
+          <t>منخفضة</t>
         </is>
       </c>
       <c r="K76" s="9" t="inlineStr">
         <is>
-          <t>إضافة اسم البرنامج إلى كل رابط (مثل: Application Form for MSCE)، وإنشاء صفحة تقديم لكل برنامج أو جعل الصفحة العامة تسمي البرامج التي تخدمها، واستخدام عناوين فريدة للروابط المختلفة الوجهة.</t>
-        </is>
-      </c>
-      <c r="L76" s="9" t="inlineStr">
-        <is>
-          <t>رُفعت الأولوية إلى متوسطة لأن إحدى الملاحظتين المدمجتين مصنفة متوسطة.</t>
-        </is>
-      </c>
+          <t>دمج الشرط في بند واحد واضح يفصل بين الخيارين: (أ) دون شهادة يُحدد موعد لاختبار تحديد المستوى، (ب) للقبول المباشر تُقدم شهادة IELTS أو TOEFL iBT بالحد الأدنى المعتمد.</t>
+        </is>
+      </c>
+      <c r="L76" s="9" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="5" t="n">
@@ -4830,50 +4830,54 @@
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/admission_graduate_degree_programs</t>
+          <t>https://www.pmu.edu.sa/admission/admission_graduate_degree_programs</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>صفحة برامج الدراسات العليا: عناوين البرامج وروابطها</t>
+          <t>روابط «Application Form» لبرامج دكتوراه الهندسة الميكانيكية وماجستير الهندسة المدنية والكهربائية والتصميم الداخلي</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>Admissions to the PhD in Business Administration … Admission to the Executive MBA Program … Admission to the MBA … [MIBL page heading] MIBL ADMISSSIONS REQUIREMENTS … [MIBL page URL] admissions_requirements_milbl_gdp</t>
+          <t>[برامج الدراسات العليا] "Application Form" → application_form_gr | [نموذج التقديم العام] "minimum scores of 6.5 overall and 5.5 in each skill" | [صفحات متطلبات البرامج الأربعة] "minimum scores of 6.0 overall and 5.5 in each skill"</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>الاتساق</t>
+          <t>دقة المعلومات</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>عدم توحيد العناوين والاختصارات</t>
+          <t>تعارض في متطلب اللغة</t>
         </is>
       </c>
       <c r="H77" s="6" t="inlineStr">
         <is>
-          <t>تتناوب عناوين البرامج بين «Admission» و«Admissions» وتتضمن كلمة «Program» في بعضها دون بعض، ويُختصر ماجستير القانون التجاري الدولي إلى «MIBL» في العناوين بينما يرد «MILBL» في عناوين صفحاته.</t>
+          <t>تحيل روابط «Application Form» لأربعة برامج (دكتوراه الهندسة الميكانيكية، وماجستير الهندسة المدنية، وماجستير الهندسة الكهربائية، وماجستير التصميم الداخلي) إلى نموذج تقديم عام يشترط IELTS بدرجة 6.5، في حين تشترط صفحات متطلبات هذه البرامج نفسها درجة 6.0.</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>توصية تحسين</t>
+          <t>تصحيح مطلوب</t>
         </is>
       </c>
       <c r="J77" s="5" t="inlineStr">
         <is>
-          <t>منخفضة</t>
+          <t>عالية</t>
         </is>
       </c>
       <c r="K77" s="6" t="inlineStr">
         <is>
-          <t>توحيد صيغة العناوين (مثل: Admissions to the [Programme Name] Program) وتوحيد الاختصار في التسميات، وتعديل العناوين الإلكترونية حيثما أمكن مع إعادة توجيه العناوين القديمة.</t>
-        </is>
-      </c>
-      <c r="L77" s="6" t="inlineStr"/>
+          <t>ربط كل برنامج بنموذج تقديم خاص به، أو توحيد درجة IELTS في النموذج العام وفق قرار عمادة الدراسات العليا.</t>
+        </is>
+      </c>
+      <c r="L77" s="6" t="inlineStr">
+        <is>
+          <t>تحقق مباشر من روابط الصفحة بتاريخ 11 أكتوبر 2026.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="8" t="n">
@@ -4881,42 +4885,42 @@
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>دكتوراه الهندسة الميكانيكية</t>
+          <t>برامج الدراسات العليا</t>
         </is>
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/application_form_deme_gdp</t>
+          <t>https://pmu.edu.sa/admission/admission_graduate_degree_programs</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>قسم «Educational Background» في صفحات متطلبات دكتوراه الهندسة الميكانيكية، وماجستير إدارة الأعمال التنفيذي، وماجستير إدارة الأعمال، وماجستير الهندسة الميكانيكية والكهربائية والمدنية، وماجستير التصميم الداخلي، وماجستير القانون التجاري الدولي</t>
+          <t>صفحة برامج الدراسات العليا: قائمة البرامج؛ وصفحة مكتب القبول (الرئيسية): رابط «Admissions to the EMGMS Program»؛ والقائمة الجانبية لصفحات الدراسات العليا</t>
         </is>
       </c>
       <c r="E78" s="10" t="inlineStr">
         <is>
-          <t>[PhD ME] A minimum cumulative GPA of 3.00 out of 4.00 or equivalent (Very Good) … [EMBA, MBA, MSME, MSEE, MSCE, MSID] … 2.50 out of 4.00 or equivalent (Very Good) in Bachelor’s Degree … [MIBL] A minimum (Very Good) in Bachelor’s Degree</t>
+          <t>[Admissions Office page] Admissions to the EMGMS Program … [Graduate Admissions] Admissions to the Master of Arts (MA) in International Business Law Program … [Sidebar] Apply for EMBA … Apply for MBA … Apply for MSHD … Apply for MSME</t>
         </is>
       </c>
       <c r="F78" s="9" t="inlineStr">
         <is>
-          <t>الاتساق</t>
+          <t>تنظيمي</t>
         </is>
       </c>
       <c r="G78" s="9" t="inlineStr">
         <is>
-          <t>تعريف متضارب للتقدير</t>
+          <t>برنامج دون مسار تقديم</t>
         </is>
       </c>
       <c r="H78" s="9" t="inlineStr">
         <is>
-          <t>يُقرن تقدير «Very Good» بمعدل 3.00 من 4.00 في صفحة دكتوراه الهندسة الميكانيكية، وبمعدل 2.50 من 4.00 في صفحات ماجستير إدارة الأعمال التنفيذي وماجستير إدارة الأعمال وماجستير الهندسة الميكانيكية والكهربائية والمدنية والتصميم الداخلي، بينما تكتفي صفحة ماجستير القانون التجاري الدولي بعبارة «Very Good» دون رقم.</t>
+          <t>يظهر برنامج ماجستير الإدارة الهندسية في صفحة مكتب القبول الرئيسية وله صفحة متطلبات ورسوم منشورة، لكنه غير مدرج في صفحة برامج الدراسات العليا، ولا يوجد له رابط تقديم أو نموذج طلب.</t>
         </is>
       </c>
       <c r="I78" s="8" t="inlineStr">
         <is>
-          <t>تصحيح مطلوب</t>
+          <t>متابعة وتحقق</t>
         </is>
       </c>
       <c r="J78" s="8" t="inlineStr">
@@ -4926,10 +4930,14 @@
       </c>
       <c r="K78" s="9" t="inlineStr">
         <is>
-          <t>الإبقاء على الحد الأدنى الخاص بكل برنامج مع ذكره رقميًا فقط أو تعريف التقديرات تعريفًا موحدًا، وتحديد المعدل المطلوب رقميًا لماجستير القانون التجاري الدولي بعد اعتماده من عمادة الدراسات العليا.</t>
-        </is>
-      </c>
-      <c r="L78" s="9" t="inlineStr"/>
+          <t>تحديد حالة طرح البرنامج من قِبل عمادة الدراسات العليا: فإن كان مطروحًا يُضاف إلى صفحة برامج الدراسات العليا مع رابط تقديم، وإلا يُزال من صفحة مكتب القبول ومن جدول الرسوم.</t>
+        </is>
+      </c>
+      <c r="L78" s="9" t="inlineStr">
+        <is>
+          <t>الجزء من الملاحظة المتعلق ببرنامج ماجستير الهندسة في الابتكار والاستدامة وريادة الأعمال مدرج في صف البرامج المسعّرة دون صفحة قبول.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n">
@@ -4937,42 +4945,42 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>دكتوراه الهندسة الميكانيكية</t>
+          <t>برامج الدراسات العليا</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/application_form_deme_gdp</t>
+          <t>https://pmu.edu.sa/admission/admission_graduate_degree_programs</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>عنوان الصفحة في المتصفح (title) لصفحة متطلبات دكتوراه الهندسة الميكانيكية</t>
+          <t>صفحة برامج الدراسات العليا: روابط «Application Form» و«Admissions Requirements» لبرامج دكتوراه الهندسة الميكانيكية وماجستير الهندسة المدنية والكهربائية والتصميم الداخلي والقانون التجاري الدولي؛ وصفحة مكتب القبول: روابط «Home» و«Tuition &amp; Fees»</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>Application Form for MSDH :: Graduate Degree Programs :: Admissions Office ::Study @ PMU</t>
+          <t>Admissions to the Doctorate in Mechanical Engineering Program … Application Form … Admissions Requirements … Admissions to the Master of Science in Civil Engineering (MSCE) Program … Application Form … Admissions Requirements … [Admissions Office page] Home … Tuition &amp; Fees</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>وظيفي وتقني</t>
+          <t>تجربة المستخدم</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>عنوان صفحة خاطئ</t>
+          <t>روابط بعناوين غير مميزة</t>
         </is>
       </c>
       <c r="H79" s="6" t="inlineStr">
         <is>
-          <t>يحمل عنوان صفحة متطلبات دكتوراه الهندسة الميكانيكية في المتصفح اسم «Application Form for MSDH»، وهو يشير إلى نوع صفحة مختلف وإلى اختصار برنامج آخر مكتوب خطأً، مما يضلل المتقدم ونتائج محركات البحث.</t>
+          <t>تتكرر عناوين روابط «Application Form» و«Admissions Requirements» دون اسم البرنامج لخمسة برامج، وتقود روابط التقديم لدكتوراه الهندسة الميكانيكية وماجستير الهندسة المدنية والكهربائية والتصميم الداخلي إلى صفحة تقديم عامة واحدة لا تسمي البرنامج، كما تتكرر عناوين «Home» و«Tuition &amp; Fees» في صفحة مكتب القبول مع اختلاف وجهاتها.</t>
         </is>
       </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
-          <t>تصحيح مطلوب</t>
+          <t>توصية تحسين</t>
         </is>
       </c>
       <c r="J79" s="5" t="inlineStr">
@@ -4982,12 +4990,12 @@
       </c>
       <c r="K79" s="6" t="inlineStr">
         <is>
-          <t>تغيير العنوان إلى «PhD in Mechanical Engineering Admissions Requirements :: Graduate Programs :: Admissions Office».</t>
+          <t>إضافة اسم البرنامج إلى كل رابط (مثل: Application Form for MSCE)، وإنشاء صفحة تقديم لكل برنامج أو جعل الصفحة العامة تسمي البرامج التي تخدمها، واستخدام عناوين فريدة للروابط المختلفة الوجهة.</t>
         </is>
       </c>
       <c r="L79" s="6" t="inlineStr">
         <is>
-          <t>إحدى الملاحظتين المدمجتين مصنفة متوسطة والأخرى منخفضة، واعتُمدت المتوسطة لأثر العنوان على نتائج البحث. ولوحظ أن صفحة نموذج التقديم لماجستير التنمية البشرية تحمل العنوان نفسه «Application Form for MSDH» (والصحيح MSHD).</t>
+          <t>رُفعت الأولوية إلى متوسطة لأن إحدى الملاحظتين المدمجتين مصنفة متوسطة.</t>
         </is>
       </c>
     </row>
@@ -4997,37 +5005,37 @@
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>دكتوراه الهندسة الميكانيكية</t>
+          <t>برامج الدراسات العليا</t>
         </is>
       </c>
       <c r="C80" s="10" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/application_form_deme_gdp</t>
+          <t>https://pmu.edu.sa/admission/admission_graduate_degree_programs</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>المحتوى الرئيس لصفحات متطلبات دكتوراه الهندسة الميكانيكية، ودكتوراه إدارة الأعمال، وماجستير التنمية البشرية، وماجستير الهندسة الكهربائية والمدنية، وماجستير التصميم الداخلي؛ مقارنةً بجدول صفحة رسوم الدراسات العليا</t>
+          <t>صفحة برامج الدراسات العليا: عناوين البرامج وروابطها</t>
         </is>
       </c>
       <c r="E80" s="10" t="inlineStr">
         <is>
-          <t>[Fees page] Doctoral program in Mechanical Engineering (72) … Doctor of Philosophy (Ph.D.) In Business Administration (72) … Master of Science in Electrical Engineering (30) … Master of Science in Civil Engineering (30) … Master of Science in Interior Design (30)</t>
+          <t>Admissions to the PhD in Business Administration … Admission to the Executive MBA Program … Admission to the MBA … [MIBL page heading] MIBL ADMISSSIONS REQUIREMENTS … [MIBL page URL] admissions_requirements_milbl_gdp</t>
         </is>
       </c>
       <c r="F80" s="9" t="inlineStr">
         <is>
-          <t>دقة المعلومات</t>
+          <t>الاتساق</t>
         </is>
       </c>
       <c r="G80" s="9" t="inlineStr">
         <is>
-          <t>معلومات أساسية ناقصة</t>
+          <t>عدم توحيد العناوين والاختصارات</t>
         </is>
       </c>
       <c r="H80" s="9" t="inlineStr">
         <is>
-          <t>لا تذكر صفحات متطلبات هذه البرامج عدد الساعات المعتمدة ولا مدة الدراسة ولا نمطها، ولا تتضمن رابط تقديم ضمن المحتوى، مع أن صفحة الرسوم تذكر الساعات المعتمدة لمعظمها (72 للدكتوراه و30 لبرامج الماجستير الهندسية والتصميم الداخلي)، ولا يذكر جدول الرسوم ساعات ماجستير التنمية البشرية. كما لا تتضمن صفحة ماجستير التصميم الداخلي أي بيان عن الخبرة العملية.</t>
+          <t>تتناوب عناوين البرامج بين «Admission» و«Admissions» وتتضمن كلمة «Program» في بعضها دون بعض، ويُختصر ماجستير القانون التجاري الدولي إلى «MIBL» في العناوين بينما يرد «MILBL» في عناوين صفحاته.</t>
         </is>
       </c>
       <c r="I80" s="8" t="inlineStr">
@@ -5037,12 +5045,12 @@
       </c>
       <c r="J80" s="8" t="inlineStr">
         <is>
-          <t>متوسطة</t>
+          <t>منخفضة</t>
         </is>
       </c>
       <c r="K80" s="9" t="inlineStr">
         <is>
-          <t>إضافة عدد الساعات المعتمدة ومدة الدراسة ونمطها ورابط التقديم إلى كل صفحة بعد تأكيدها من الكليات المعنية، وإضافة ساعات ماجستير التنمية البشرية إلى جدول الرسوم، وبيان متطلب الخبرة لماجستير التصميم الداخلي.</t>
+          <t>توحيد صيغة العناوين (مثل: Admissions to the [Programme Name] Program) وتوحيد الاختصار في التسميات، وتعديل العناوين الإلكترونية حيثما أمكن مع إعادة توجيه العناوين القديمة.</t>
         </is>
       </c>
       <c r="L80" s="9" t="inlineStr"/>
@@ -5063,27 +5071,27 @@
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>صفحات متطلبات برامج الدراسات العليا – بند المقابلة الشخصية (دكتوراه الهندسة الميكانيكية، دكتوراه إدارة الأعمال، ماجستير الهندسة الميكانيكية والكهربائية والمدنية والتصميم الداخلي وغيرها)</t>
+          <t>قسم «Educational Background» في صفحات متطلبات دكتوراه الهندسة الميكانيكية، وماجستير إدارة الأعمال التنفيذي، وماجستير إدارة الأعمال، وماجستير الهندسة الميكانيكية والكهربائية والمدنية، وماجستير التصميم الداخلي، وماجستير القانون التجاري الدولي</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>Candidates will be personally interviewed by committee of the program administrators and faculty</t>
+          <t>[PhD ME] A minimum cumulative GPA of 3.00 out of 4.00 or equivalent (Very Good) … [EMBA, MBA, MSME, MSEE, MSCE, MSID] … 2.50 out of 4.00 or equivalent (Very Good) in Bachelor’s Degree … [MIBL] A minimum (Very Good) in Bachelor’s Degree</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>لغوي ونحوي</t>
+          <t>الاتساق</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>خطأ نحوي متكرر</t>
+          <t>تعريف متضارب للتقدير</t>
         </is>
       </c>
       <c r="H81" s="6" t="inlineStr">
         <is>
-          <t>تفتقد جملة المقابلة أداة التنكير "a" قبل "committee"، وتتكرر بالصياغة نفسها في عدة صفحات للدراسات العليا.</t>
+          <t>يُقرن تقدير «Very Good» بمعدل 3.00 من 4.00 في صفحة دكتوراه الهندسة الميكانيكية، وبمعدل 2.50 من 4.00 في صفحات ماجستير إدارة الأعمال التنفيذي وماجستير إدارة الأعمال وماجستير الهندسة الميكانيكية والكهربائية والمدنية والتصميم الداخلي، بينما تكتفي صفحة ماجستير القانون التجاري الدولي بعبارة «Very Good» دون رقم.</t>
         </is>
       </c>
       <c r="I81" s="5" t="inlineStr">
@@ -5093,12 +5101,12 @@
       </c>
       <c r="J81" s="5" t="inlineStr">
         <is>
-          <t>منخفضة</t>
+          <t>متوسطة</t>
         </is>
       </c>
       <c r="K81" s="6" t="inlineStr">
         <is>
-          <t>التصحيح إلى "Candidates will be interviewed by a committee of program administrators and faculty." في جميع الصفحات.</t>
+          <t>الإبقاء على الحد الأدنى الخاص بكل برنامج مع ذكره رقميًا فقط أو تعريف التقديرات تعريفًا موحدًا، وتحديد المعدل المطلوب رقميًا لماجستير القانون التجاري الدولي بعد اعتماده من عمادة الدراسات العليا.</t>
         </is>
       </c>
       <c r="L81" s="6" t="inlineStr"/>
@@ -5119,27 +5127,27 @@
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>العنوان الرئيس ومسار التنقل في صفحات متطلبات دكتوراه الهندسة الميكانيكية، وماجستير الهندسة الميكانيكية والكهربائية والمدنية، وماجستير التصميم الداخلي، وماجستير القانون التجاري الدولي (وعنوان المتصفح في صفحات الهندسة الكهربائية والمدنية والتصميم الداخلي)</t>
+          <t>عنوان الصفحة في المتصفح (title) لصفحة متطلبات دكتوراه الهندسة الميكانيكية</t>
         </is>
       </c>
       <c r="E82" s="10" t="inlineStr">
         <is>
-          <t>PHD IN MECHANICAL ENGINEERING ADMISSSIONS REQUIREMENTS … MSME ADMISSSIONS REQUIREMENTS … MSEE ADMISSSIONS REQUIREMENTS … MSCE ADMISSSIONS REQUIREMENTS … MSID ADMISSSIONS REQUIREMENTS … MIBL ADMISSSIONS REQUIREMENTS</t>
+          <t>Application Form for MSDH :: Graduate Degree Programs :: Admissions Office ::Study @ PMU</t>
         </is>
       </c>
       <c r="F82" s="9" t="inlineStr">
         <is>
-          <t>لغوي ونحوي</t>
+          <t>وظيفي وتقني</t>
         </is>
       </c>
       <c r="G82" s="9" t="inlineStr">
         <is>
-          <t>خطأ إملائي</t>
+          <t>عنوان صفحة خاطئ</t>
         </is>
       </c>
       <c r="H82" s="9" t="inlineStr">
         <is>
-          <t>كُتبت كلمة «ADMISSIONS» بثلاثة أحرف S في عناوين ست صفحات من صفحات الدراسات العليا ومسارات التنقل فيها، وفي عنوان المتصفح لثلاث منها.</t>
+          <t>يحمل عنوان صفحة متطلبات دكتوراه الهندسة الميكانيكية في المتصفح اسم «Application Form for MSDH»، وهو يشير إلى نوع صفحة مختلف وإلى اختصار برنامج آخر مكتوب خطأً، مما يضلل المتقدم ونتائج محركات البحث.</t>
         </is>
       </c>
       <c r="I82" s="8" t="inlineStr">
@@ -5149,15 +5157,19 @@
       </c>
       <c r="J82" s="8" t="inlineStr">
         <is>
-          <t>منخفضة</t>
+          <t>متوسطة</t>
         </is>
       </c>
       <c r="K82" s="9" t="inlineStr">
         <is>
-          <t>تصحيح الكلمة إلى «ADMISSIONS» في العناوين ومسارات التنقل وعناوين المتصفح في الصفحات الست.</t>
-        </is>
-      </c>
-      <c r="L82" s="9" t="inlineStr"/>
+          <t>تغيير العنوان إلى «PhD in Mechanical Engineering Admissions Requirements :: Graduate Programs :: Admissions Office».</t>
+        </is>
+      </c>
+      <c r="L82" s="9" t="inlineStr">
+        <is>
+          <t>إحدى الملاحظتين المدمجتين مصنفة متوسطة والأخرى منخفضة، واعتُمدت المتوسطة لأثر العنوان على نتائج البحث. ولوحظ أن صفحة نموذج التقديم لماجستير التنمية البشرية تحمل العنوان نفسه «Application Form for MSDH» (والصحيح MSHD).</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n">
@@ -5175,27 +5187,27 @@
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>صفحة متطلبات دكتوراه الهندسة الميكانيكية: الفقرة التعريفية وبند «Work experience»</t>
+          <t>المحتوى الرئيس لصفحات متطلبات دكتوراه الهندسة الميكانيكية، ودكتوراه إدارة الأعمال، وماجستير التنمية البشرية، وماجستير الهندسة الكهربائية والمدنية، وماجستير التصميم الداخلي؛ مقارنةً بجدول صفحة رسوم الدراسات العليا</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>widen the horizons of engineer professionals. The PhD program provides employees with the skills … Work experience: Successful candidates are preferred to have industrial experience.</t>
+          <t>[Fees page] Doctoral program in Mechanical Engineering (72) … Doctor of Philosophy (Ph.D.) In Business Administration (72) … Master of Science in Electrical Engineering (30) … Master of Science in Civil Engineering (30) … Master of Science in Interior Design (30)</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr">
         <is>
-          <t>لغوي ونحوي</t>
+          <t>دقة المعلومات</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>صياغة غير دقيقة</t>
+          <t>معلومات أساسية ناقصة</t>
         </is>
       </c>
       <c r="H83" s="6" t="inlineStr">
         <is>
-          <t>تستخدم الفقرة التعريفية عبارة «engineer professionals» بدلًا من «engineering professionals» وتفترض أن المتقدمين موظفون، ولا يوضح بند الخبرة العملية ما إذا كانت الخبرة الصناعية شرطًا أم ميزة مفضلة.</t>
+          <t>لا تذكر صفحات متطلبات هذه البرامج عدد الساعات المعتمدة ولا مدة الدراسة ولا نمطها، ولا تتضمن رابط تقديم ضمن المحتوى، مع أن صفحة الرسوم تذكر الساعات المعتمدة لمعظمها (72 للدكتوراه و30 لبرامج الماجستير الهندسية والتصميم الداخلي)، ولا يذكر جدول الرسوم ساعات ماجستير التنمية البشرية. كما لا تتضمن صفحة ماجستير التصميم الداخلي أي بيان عن الخبرة العملية.</t>
         </is>
       </c>
       <c r="I83" s="5" t="inlineStr">
@@ -5205,19 +5217,15 @@
       </c>
       <c r="J83" s="5" t="inlineStr">
         <is>
-          <t>منخفضة</t>
+          <t>متوسطة</t>
         </is>
       </c>
       <c r="K83" s="6" t="inlineStr">
         <is>
-          <t>تعديل العبارتين إلى «engineering professionals» و«provides participants with the skills»، وإعادة صياغة بند الخبرة إلى «Industrial experience is preferred but not required» أو النص على المتطلب صراحة.</t>
-        </is>
-      </c>
-      <c r="L83" s="6" t="inlineStr">
-        <is>
-          <t>ترد عبارة بند الخبرة نفسها في صفحتي ماجستير الهندسة الكهربائية والمدنية.</t>
-        </is>
-      </c>
+          <t>إضافة عدد الساعات المعتمدة ومدة الدراسة ونمطها ورابط التقديم إلى كل صفحة بعد تأكيدها من الكليات المعنية، وإضافة ساعات ماجستير التنمية البشرية إلى جدول الرسوم، وبيان متطلب الخبرة لماجستير التصميم الداخلي.</t>
+        </is>
+      </c>
+      <c r="L83" s="6" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="8" t="n">
@@ -5225,59 +5233,55 @@
       </c>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>دكتوراه إدارة الأعمال</t>
+          <t>دكتوراه الهندسة الميكانيكية</t>
         </is>
       </c>
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/admissions_requirements_phdba_gdp</t>
+          <t>https://pmu.edu.sa/admission/application_form_deme_gdp</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>صفحة متطلبات دكتوراه إدارة الأعمال: الفقرة التعريفية</t>
+          <t>صفحات متطلبات برامج الدراسات العليا – بند المقابلة الشخصية (دكتوراه الهندسة الميكانيكية، دكتوراه إدارة الأعمال، ماجستير الهندسة الميكانيكية والكهربائية والمدنية والتصميم الداخلي وغيرها)</t>
         </is>
       </c>
       <c r="E84" s="10" t="inlineStr">
         <is>
-          <t>The Ph.D. program is internationally accredited by AACSB as top 6% of business schools worldwide.</t>
+          <t>Candidates will be personally interviewed by committee of the program administrators and faculty</t>
         </is>
       </c>
       <c r="F84" s="9" t="inlineStr">
         <is>
-          <t>دقة المعلومات</t>
+          <t>لغوي ونحوي</t>
         </is>
       </c>
       <c r="G84" s="9" t="inlineStr">
         <is>
-          <t>ادعاء اعتماد غير موثق</t>
+          <t>خطأ نحوي متكرر</t>
         </is>
       </c>
       <c r="H84" s="9" t="inlineStr">
         <is>
-          <t>تنسب الصفحة اعتماد AACSB إلى برنامج الدكتوراه بوصفه برنامجًا، مع أن الاعتماد يُمنح للكلية، وتذكر نسبة «أعلى 6%» دون مرجع.</t>
+          <t>تفتقد جملة المقابلة أداة التنكير "a" قبل "committee"، وتتكرر بالصياغة نفسها في عدة صفحات للدراسات العليا.</t>
         </is>
       </c>
       <c r="I84" s="8" t="inlineStr">
         <is>
-          <t>متابعة وتحقق</t>
+          <t>تصحيح مطلوب</t>
         </is>
       </c>
       <c r="J84" s="8" t="inlineStr">
         <is>
-          <t>متوسطة</t>
+          <t>منخفضة</t>
         </is>
       </c>
       <c r="K84" s="9" t="inlineStr">
         <is>
-          <t>التحقق من حالة الاعتماد مع كلية إدارة الأعمال، ثم إعادة الصياغة بما يطابق الوضع الفعلي (مثل: «PMU’s College of Business is AACSB-accredited») مع ذكر مرجع لنسبة 6% أو حذفها.</t>
-        </is>
-      </c>
-      <c r="L84" s="9" t="inlineStr">
-        <is>
-          <t>الملاحظة الرئيسة المتعلقة بهذه الصفحة (المدمجة في صف شروط الأهلية) تشير إلى أن المصادر المتاحة تؤكد العضوية لا الاعتماد الكامل؛ لا يمكن تأكيد ذلك من نص الصفحة وحده. رُفعت الأولوية إلى متوسطة لأثر الادعاء على سمعة الجامعة.</t>
-        </is>
-      </c>
+          <t>التصحيح إلى "Candidates will be interviewed by a committee of program administrators and faculty." في جميع الصفحات.</t>
+        </is>
+      </c>
+      <c r="L84" s="9" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="5" t="n">
@@ -5285,37 +5289,37 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>دكتوراه إدارة الأعمال</t>
+          <t>دكتوراه الهندسة الميكانيكية</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/admissions_requirements_phdba_gdp</t>
+          <t>https://pmu.edu.sa/admission/application_form_deme_gdp</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>صفحة متطلبات دكتوراه إدارة الأعمال: قسم «Educational Background»</t>
+          <t>العنوان الرئيس ومسار التنقل في صفحات متطلبات دكتوراه الهندسة الميكانيكية، وماجستير الهندسة الميكانيكية والكهربائية والمدنية، وماجستير التصميم الداخلي، وماجستير القانون التجاري الدولي (وعنوان المتصفح في صفحات الهندسة الكهربائية والمدنية والتصميم الداخلي)</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>Otherwise, if the master degree is not from another discipline they must successfully attend and complete with minimum GPA 2.80 12 credit hours of MBA … Applicants must have a minimum cumulative GPA of 3.00 (scale is 4.00 = "A”) or they must have a minimum cumulative GPA of 3.20</t>
+          <t>PHD IN MECHANICAL ENGINEERING ADMISSSIONS REQUIREMENTS … MSME ADMISSSIONS REQUIREMENTS … MSEE ADMISSSIONS REQUIREMENTS … MSCE ADMISSSIONS REQUIREMENTS … MSID ADMISSSIONS REQUIREMENTS … MIBL ADMISSSIONS REQUIREMENTS</t>
         </is>
       </c>
       <c r="F85" s="6" t="inlineStr">
         <is>
-          <t>دقة المعلومات</t>
+          <t>لغوي ونحوي</t>
         </is>
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>شرط أهلية ملتبس</t>
+          <t>خطأ إملائي</t>
         </is>
       </c>
       <c r="H85" s="6" t="inlineStr">
         <is>
-          <t>تتضمن جملة الأهلية نفيًا مزدوجًا («not from another discipline») يعكس المعنى المقصود، وتذكر ثلاثة حدود للمعدل (2.80 و3.00 و3.20) دون بيان الحالة التي ينطبق عليها كل منها.</t>
+          <t>كُتبت كلمة «ADMISSIONS» بثلاثة أحرف S في عناوين ست صفحات من صفحات الدراسات العليا ومسارات التنقل فيها، وفي عنوان المتصفح لثلاث منها.</t>
         </is>
       </c>
       <c r="I85" s="5" t="inlineStr">
@@ -5325,19 +5329,15 @@
       </c>
       <c r="J85" s="5" t="inlineStr">
         <is>
-          <t>متوسطة</t>
+          <t>منخفضة</t>
         </is>
       </c>
       <c r="K85" s="6" t="inlineStr">
         <is>
-          <t>إعادة صياغة الشروط في بنود منفصلة واضحة تحدد لكل حالة (تخصص الماجستير، ومرحلة الدراسة) المعدل المطلوب، بعد اعتمادها من عمادة الدراسات العليا.</t>
-        </is>
-      </c>
-      <c r="L85" s="6" t="inlineStr">
-        <is>
-          <t>الشق الثاني من إحدى الملاحظتين المدمجتين (ادعاء اعتماد AACSB) معالج في صف مستقل.</t>
-        </is>
-      </c>
+          <t>تصحيح الكلمة إلى «ADMISSIONS» في العناوين ومسارات التنقل وعناوين المتصفح في الصفحات الست.</t>
+        </is>
+      </c>
+      <c r="L85" s="6" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="8" t="n">
@@ -5345,22 +5345,22 @@
       </c>
       <c r="B86" s="9" t="inlineStr">
         <is>
-          <t>دكتوراه إدارة الأعمال</t>
+          <t>دكتوراه الهندسة الميكانيكية</t>
         </is>
       </c>
       <c r="C86" s="10" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/admissions_requirements_phdba_gdp</t>
+          <t>https://pmu.edu.sa/admission/application_form_deme_gdp</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>صفحة متطلبات دكتوراه إدارة الأعمال: الفقرة التعريفية وقسم «Educational Background»</t>
+          <t>صفحة متطلبات دكتوراه الهندسة الميكانيكية: الفقرة التعريفية وبند «Work experience»</t>
         </is>
       </c>
       <c r="E86" s="10" t="inlineStr">
         <is>
-          <t>Doctor of Philosophy (Ph.D.) in Business Administration program is to develop scholars … (scale is 4.00 = "A”)</t>
+          <t>widen the horizons of engineer professionals. The PhD program provides employees with the skills … Work experience: Successful candidates are preferred to have industrial experience.</t>
         </is>
       </c>
       <c r="F86" s="9" t="inlineStr">
@@ -5370,17 +5370,17 @@
       </c>
       <c r="G86" s="9" t="inlineStr">
         <is>
-          <t>خطأ نحوي وترقيمي</t>
+          <t>صياغة غير دقيقة</t>
         </is>
       </c>
       <c r="H86" s="9" t="inlineStr">
         <is>
-          <t>الجملة الافتتاحية غير سليمة نحويًا (تنقصها أداة التعريف وفعل مناسب)، وتستخدم ملاحظة سلّم المعدل علامتي تنصيص غير متطابقتين.</t>
+          <t>تستخدم الفقرة التعريفية عبارة «engineer professionals» بدلًا من «engineering professionals» وتفترض أن المتقدمين موظفون، ولا يوضح بند الخبرة العملية ما إذا كانت الخبرة الصناعية شرطًا أم ميزة مفضلة.</t>
         </is>
       </c>
       <c r="I86" s="8" t="inlineStr">
         <is>
-          <t>تصحيح مطلوب</t>
+          <t>توصية تحسين</t>
         </is>
       </c>
       <c r="J86" s="8" t="inlineStr">
@@ -5390,10 +5390,14 @@
       </c>
       <c r="K86" s="9" t="inlineStr">
         <is>
-          <t>إعادة الصياغة إلى «The PhD in Business Administration program aims to develop scholars…»، وتوحيد علامتي التنصيص.</t>
-        </is>
-      </c>
-      <c r="L86" s="9" t="inlineStr"/>
+          <t>تعديل العبارتين إلى «engineering professionals» و«provides participants with the skills»، وإعادة صياغة بند الخبرة إلى «Industrial experience is preferred but not required» أو النص على المتطلب صراحة.</t>
+        </is>
+      </c>
+      <c r="L86" s="9" t="inlineStr">
+        <is>
+          <t>ترد عبارة بند الخبرة نفسها في صفحتي ماجستير الهندسة الكهربائية والمدنية.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="n">
@@ -5401,42 +5405,42 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>ماجستير إدارة الأعمال التنفيذي EMBA</t>
+          <t>دكتوراه إدارة الأعمال</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/admissions_requirements_emba_gdp</t>
+          <t>https://pmu.edu.sa/admission/admissions_requirements_phdba_gdp</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>المحتوى الرئيس لصفحات متطلبات ماجستير إدارة الأعمال التنفيذي وماجستير إدارة الأعمال وماجستير الهندسة الميكانيكية وبقية برامج الدراسات العليا؛ والقائمة الجانبية؛ وصفحات نماذج التقديم</t>
+          <t>صفحة متطلبات دكتوراه إدارة الأعمال: الفقرة التعريفية</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>[Application Form pages] Pay a non-refundable application fee of SAR 950 (incl. VAT) upon submission of documents … [Sidebar] Apply for EMBA … Apply for MBA … Apply for MSHD … Apply for MSME</t>
+          <t>The Ph.D. program is internationally accredited by AACSB as top 6% of business schools worldwide.</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>تجربة المستخدم</t>
+          <t>دقة المعلومات</t>
         </is>
       </c>
       <c r="G87" s="6" t="inlineStr">
         <is>
-          <t>معلومات التقديم غير ظاهرة</t>
+          <t>ادعاء اعتماد غير موثق</t>
         </is>
       </c>
       <c r="H87" s="6" t="inlineStr">
         <is>
-          <t>لا تعرض صفحة برامج الدراسات العليا ولا صفحات متطلبات البرامج رسوم التقديم (950 ريالًا شاملة ضريبة القيمة المضافة، غير مستردة، وهي منشورة في صفحات نماذج التقديم فقط) ولا قائمة المستندات المطلوبة، ولا تحيل إلى مواعيد التقديم في تقويم القبول.</t>
+          <t>تنسب الصفحة اعتماد AACSB إلى برنامج الدكتوراه بوصفه برنامجًا، مع أن الاعتماد يُمنح للكلية، وتذكر نسبة «أعلى 6%» دون مرجع.</t>
         </is>
       </c>
       <c r="I87" s="5" t="inlineStr">
         <is>
-          <t>توصية تحسين</t>
+          <t>متابعة وتحقق</t>
         </is>
       </c>
       <c r="J87" s="5" t="inlineStr">
@@ -5446,12 +5450,12 @@
       </c>
       <c r="K87" s="6" t="inlineStr">
         <is>
-          <t>إضافة زر تقديم واضح، ورسوم التقديم، وقائمة المستندات المطلوبة، وموعد البدء أو رابط تقويم القبول للدراسات العليا ضمن محتوى كل صفحة برنامج.</t>
+          <t>التحقق من حالة الاعتماد مع كلية إدارة الأعمال، ثم إعادة الصياغة بما يطابق الوضع الفعلي (مثل: «PMU’s College of Business is AACSB-accredited») مع ذكر مرجع لنسبة 6% أو حذفها.</t>
         </is>
       </c>
       <c r="L87" s="6" t="inlineStr">
         <is>
-          <t>عدم ظهور القائمة الجانبية في عرض الجوال وارد في الملاحظات المصدرية، ويتسق مع النص المعروض في عرض الجوال الذي لا يتضمن روابط «Apply for».</t>
+          <t>الملاحظة الرئيسة المتعلقة بهذه الصفحة (المدمجة في صف شروط الأهلية) تشير إلى أن المصادر المتاحة تؤكد العضوية لا الاعتماد الكامل؛ لا يمكن تأكيد ذلك من نص الصفحة وحده. رُفعت الأولوية إلى متوسطة لأثر الادعاء على سمعة الجامعة.</t>
         </is>
       </c>
     </row>
@@ -5461,22 +5465,22 @@
       </c>
       <c r="B88" s="9" t="inlineStr">
         <is>
-          <t>ماجستير إدارة الأعمال التنفيذي EMBA</t>
+          <t>دكتوراه إدارة الأعمال</t>
         </is>
       </c>
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/admissions_requirements_emba_gdp</t>
+          <t>https://pmu.edu.sa/admission/admissions_requirements_phdba_gdp</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>صفحة متطلبات ماجستير إدارة الأعمال التنفيذي: قسم «Work Experience»</t>
+          <t>صفحة متطلبات دكتوراه إدارة الأعمال: قسم «Educational Background»</t>
         </is>
       </c>
       <c r="E88" s="10" t="inlineStr">
         <is>
-          <t>Successful candidates should have from three to five years of professional work experience</t>
+          <t>Otherwise, if the master degree is not from another discipline they must successfully attend and complete with minimum GPA 2.80 12 credit hours of MBA … Applicants must have a minimum cumulative GPA of 3.00 (scale is 4.00 = "A”) or they must have a minimum cumulative GPA of 3.20</t>
         </is>
       </c>
       <c r="F88" s="9" t="inlineStr">
@@ -5486,30 +5490,34 @@
       </c>
       <c r="G88" s="9" t="inlineStr">
         <is>
-          <t>متطلب خبرة ملتبس</t>
+          <t>شرط أهلية ملتبس</t>
         </is>
       </c>
       <c r="H88" s="9" t="inlineStr">
         <is>
-          <t>توحي عبارة «من ثلاث إلى خمس سنوات» بوجود حد أعلى للخبرة العملية، في حين تذكر الفقرة التعريفية أن المشاركين يلزمهم عدة سنوات من الخبرة بعد البكالوريوس.</t>
+          <t>تتضمن جملة الأهلية نفيًا مزدوجًا («not from another discipline») يعكس المعنى المقصود، وتذكر ثلاثة حدود للمعدل (2.80 و3.00 و3.20) دون بيان الحالة التي ينطبق عليها كل منها.</t>
         </is>
       </c>
       <c r="I88" s="8" t="inlineStr">
         <is>
-          <t>متابعة وتحقق</t>
+          <t>تصحيح مطلوب</t>
         </is>
       </c>
       <c r="J88" s="8" t="inlineStr">
         <is>
-          <t>منخفضة</t>
+          <t>متوسطة</t>
         </is>
       </c>
       <c r="K88" s="9" t="inlineStr">
         <is>
-          <t>تأكيد المقصود مع كلية إدارة الأعمال، والنص على الحد الأدنى فقط (مثل: «A minimum of three years of professional work experience») إن لم يكن الحد الأعلى مقصودًا.</t>
-        </is>
-      </c>
-      <c r="L88" s="9" t="inlineStr"/>
+          <t>إعادة صياغة الشروط في بنود منفصلة واضحة تحدد لكل حالة (تخصص الماجستير، ومرحلة الدراسة) المعدل المطلوب، بعد اعتمادها من عمادة الدراسات العليا.</t>
+        </is>
+      </c>
+      <c r="L88" s="9" t="inlineStr">
+        <is>
+          <t>الشق الثاني من إحدى الملاحظتين المدمجتين (ادعاء اعتماد AACSB) معالج في صف مستقل.</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="n">
@@ -5517,22 +5525,22 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>ماجستير إدارة الأعمال التنفيذي EMBA</t>
+          <t>دكتوراه إدارة الأعمال</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/admissions_requirements_emba_gdp</t>
+          <t>https://pmu.edu.sa/admission/admissions_requirements_phdba_gdp</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>صفحة متطلبات ماجستير إدارة الأعمال التنفيذي: قسم «Supporting Documents»</t>
+          <t>صفحة متطلبات دكتوراه إدارة الأعمال: الفقرة التعريفية وقسم «Educational Background»</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>Three reference letters from supervisors and others in superior positions within the employing organization or others who can provide appropriate references</t>
+          <t>Doctor of Philosophy (Ph.D.) in Business Administration program is to develop scholars … (scale is 4.00 = "A”)</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr">
@@ -5542,17 +5550,17 @@
       </c>
       <c r="G89" s="6" t="inlineStr">
         <is>
-          <t>صياغة مطوّلة</t>
+          <t>خطأ نحوي وترقيمي</t>
         </is>
       </c>
       <c r="H89" s="6" t="inlineStr">
         <is>
-          <t>صيغت عبارة خطابات التوصية صياغة مطوّلة وغير مألوفة («others in superior positions»).</t>
+          <t>الجملة الافتتاحية غير سليمة نحويًا (تنقصها أداة التعريف وفعل مناسب)، وتستخدم ملاحظة سلّم المعدل علامتي تنصيص غير متطابقتين.</t>
         </is>
       </c>
       <c r="I89" s="5" t="inlineStr">
         <is>
-          <t>توصية تحسين</t>
+          <t>تصحيح مطلوب</t>
         </is>
       </c>
       <c r="J89" s="5" t="inlineStr">
@@ -5562,7 +5570,7 @@
       </c>
       <c r="K89" s="6" t="inlineStr">
         <is>
-          <t>إعادة الصياغة إلى: «Three reference letters from supervisors or senior colleagues».</t>
+          <t>إعادة الصياغة إلى «The PhD in Business Administration program aims to develop scholars…»، وتوحيد علامتي التنصيص.</t>
         </is>
       </c>
       <c r="L89" s="6" t="inlineStr"/>
@@ -5573,37 +5581,37 @@
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>ماجستير إدارة الأعمال MBA</t>
+          <t>ماجستير إدارة الأعمال التنفيذي EMBA</t>
         </is>
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/admissions_requirements_mba_gdp</t>
+          <t>https://pmu.edu.sa/admission/admissions_requirements_emba_gdp</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>صفحة متطلبات ماجستير إدارة الأعمال: الفقرة التعريفية</t>
+          <t>المحتوى الرئيس لصفحات متطلبات ماجستير إدارة الأعمال التنفيذي وماجستير إدارة الأعمال وماجستير الهندسة الميكانيكية وبقية برامج الدراسات العليا؛ والقائمة الجانبية؛ وصفحات نماذج التقديم</t>
         </is>
       </c>
       <c r="E90" s="10" t="inlineStr">
         <is>
-          <t>non-business majors may be given the opportunity to take four business foundation courses before beginning their MBA coursework</t>
+          <t>[Application Form pages] Pay a non-refundable application fee of SAR 950 (incl. VAT) upon submission of documents … [Sidebar] Apply for EMBA … Apply for MBA … Apply for MSHD … Apply for MSME</t>
         </is>
       </c>
       <c r="F90" s="9" t="inlineStr">
         <is>
-          <t>دقة المعلومات</t>
+          <t>تجربة المستخدم</t>
         </is>
       </c>
       <c r="G90" s="9" t="inlineStr">
         <is>
-          <t>شرط غير واضح</t>
+          <t>معلومات التقديم غير ظاهرة</t>
         </is>
       </c>
       <c r="H90" s="9" t="inlineStr">
         <is>
-          <t>لا توضح الصفحة ما إذا كانت المقررات التأسيسية الأربعة لخريجي التخصصات غير الإدارية إلزامية أم اختيارية، ولا ما إذا كانت ضمن الساعات المعتمدة الـ 36 أم إضافية إليها.</t>
+          <t>لا تعرض صفحة برامج الدراسات العليا ولا صفحات متطلبات البرامج رسوم التقديم (950 ريالًا شاملة ضريبة القيمة المضافة، غير مستردة، وهي منشورة في صفحات نماذج التقديم فقط) ولا قائمة المستندات المطلوبة، ولا تحيل إلى مواعيد التقديم في تقويم القبول.</t>
         </is>
       </c>
       <c r="I90" s="8" t="inlineStr">
@@ -5613,15 +5621,19 @@
       </c>
       <c r="J90" s="8" t="inlineStr">
         <is>
-          <t>منخفضة</t>
+          <t>متوسطة</t>
         </is>
       </c>
       <c r="K90" s="9" t="inlineStr">
         <is>
-          <t>النص صراحة على إلزامية المقررات التأسيسية من عدمها وعلاقتها بالساعات المعتمدة الـ 36، بعد تأكيد ذلك من كلية إدارة الأعمال.</t>
-        </is>
-      </c>
-      <c r="L90" s="9" t="inlineStr"/>
+          <t>إضافة زر تقديم واضح، ورسوم التقديم، وقائمة المستندات المطلوبة، وموعد البدء أو رابط تقويم القبول للدراسات العليا ضمن محتوى كل صفحة برنامج.</t>
+        </is>
+      </c>
+      <c r="L90" s="9" t="inlineStr">
+        <is>
+          <t>عدم ظهور القائمة الجانبية في عرض الجوال وارد في الملاحظات المصدرية، ويتسق مع النص المعروض في عرض الجوال الذي لا يتضمن روابط «Apply for».</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="n">
@@ -5629,22 +5641,22 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>ماجستير التنمية البشرية MSHD</t>
+          <t>ماجستير إدارة الأعمال التنفيذي EMBA</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/admissions_requirements_msehd_gdp</t>
+          <t>https://pmu.edu.sa/admission/admissions_requirements_emba_gdp</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>صفحة متطلبات ماجستير التنمية البشرية: عنوان «Work Experience»</t>
+          <t>صفحة متطلبات ماجستير إدارة الأعمال التنفيذي: قسم «Work Experience»</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>Work Experience … Personal Data Sheet/Curriculum Vita: The Personal Data Sheet should include relevant biographical information and professional/educational experience.</t>
+          <t>Successful candidates should have from three to five years of professional work experience</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
@@ -5654,34 +5666,30 @@
       </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
-          <t>متطلب ناقص</t>
+          <t>متطلب خبرة ملتبس</t>
         </is>
       </c>
       <c r="H91" s="6" t="inlineStr">
         <is>
-          <t>يرد عنوان «Work Experience» دون أي متطلب تحته، ويليه مباشرة بند السيرة الذاتية.</t>
+          <t>توحي عبارة «من ثلاث إلى خمس سنوات» بوجود حد أعلى للخبرة العملية، في حين تذكر الفقرة التعريفية أن المشاركين يلزمهم عدة سنوات من الخبرة بعد البكالوريوس.</t>
         </is>
       </c>
       <c r="I91" s="5" t="inlineStr">
         <is>
-          <t>تصحيح مطلوب</t>
+          <t>متابعة وتحقق</t>
         </is>
       </c>
       <c r="J91" s="5" t="inlineStr">
         <is>
-          <t>متوسطة</t>
+          <t>منخفضة</t>
         </is>
       </c>
       <c r="K91" s="6" t="inlineStr">
         <is>
-          <t>النص على متطلب الخبرة العملية (عدد السنوات أو «غير مطلوبة») بعد تأكيده من الكلية، ونقل بند السيرة الذاتية إلى قائمة المستندات الداعمة، أو حذف العنوان.</t>
-        </is>
-      </c>
-      <c r="L91" s="6" t="inlineStr">
-        <is>
-          <t>إحدى الملاحظتين المدمجتين مصنفة متوسطة والأخرى منخفضة، واعتُمدت المتوسطة لأن النقص يمس متطلبًا من متطلبات القبول.</t>
-        </is>
-      </c>
+          <t>تأكيد المقصود مع كلية إدارة الأعمال، والنص على الحد الأدنى فقط (مثل: «A minimum of three years of professional work experience») إن لم يكن الحد الأعلى مقصودًا.</t>
+        </is>
+      </c>
+      <c r="L91" s="6" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="8" t="n">
@@ -5689,22 +5697,22 @@
       </c>
       <c r="B92" s="9" t="inlineStr">
         <is>
-          <t>ماجستير التنمية البشرية MSHD</t>
+          <t>ماجستير إدارة الأعمال التنفيذي EMBA</t>
         </is>
       </c>
       <c r="C92" s="10" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/admissions_requirements_msehd_gdp</t>
+          <t>https://pmu.edu.sa/admission/admissions_requirements_emba_gdp</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>صفحة متطلبات ماجستير التنمية البشرية: العنوان الرئيس وقسما السيرة الذاتية وخطابات التوصية</t>
+          <t>صفحة متطلبات ماجستير إدارة الأعمال التنفيذي: قسم «Supporting Documents»</t>
         </is>
       </c>
       <c r="E92" s="10" t="inlineStr">
         <is>
-          <t>ADMISSIONS REQUIREMENTS … Personal Data Sheet/Curriculum Vita: … who can discuss the Applicant’s academic abilities</t>
+          <t>Three reference letters from supervisors and others in superior positions within the employing organization or others who can provide appropriate references</t>
         </is>
       </c>
       <c r="F92" s="9" t="inlineStr">
@@ -5714,17 +5722,17 @@
       </c>
       <c r="G92" s="9" t="inlineStr">
         <is>
-          <t>أخطاء تحريرية</t>
+          <t>صياغة مطوّلة</t>
         </is>
       </c>
       <c r="H92" s="9" t="inlineStr">
         <is>
-          <t>لا يتضمن العنوان الرئيس اسم البرنامج خلافًا لبقية صفحات البرامج، وكُتبت «Curriculum Vitae» بصيغة «Curriculum Vita»، وكُتبت كلمة «Applicant’s» بحرف كبير في وسط الجملة.</t>
+          <t>صيغت عبارة خطابات التوصية صياغة مطوّلة وغير مألوفة («others in superior positions»).</t>
         </is>
       </c>
       <c r="I92" s="8" t="inlineStr">
         <is>
-          <t>تصحيح مطلوب</t>
+          <t>توصية تحسين</t>
         </is>
       </c>
       <c r="J92" s="8" t="inlineStr">
@@ -5734,7 +5742,7 @@
       </c>
       <c r="K92" s="9" t="inlineStr">
         <is>
-          <t>تعديل العنوان إلى «MSHD ADMISSIONS REQUIREMENTS»، وتصحيح «Curriculum Vitae»، وكتابة «the applicant’s» بحرف صغير.</t>
+          <t>إعادة الصياغة إلى: «Three reference letters from supervisors or senior colleagues».</t>
         </is>
       </c>
       <c r="L92" s="9" t="inlineStr"/>
@@ -5745,42 +5753,42 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>ماجستير التنمية البشرية MSHD</t>
+          <t>ماجستير إدارة الأعمال MBA</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/admissions_requirements_msehd_gdp</t>
+          <t>https://pmu.edu.sa/admission/admissions_requirements_mba_gdp</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>صفحة متطلبات ماجستير التنمية البشرية: قسم «Educational Background»</t>
+          <t>صفحة متطلبات ماجستير إدارة الأعمال: الفقرة التعريفية</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
-          <t>A completed baccalaureate degree (with GPA 2.50/4.00) from an accredited and/or recognized university</t>
+          <t>non-business majors may be given the opportunity to take four business foundation courses before beginning their MBA coursework</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr">
         <is>
-          <t>الاتساق</t>
+          <t>دقة المعلومات</t>
         </is>
       </c>
       <c r="G93" s="6" t="inlineStr">
         <is>
-          <t>اختلاف في صياغة الشرط</t>
+          <t>شرط غير واضح</t>
         </is>
       </c>
       <c r="H93" s="6" t="inlineStr">
         <is>
-          <t>تشترط الصفحة شهادة من جامعة «معتمدة و/أو معترف بها»، بينما تكتفي بقية صفحات الدراسات العليا بعبارة «جامعة معترف بها».</t>
+          <t>لا توضح الصفحة ما إذا كانت المقررات التأسيسية الأربعة لخريجي التخصصات غير الإدارية إلزامية أم اختيارية، ولا ما إذا كانت ضمن الساعات المعتمدة الـ 36 أم إضافية إليها.</t>
         </is>
       </c>
       <c r="I93" s="5" t="inlineStr">
         <is>
-          <t>متابعة وتحقق</t>
+          <t>توصية تحسين</t>
         </is>
       </c>
       <c r="J93" s="5" t="inlineStr">
@@ -5790,7 +5798,7 @@
       </c>
       <c r="K93" s="6" t="inlineStr">
         <is>
-          <t>تأكيد ما إذا كان الاختلاف مقصودًا من عمادة الدراسات العليا، وإلا توحيد الصياغة في جميع صفحات الدراسات العليا.</t>
+          <t>النص صراحة على إلزامية المقررات التأسيسية من عدمها وعلاقتها بالساعات المعتمدة الـ 36، بعد تأكيد ذلك من كلية إدارة الأعمال.</t>
         </is>
       </c>
       <c r="L93" s="6" t="inlineStr"/>
@@ -5801,37 +5809,37 @@
       </c>
       <c r="B94" s="9" t="inlineStr">
         <is>
-          <t>ماجستير الهندسة الميكانيكية MSME</t>
+          <t>ماجستير التنمية البشرية MSHD</t>
         </is>
       </c>
       <c r="C94" s="10" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/admissions_requirements_msme_gdp</t>
+          <t>https://pmu.edu.sa/admission/admissions_requirements_msehd_gdp</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>صفحة متطلبات ماجستير الهندسة الميكانيكية: الفقرة التعريفية</t>
+          <t>صفحة متطلبات ماجستير التنمية البشرية: عنوان «Work Experience»</t>
         </is>
       </c>
       <c r="E94" s="10" t="inlineStr">
         <is>
-          <t>The MSME is offered in Two tracks: Thermofluids track and Mechanical Systems track.</t>
+          <t>Work Experience … Personal Data Sheet/Curriculum Vita: The Personal Data Sheet should include relevant biographical information and professional/educational experience.</t>
         </is>
       </c>
       <c r="F94" s="9" t="inlineStr">
         <is>
-          <t>لغوي ونحوي</t>
+          <t>دقة المعلومات</t>
         </is>
       </c>
       <c r="G94" s="9" t="inlineStr">
         <is>
-          <t>خطأ في الأحرف الكبيرة</t>
+          <t>متطلب ناقص</t>
         </is>
       </c>
       <c r="H94" s="9" t="inlineStr">
         <is>
-          <t>كُتبت كلمة «Two» بحرف كبير في وسط الجملة.</t>
+          <t>يرد عنوان «Work Experience» دون أي متطلب تحته، ويليه مباشرة بند السيرة الذاتية.</t>
         </is>
       </c>
       <c r="I94" s="8" t="inlineStr">
@@ -5841,15 +5849,19 @@
       </c>
       <c r="J94" s="8" t="inlineStr">
         <is>
-          <t>منخفضة</t>
+          <t>متوسطة</t>
         </is>
       </c>
       <c r="K94" s="9" t="inlineStr">
         <is>
-          <t>تصحيحها إلى «two tracks».</t>
-        </is>
-      </c>
-      <c r="L94" s="9" t="inlineStr"/>
+          <t>النص على متطلب الخبرة العملية (عدد السنوات أو «غير مطلوبة») بعد تأكيده من الكلية، ونقل بند السيرة الذاتية إلى قائمة المستندات الداعمة، أو حذف العنوان.</t>
+        </is>
+      </c>
+      <c r="L94" s="9" t="inlineStr">
+        <is>
+          <t>إحدى الملاحظتين المدمجتين مصنفة متوسطة والأخرى منخفضة، واعتُمدت المتوسطة لأن النقص يمس متطلبًا من متطلبات القبول.</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="n">
@@ -5857,42 +5869,42 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>ماجستير الهندسة الكهربائية MSEE</t>
+          <t>ماجستير التنمية البشرية MSHD</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/application_form_msee_gdp</t>
+          <t>https://pmu.edu.sa/admission/admissions_requirements_msehd_gdp</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>الفقرة التعريفية في صفحات متطلبات ماجستير الهندسة الكهربائية والمدنية وماجستير التصميم الداخلي</t>
+          <t>صفحة متطلبات ماجستير التنمية البشرية: العنوان الرئيس وقسما السيرة الذاتية وخطابات التوصية</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>[MSEE, MSCE] The program will be offered under the College of Engineering. … [MSID] The Department of Interior Design at PMU will educate tomorrow’s interior design leaders and innovators … will be to provide an environment conducive</t>
+          <t>ADMISSIONS REQUIREMENTS … Personal Data Sheet/Curriculum Vita: … who can discuss the Applicant’s academic abilities</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>دقة المعلومات</t>
+          <t>لغوي ونحوي</t>
         </is>
       </c>
       <c r="G95" s="6" t="inlineStr">
         <is>
-          <t>صياغة سابقة للإطلاق</t>
+          <t>أخطاء تحريرية</t>
         </is>
       </c>
       <c r="H95" s="6" t="inlineStr">
         <is>
-          <t>تصف الصفحات الثلاث البرامج بصيغة المستقبل («will be offered» و«will educate» و«will be to provide»)، مع أن رسومها منشورة، مما يوحي بأنها لم تُطرح بعد.</t>
+          <t>لا يتضمن العنوان الرئيس اسم البرنامج خلافًا لبقية صفحات البرامج، وكُتبت «Curriculum Vitae» بصيغة «Curriculum Vita»، وكُتبت كلمة «Applicant’s» بحرف كبير في وسط الجملة.</t>
         </is>
       </c>
       <c r="I95" s="5" t="inlineStr">
         <is>
-          <t>توصية تحسين</t>
+          <t>تصحيح مطلوب</t>
         </is>
       </c>
       <c r="J95" s="5" t="inlineStr">
@@ -5902,7 +5914,7 @@
       </c>
       <c r="K95" s="6" t="inlineStr">
         <is>
-          <t>إعادة الصياغة بصيغة المضارع، مثل: «The program is offered by the College of Engineering.»</t>
+          <t>تعديل العنوان إلى «MSHD ADMISSIONS REQUIREMENTS»، وتصحيح «Curriculum Vitae»، وكتابة «the applicant’s» بحرف صغير.</t>
         </is>
       </c>
       <c r="L95" s="6" t="inlineStr"/>
@@ -5913,42 +5925,42 @@
       </c>
       <c r="B96" s="9" t="inlineStr">
         <is>
-          <t>ماجستير الهندسة الكهربائية MSEE</t>
+          <t>ماجستير التنمية البشرية MSHD</t>
         </is>
       </c>
       <c r="C96" s="10" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/application_form_msee_gdp</t>
+          <t>https://pmu.edu.sa/admission/admissions_requirements_msehd_gdp</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>صفحة متطلبات ماجستير الهندسة الكهربائية: قسم «Educational Background»</t>
+          <t>صفحة متطلبات ماجستير التنمية البشرية: قسم «Educational Background»</t>
         </is>
       </c>
       <c r="E96" s="10" t="inlineStr">
         <is>
-          <t>A Bachelor’s Degree of Science in Engineering from a recognized university … *Students with Bachelor of Science degrees in closely related disciplines to Engineering can apply upon conditions specified by the College of Engineering.</t>
+          <t>A completed baccalaureate degree (with GPA 2.50/4.00) from an accredited and/or recognized university</t>
         </is>
       </c>
       <c r="F96" s="9" t="inlineStr">
         <is>
-          <t>دقة المعلومات</t>
+          <t>الاتساق</t>
         </is>
       </c>
       <c r="G96" s="9" t="inlineStr">
         <is>
-          <t>شرط غير محدد</t>
+          <t>اختلاف في صياغة الشرط</t>
         </is>
       </c>
       <c r="H96" s="9" t="inlineStr">
         <is>
-          <t>ترد الحاشية المعلّمة بنجمة دون نجمة مقابلة في شرط الشهادة، ويُذكر التخصص المطلوب «Engineering» عامًا دون تحديد، خلافًا لصفحتي الهندسة الميكانيكية والمدنية.</t>
+          <t>تشترط الصفحة شهادة من جامعة «معتمدة و/أو معترف بها»، بينما تكتفي بقية صفحات الدراسات العليا بعبارة «جامعة معترف بها».</t>
         </is>
       </c>
       <c r="I96" s="8" t="inlineStr">
         <is>
-          <t>تصحيح مطلوب</t>
+          <t>متابعة وتحقق</t>
         </is>
       </c>
       <c r="J96" s="8" t="inlineStr">
@@ -5958,7 +5970,7 @@
       </c>
       <c r="K96" s="9" t="inlineStr">
         <is>
-          <t>إضافة النجمة وتحديد التخصص المطلوب (مثل: Electrical Engineering) بعد تأكيده من كلية الهندسة.</t>
+          <t>تأكيد ما إذا كان الاختلاف مقصودًا من عمادة الدراسات العليا، وإلا توحيد الصياغة في جميع صفحات الدراسات العليا.</t>
         </is>
       </c>
       <c r="L96" s="9" t="inlineStr"/>
@@ -5969,22 +5981,22 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>ماجستير الهندسة المدنية MSCE</t>
+          <t>ماجستير الهندسة الميكانيكية MSME</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/application_form_msce_gdp</t>
+          <t>https://pmu.edu.sa/admission/admissions_requirements_msme_gdp</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>الفقرة التعريفية وقسم «Supporting Documents» في صفحة متطلبات ماجستير الهندسة المدنية؛ والفقرة التعريفية في صفحة ماجستير الهندسة الكهربائية</t>
+          <t>صفحة متطلبات ماجستير الهندسة الميكانيكية: الفقرة التعريفية</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
-          <t>[MSCE] The core curriculum has two tracks Structural and Geotechnical Engineering, Environment and Water Resources Engineering. … Statement of purpose:A statement of purpose … [MSEE] Masters in Electrical Engineering … two tracks; Communication Systems and Signal Processing track</t>
+          <t>The MSME is offered in Two tracks: Thermofluids track and Mechanical Systems track.</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr">
@@ -5994,12 +6006,12 @@
       </c>
       <c r="G97" s="6" t="inlineStr">
         <is>
-          <t>أخطاء ترقيم وتسمية</t>
+          <t>خطأ في الأحرف الكبيرة</t>
         </is>
       </c>
       <c r="H97" s="6" t="inlineStr">
         <is>
-          <t>تُسرد مساري ماجستير الهندسة المدنية دون نقطتين أو فاصل واضح فيمكن قراءتهما ثلاثة بنود، وتنقص مسافة بعد النقطتين في «Statement of purpose:A»، وتستخدم صفحة الهندسة الكهربائية فاصلة منقوطة قبل قائمة المسارين واسم «Masters in Electrical Engineering» بدلًا من الاسم الرسمي.</t>
+          <t>كُتبت كلمة «Two» بحرف كبير في وسط الجملة.</t>
         </is>
       </c>
       <c r="I97" s="5" t="inlineStr">
@@ -6014,14 +6026,10 @@
       </c>
       <c r="K97" s="6" t="inlineStr">
         <is>
-          <t>تصحيح الصياغة إلى «two tracks: (1) Structural and Geotechnical Engineering; (2) Environmental and Water Resources Engineering»، وإضافة المسافة، واستخدام «Master of Science in Electrical Engineering» و«two tracks: Communication Systems and Signal Processing, and Power Systems».</t>
-        </is>
-      </c>
-      <c r="L97" s="6" t="inlineStr">
-        <is>
-          <t>ترد عبارة «Masters in Civil Engineering» بالصيغة نفسها في صفحة الهندسة المدنية.</t>
-        </is>
-      </c>
+          <t>تصحيحها إلى «two tracks».</t>
+        </is>
+      </c>
+      <c r="L97" s="6" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="8" t="n">
@@ -6029,22 +6037,22 @@
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>ماجستير الإدارة الهندسية EMGMS</t>
+          <t>ماجستير الهندسة الكهربائية MSEE</t>
         </is>
       </c>
       <c r="C98" s="10" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/admissions_requirements_emgms_gdp</t>
+          <t>https://pmu.edu.sa/admission/application_form_msee_gdp</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>صفحة متطلبات القبول لماجستير الإدارة الهندسية: قائمة «Application Materials» (كشف الدرجات، خطابات التوصية، درجات إتقان اللغة الإنجليزية)</t>
+          <t>الفقرة التعريفية في صفحات متطلبات ماجستير الهندسة الكهربائية والمدنية وماجستير التصميم الداخلي</t>
         </is>
       </c>
       <c r="E98" s="10" t="inlineStr">
         <is>
-          <t>(minimum 3.00 out of 4.00) … Letters of Recommendation (Minimum 3) … TOEFL – minimum of 79 iBT … IELTS – minimum composite score of 7, with no subject area below a 6 … Graduate English Language Endorsement from UA Center for English as Second Language (CESL)</t>
+          <t>[MSEE, MSCE] The program will be offered under the College of Engineering. … [MSID] The Department of Interior Design at PMU will educate tomorrow’s interior design leaders and innovators … will be to provide an environment conducive</t>
         </is>
       </c>
       <c r="F98" s="9" t="inlineStr">
@@ -6054,34 +6062,30 @@
       </c>
       <c r="G98" s="9" t="inlineStr">
         <is>
-          <t>نص يشير إلى جامعة أخرى</t>
+          <t>صياغة سابقة للإطلاق</t>
         </is>
       </c>
       <c r="H98" s="9" t="inlineStr">
         <is>
-          <t>تتضمن صفحة متطلبات القبول لبرنامج ماجستير الإدارة الهندسية نصًا يشير إلى مركز لغة تابع لجامعة أخرى (UA CESL)، وتشترط درجة IELTS 7 مقابل TOEFL iBT 79 غير المتكافئتين، وتشير إلى اختبار PBT القديم. كما تختلف متطلباتها عن بقية برامج الهندسة (معدل 3.00 بدلًا من 2.50، وثلاثة خطابات توصية بدلًا من اثنين)، ولا يمكن الاعتماد عليها بوصفها متطلبات معتمدة للجامعة.</t>
+          <t>تصف الصفحات الثلاث البرامج بصيغة المستقبل («will be offered» و«will educate» و«will be to provide»)، مع أن رسومها منشورة، مما يوحي بأنها لم تُطرح بعد.</t>
         </is>
       </c>
       <c r="I98" s="8" t="inlineStr">
         <is>
-          <t>تصحيح مطلوب</t>
+          <t>توصية تحسين</t>
         </is>
       </c>
       <c r="J98" s="8" t="inlineStr">
         <is>
-          <t>عالية</t>
+          <t>منخفضة</t>
         </is>
       </c>
       <c r="K98" s="9" t="inlineStr">
         <is>
-          <t>إزالة المحتوى المنقول فورًا، واستبدال متطلبات البرنامج كاملة (المعدل، واختبارات اللغة، وعدد خطابات التوصية) بالمتطلبات المعتمدة من عمادة الدراسات العليا وكلية الهندسة.</t>
-        </is>
-      </c>
-      <c r="L98" s="9" t="inlineStr">
-        <is>
-          <t>تكافؤ TOEFL iBT 79 مع IELTS 6.5 تقريبًا مرجعه جداول المقارنة المنشورة من جهة الاختبار، وليس نص الصفحة.</t>
-        </is>
-      </c>
+          <t>إعادة الصياغة بصيغة المضارع، مثل: «The program is offered by the College of Engineering.»</t>
+        </is>
+      </c>
+      <c r="L98" s="9" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="5" t="n">
@@ -6089,37 +6093,37 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>ماجستير الإدارة الهندسية EMGMS</t>
+          <t>ماجستير الهندسة الكهربائية MSEE</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/admissions_requirements_emgms_gdp</t>
+          <t>https://pmu.edu.sa/admission/application_form_msee_gdp</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>صفحة متطلبات ماجستير الإدارة الهندسية: العنوان الفرعي</t>
+          <t>صفحة متطلبات ماجستير الهندسة الكهربائية: قسم «Educational Background»</t>
         </is>
       </c>
       <c r="E99" s="7" t="inlineStr">
         <is>
-          <t>Master of Science in Engineering Management Application(EMGMS) Checklist</t>
+          <t>A Bachelor’s Degree of Science in Engineering from a recognized university … *Students with Bachelor of Science degrees in closely related disciplines to Engineering can apply upon conditions specified by the College of Engineering.</t>
         </is>
       </c>
       <c r="F99" s="6" t="inlineStr">
         <is>
-          <t>لغوي ونحوي</t>
+          <t>دقة المعلومات</t>
         </is>
       </c>
       <c r="G99" s="6" t="inlineStr">
         <is>
-          <t>خطأ في المسافات والاختصار</t>
+          <t>شرط غير محدد</t>
         </is>
       </c>
       <c r="H99" s="6" t="inlineStr">
         <is>
-          <t>تنقص مسافة قبل «(EMGMS)» في العنوان الفرعي، ولا يتبع الاختصار «EMGMS» نمط الاختصارات المعتمد لبقية برامج الماجستير (البادئة MS).</t>
+          <t>ترد الحاشية المعلّمة بنجمة دون نجمة مقابلة في شرط الشهادة، ويُذكر التخصص المطلوب «Engineering» عامًا دون تحديد، خلافًا لصفحتي الهندسة الميكانيكية والمدنية.</t>
         </is>
       </c>
       <c r="I99" s="5" t="inlineStr">
@@ -6134,14 +6138,10 @@
       </c>
       <c r="K99" s="6" t="inlineStr">
         <is>
-          <t>إضافة المسافة الناقصة، وتأكيد الاختصار الرسمي للبرنامج من عمادة الدراسات العليا وتوحيده.</t>
-        </is>
-      </c>
-      <c r="L99" s="6" t="inlineStr">
-        <is>
-          <t>شق الاختصار يتطلب تأكيدًا من الجهة المالكة.</t>
-        </is>
-      </c>
+          <t>إضافة النجمة وتحديد التخصص المطلوب (مثل: Electrical Engineering) بعد تأكيده من كلية الهندسة.</t>
+        </is>
+      </c>
+      <c r="L99" s="6" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="8" t="n">
@@ -6149,37 +6149,37 @@
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>ماجستير القانون التجاري الدولي MIBL</t>
+          <t>ماجستير الهندسة المدنية MSCE</t>
         </is>
       </c>
       <c r="C100" s="10" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/admissions_requirements_milbl_gdp</t>
+          <t>https://pmu.edu.sa/admission/application_form_msce_gdp</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>صفحة متطلبات القبول لماجستير القانون التجاري الدولي: قسم «Admission Criteria» وأوزان المفاضلة</t>
+          <t>الفقرة التعريفية وقسم «Supporting Documents» في صفحة متطلبات ماجستير الهندسة المدنية؛ والفقرة التعريفية في صفحة ماجستير الهندسة الكهربائية</t>
         </is>
       </c>
       <c r="E100" s="10" t="inlineStr">
         <is>
-          <t>A minimum (Very Good) in Bachelor’s Degree … In selecting applicants, the following weight is assigned to each admission requirement … 30% for the written test.</t>
+          <t>[MSCE] The core curriculum has two tracks Structural and Geotechnical Engineering, Environment and Water Resources Engineering. … Statement of purpose:A statement of purpose … [MSEE] Masters in Electrical Engineering … two tracks; Communication Systems and Signal Processing track</t>
         </is>
       </c>
       <c r="F100" s="9" t="inlineStr">
         <is>
-          <t>دقة المعلومات</t>
+          <t>لغوي ونحوي</t>
         </is>
       </c>
       <c r="G100" s="9" t="inlineStr">
         <is>
-          <t>متطلبات قبول ناقصة</t>
+          <t>أخطاء ترقيم وتسمية</t>
         </is>
       </c>
       <c r="H100" s="9" t="inlineStr">
         <is>
-          <t>لا تحدد الصفحة المعدل الأدنى رقميًا، وتمنح الاختبار التحريري وزنًا قدره 30% دون أي وصف له في معايير القبول، ولا تتضمن قائمة بالمستندات المطلوبة ولا رابط تقديم ضمن محتوى الصفحة.</t>
+          <t>تُسرد مساري ماجستير الهندسة المدنية دون نقطتين أو فاصل واضح فيمكن قراءتهما ثلاثة بنود، وتنقص مسافة بعد النقطتين في «Statement of purpose:A»، وتستخدم صفحة الهندسة الكهربائية فاصلة منقوطة قبل قائمة المسارين واسم «Masters in Electrical Engineering» بدلًا من الاسم الرسمي.</t>
         </is>
       </c>
       <c r="I100" s="8" t="inlineStr">
@@ -6189,15 +6189,19 @@
       </c>
       <c r="J100" s="8" t="inlineStr">
         <is>
-          <t>متوسطة</t>
+          <t>منخفضة</t>
         </is>
       </c>
       <c r="K100" s="9" t="inlineStr">
         <is>
-          <t>استكمال المتطلبات بذكر المعدل الأدنى رقميًا، ووصف الاختبار التحريري (محتواه وموعده وطريقة التسجيل)، وإضافة قائمة المستندات المطلوبة ورابط التقديم.</t>
-        </is>
-      </c>
-      <c r="L100" s="9" t="inlineStr"/>
+          <t>تصحيح الصياغة إلى «two tracks: (1) Structural and Geotechnical Engineering; (2) Environmental and Water Resources Engineering»، وإضافة المسافة، واستخدام «Master of Science in Electrical Engineering» و«two tracks: Communication Systems and Signal Processing, and Power Systems».</t>
+        </is>
+      </c>
+      <c r="L100" s="9" t="inlineStr">
+        <is>
+          <t>ترد عبارة «Masters in Civil Engineering» بالصيغة نفسها في صفحة الهندسة المدنية.</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="n">
@@ -6205,37 +6209,37 @@
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>ماجستير القانون التجاري الدولي MIBL</t>
+          <t>ماجستير الإدارة الهندسية EMGMS</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/admissions_requirements_milbl_gdp</t>
+          <t>https://pmu.edu.sa/admission/admissions_requirements_emgms_gdp</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>صفحة متطلبات القبول لماجستير القانون التجاري الدولي: قسم «English Language Proficiency Test»؛ وصفحة نموذج التقديم للبرنامج نفسه</t>
+          <t>صفحة متطلبات القبول لماجستير الإدارة الهندسية: قائمة «Application Materials» (كشف الدرجات، خطابات التوصية، درجات إتقان اللغة الإنجليزية)</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
-          <t>[MIBL requirements] A valid IELTS certificate (Academic version) with minimum scores of 6.5 overall and 5.5 in each skill or equivalent TOEFL iBT minimum scores of 83 overall … [MIBL application form] Submit original IELTS (Academic version) certificate with minimum scores of 6.0 overall</t>
+          <t>(minimum 3.00 out of 4.00) … Letters of Recommendation (Minimum 3) … TOEFL – minimum of 79 iBT … IELTS – minimum composite score of 7, with no subject area below a 6 … Graduate English Language Endorsement from UA Center for English as Second Language (CESL)</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>الاتساق</t>
+          <t>دقة المعلومات</t>
         </is>
       </c>
       <c r="G101" s="6" t="inlineStr">
         <is>
-          <t>تعارض في متطلب اللغة</t>
+          <t>نص يشير إلى جامعة أخرى</t>
         </is>
       </c>
       <c r="H101" s="6" t="inlineStr">
         <is>
-          <t>تشترط صفحة متطلبات البرنامج IELTS بدرجة 6.5، بينما تشترط صفحة نموذج التقديم للبرنامج نفسه 6.0، وتشترط بقية صفحات الدراسات العليا 6.0. وتعدّ الصفحة TOEFL iBT 83 معادلًا لـ IELTS 6.5، في حين تعدّه بقية الصفحات معادلًا لـ 6.0.</t>
+          <t>تتضمن صفحة متطلبات القبول لبرنامج ماجستير الإدارة الهندسية نصًا يشير إلى مركز لغة تابع لجامعة أخرى (UA CESL)، وتشترط درجة IELTS 7 مقابل TOEFL iBT 79 غير المتكافئتين، وتشير إلى اختبار PBT القديم. كما تختلف متطلباتها عن بقية برامج الهندسة (معدل 3.00 بدلًا من 2.50، وثلاثة خطابات توصية بدلًا من اثنين)، ولا يمكن الاعتماد عليها بوصفها متطلبات معتمدة للجامعة.</t>
         </is>
       </c>
       <c r="I101" s="5" t="inlineStr">
@@ -6245,17 +6249,17 @@
       </c>
       <c r="J101" s="5" t="inlineStr">
         <is>
-          <t>متوسطة</t>
+          <t>عالية</t>
         </is>
       </c>
       <c r="K101" s="6" t="inlineStr">
         <is>
-          <t>تأكيد الدرجة المعتمدة للبرنامج من عمادة الدراسات العليا، ثم توحيدها في صفحتي المتطلبات والتقديم، ومواءمة درجة TOEFL المعادلة معها.</t>
+          <t>إزالة المحتوى المنقول فورًا، واستبدال متطلبات البرنامج كاملة (المعدل، واختبارات اللغة، وعدد خطابات التوصية) بالمتطلبات المعتمدة من عمادة الدراسات العليا وكلية الهندسة.</t>
         </is>
       </c>
       <c r="L101" s="6" t="inlineStr">
         <is>
-          <t>لوحظ أيضًا أن صفحة نموذج التقديم العامة للدراسات العليا (المرتبطة ببرامج دكتوراه الهندسة الميكانيكية وماجستير الهندسة المدنية والكهربائية والتصميم الداخلي) تشترط IELTS 6.5، بخلاف صفحات متطلبات تلك البرامج (6.0)؛ يُستحسن مراجعتها ضمن التصحيح نفسه.</t>
+          <t>تكافؤ TOEFL iBT 79 مع IELTS 6.5 تقريبًا مرجعه جداول المقارنة المنشورة من جهة الاختبار، وليس نص الصفحة.</t>
         </is>
       </c>
     </row>
@@ -6265,55 +6269,59 @@
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>ماجستير القانون التجاري الدولي MIBL</t>
+          <t>ماجستير الإدارة الهندسية EMGMS</t>
         </is>
       </c>
       <c r="C102" s="10" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/admissions_requirements_milbl_gdp</t>
+          <t>https://pmu.edu.sa/admission/admissions_requirements_emgms_gdp</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>صفحة متطلبات القبول لماجستير القانون التجاري الدولي: الفقرة التعريفية</t>
+          <t>صفحة متطلبات ماجستير الإدارة الهندسية: العنوان الفرعي</t>
         </is>
       </c>
       <c r="E102" s="10" t="inlineStr">
         <is>
-          <t>Typically, candidates will complete the program within two years in a full-time mode (maximum 6 credits in each semester)</t>
+          <t>Master of Science in Engineering Management Application(EMGMS) Checklist</t>
         </is>
       </c>
       <c r="F102" s="9" t="inlineStr">
         <is>
-          <t>دقة المعلومات</t>
+          <t>لغوي ونحوي</t>
         </is>
       </c>
       <c r="G102" s="9" t="inlineStr">
         <is>
-          <t>تعارض في مدة الدراسة</t>
+          <t>خطأ في المسافات والاختصار</t>
         </is>
       </c>
       <c r="H102" s="9" t="inlineStr">
         <is>
-          <t>تذكر الصفحة إكمال البرنامج في سنتين بدوام كامل بحد أقصى 6 ساعات معتمدة في الفصل، بينما يحدد جدول الرسوم البرنامج بـ 36 ساعة معتمدة، وهو ما يتطلب ستة فصول دراسية ولا يتوافق مع مفهوم الدوام الكامل.</t>
+          <t>تنقص مسافة قبل «(EMGMS)» في العنوان الفرعي، ولا يتبع الاختصار «EMGMS» نمط الاختصارات المعتمد لبقية برامج الماجستير (البادئة MS).</t>
         </is>
       </c>
       <c r="I102" s="8" t="inlineStr">
         <is>
-          <t>متابعة وتحقق</t>
+          <t>تصحيح مطلوب</t>
         </is>
       </c>
       <c r="J102" s="8" t="inlineStr">
         <is>
-          <t>متوسطة</t>
+          <t>منخفضة</t>
         </is>
       </c>
       <c r="K102" s="9" t="inlineStr">
         <is>
-          <t>تأكيد العبء الدراسي الفصلي ومدة البرنامج مع كلية القانون، ثم تصحيح أحدهما أو النص على وجوب الدراسة في الفصول الصيفية إن كان ذلك مقصودًا.</t>
-        </is>
-      </c>
-      <c r="L102" s="9" t="inlineStr"/>
+          <t>إضافة المسافة الناقصة، وتأكيد الاختصار الرسمي للبرنامج من عمادة الدراسات العليا وتوحيده.</t>
+        </is>
+      </c>
+      <c r="L102" s="9" t="inlineStr">
+        <is>
+          <t>شق الاختصار يتطلب تأكيدًا من الجهة المالكة.</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="n">
@@ -6331,12 +6339,12 @@
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>صفحة متطلبات القبول لماجستير القانون التجاري الدولي: الفقرة التعريفية</t>
+          <t>صفحة متطلبات القبول لماجستير القانون التجاري الدولي: قسم «Admission Criteria» وأوزان المفاضلة</t>
         </is>
       </c>
       <c r="E103" s="7" t="inlineStr">
         <is>
-          <t>The year 2025 marks another milestone for PMU Law with the approval of the postgraduate program</t>
+          <t>A minimum (Very Good) in Bachelor’s Degree … In selecting applicants, the following weight is assigned to each admission requirement … 30% for the written test.</t>
         </is>
       </c>
       <c r="F103" s="6" t="inlineStr">
@@ -6346,27 +6354,27 @@
       </c>
       <c r="G103" s="6" t="inlineStr">
         <is>
-          <t>صياغة مرتبطة بتاريخ مضى</t>
+          <t>متطلبات قبول ناقصة</t>
         </is>
       </c>
       <c r="H103" s="6" t="inlineStr">
         <is>
-          <t>تستخدم الفقرة التعريفية صياغة تفترض أن عام 2025 هو العام الجاري، وقد أصبحت قديمة.</t>
+          <t>لا تحدد الصفحة المعدل الأدنى رقميًا، وتمنح الاختبار التحريري وزنًا قدره 30% دون أي وصف له في معايير القبول، ولا تتضمن قائمة بالمستندات المطلوبة ولا رابط تقديم ضمن محتوى الصفحة.</t>
         </is>
       </c>
       <c r="I103" s="5" t="inlineStr">
         <is>
-          <t>توصية تحسين</t>
+          <t>تصحيح مطلوب</t>
         </is>
       </c>
       <c r="J103" s="5" t="inlineStr">
         <is>
-          <t>منخفضة</t>
+          <t>متوسطة</t>
         </is>
       </c>
       <c r="K103" s="6" t="inlineStr">
         <is>
-          <t>إعادة الصياغة بصيغة ثابتة، مثل: «In 2025, the Ministry of Education approved the Master of Arts (MA) in International Business Law…».</t>
+          <t>استكمال المتطلبات بذكر المعدل الأدنى رقميًا، ووصف الاختبار التحريري (محتواه وموعده وطريقة التسجيل)، وإضافة قائمة المستندات المطلوبة ورابط التقديم.</t>
         </is>
       </c>
       <c r="L103" s="6" t="inlineStr"/>
@@ -6387,45 +6395,49 @@
       </c>
       <c r="D104" s="9" t="inlineStr">
         <is>
-          <t>صفحة متطلبات القبول لماجستير القانون التجاري الدولي: الفقرة التعريفية</t>
+          <t>صفحة متطلبات القبول لماجستير القانون التجاري الدولي: قسم «English Language Proficiency Test»؛ وصفحة نموذج التقديم للبرنامج نفسه</t>
         </is>
       </c>
       <c r="E104" s="10" t="inlineStr">
         <is>
-          <t>admission on a part-time basis may be considered subject to the applicable regulation, delivered and facilitated by qualified and experienced academics in the respective areas.</t>
+          <t>[MIBL requirements] A valid IELTS certificate (Academic version) with minimum scores of 6.5 overall and 5.5 in each skill or equivalent TOEFL iBT minimum scores of 83 overall … [MIBL application form] Submit original IELTS (Academic version) certificate with minimum scores of 6.0 overall</t>
         </is>
       </c>
       <c r="F104" s="9" t="inlineStr">
         <is>
-          <t>لغوي ونحوي</t>
+          <t>الاتساق</t>
         </is>
       </c>
       <c r="G104" s="9" t="inlineStr">
         <is>
-          <t>جملة طويلة متداخلة</t>
+          <t>تعارض في متطلب اللغة</t>
         </is>
       </c>
       <c r="H104" s="9" t="inlineStr">
         <is>
-          <t>تدمج الجملة موضوع القبول بدوام جزئي مع موضوع تقديم البرنامج من قِبل أكاديميين مؤهلين في جملة واحدة، فيلتبس المعنى.</t>
+          <t>تشترط صفحة متطلبات البرنامج IELTS بدرجة 6.5، بينما تشترط صفحة نموذج التقديم للبرنامج نفسه 6.0، وتشترط بقية صفحات الدراسات العليا 6.0. وتعدّ الصفحة TOEFL iBT 83 معادلًا لـ IELTS 6.5، في حين تعدّه بقية الصفحات معادلًا لـ 6.0.</t>
         </is>
       </c>
       <c r="I104" s="8" t="inlineStr">
         <is>
-          <t>توصية تحسين</t>
+          <t>تصحيح مطلوب</t>
         </is>
       </c>
       <c r="J104" s="8" t="inlineStr">
         <is>
-          <t>منخفضة</t>
+          <t>متوسطة</t>
         </is>
       </c>
       <c r="K104" s="9" t="inlineStr">
         <is>
-          <t>تقسيم الجملة إلى جملتين، مثل: «...subject to the applicable regulations. The program is delivered by qualified and experienced academics in the respective areas.»</t>
-        </is>
-      </c>
-      <c r="L104" s="9" t="inlineStr"/>
+          <t>تأكيد الدرجة المعتمدة للبرنامج من عمادة الدراسات العليا، ثم توحيدها في صفحتي المتطلبات والتقديم، ومواءمة درجة TOEFL المعادلة معها.</t>
+        </is>
+      </c>
+      <c r="L104" s="9" t="inlineStr">
+        <is>
+          <t>لوحظ أيضًا أن صفحة نموذج التقديم العامة للدراسات العليا (المرتبطة ببرامج دكتوراه الهندسة الميكانيكية وماجستير الهندسة المدنية والكهربائية والتصميم الداخلي) تشترط IELTS 6.5، بخلاف صفحات متطلبات تلك البرامج (6.0)؛ يُستحسن مراجعتها ضمن التصحيح نفسه.</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="n">
@@ -6433,22 +6445,22 @@
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>رسوم الدراسات العليا</t>
+          <t>ماجستير القانون التجاري الدولي MIBL</t>
         </is>
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/post_graduate_fees_tf_ro</t>
+          <t>https://pmu.edu.sa/admission/admissions_requirements_milbl_gdp</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>صفحة رسوم الدراسات العليا: جدول الرسوم الدراسية الكاملة؛ وصفحة قائمة التخصصات</t>
+          <t>صفحة متطلبات القبول لماجستير القانون التجاري الدولي: الفقرة التعريفية</t>
         </is>
       </c>
       <c r="E105" s="7" t="inlineStr">
         <is>
-          <t>Master of Engineering in Innovation, Sustainability, and Entrepreneurship (33) | SAR 80,000 | SAR 80,000 … PRE-Master for Master of Education | NA | SAR 30,000 … [List of Majors] Master of Science in Engineering Innovation, Sustainability, and Entrepreneurship</t>
+          <t>Typically, candidates will complete the program within two years in a full-time mode (maximum 6 credits in each semester)</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr">
@@ -6458,12 +6470,12 @@
       </c>
       <c r="G105" s="6" t="inlineStr">
         <is>
-          <t>برامج مسعّرة دون صفحة قبول</t>
+          <t>تعارض في مدة الدراسة</t>
         </is>
       </c>
       <c r="H105" s="6" t="inlineStr">
         <is>
-          <t>يتضمن جدول رسوم الدراسات العليا رسومًا لبرنامج ماجستير الهندسة في الابتكار والاستدامة وريادة الأعمال ولبرنامج «ما قبل الماجستير لماجستير التربية»، ولا توجد لهما صفحة قبول ولا إدراج في صفحة برامج الدراسات العليا أو صفحة الدرجات والبرامج، كما يرد اسم الأول بصيغة مختلفة في قائمة التخصصات.</t>
+          <t>تذكر الصفحة إكمال البرنامج في سنتين بدوام كامل بحد أقصى 6 ساعات معتمدة في الفصل، بينما يحدد جدول الرسوم البرنامج بـ 36 ساعة معتمدة، وهو ما يتطلب ستة فصول دراسية ولا يتوافق مع مفهوم الدوام الكامل.</t>
         </is>
       </c>
       <c r="I105" s="5" t="inlineStr">
@@ -6478,14 +6490,10 @@
       </c>
       <c r="K105" s="6" t="inlineStr">
         <is>
-          <t>تأكيد حالة طرح البرنامجين من عمادة الدراسات العليا والإدارة المالية، ثم إما إضافة صفحة قبول ورابط تقديم لكل برنامج مطروح، أو حذف صفّي الرسوم، مع توحيد الاسم الرسمي.</t>
-        </is>
-      </c>
-      <c r="L105" s="6" t="inlineStr">
-        <is>
-          <t>الجزء من الملاحظة الخاص باختلاف اسم برنامج التنمية البشرية مدرج في صف توحيد أسماء البرامج.</t>
-        </is>
-      </c>
+          <t>تأكيد العبء الدراسي الفصلي ومدة البرنامج مع كلية القانون، ثم تصحيح أحدهما أو النص على وجوب الدراسة في الفصول الصيفية إن كان ذلك مقصودًا.</t>
+        </is>
+      </c>
+      <c r="L105" s="6" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="8" t="n">
@@ -6493,22 +6501,22 @@
       </c>
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>رسوم الدراسات العليا</t>
+          <t>ماجستير القانون التجاري الدولي MIBL</t>
         </is>
       </c>
       <c r="C106" s="10" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/post_graduate_fees_tf_ro</t>
+          <t>https://pmu.edu.sa/admission/admissions_requirements_milbl_gdp</t>
         </is>
       </c>
       <c r="D106" s="9" t="inlineStr">
         <is>
-          <t>صفحة رسوم الدراسات العليا: عنوان الجدول الأول وتمهيد جدولي الرسوم بالساعة المعتمدة</t>
+          <t>صفحة متطلبات القبول لماجستير القانون التجاري الدولي: الفقرة التعريفية</t>
         </is>
       </c>
       <c r="E106" s="10" t="inlineStr">
         <is>
-          <t>Graduate FULL-TIME Students Tuition … EMBA | SAR 60,000 | SAR 75,000 … Not successfully completing a course in Graduate program for PMU Alumni and non-PMU alumni and having to repeat it will cost as per the credit hour fee as follows:</t>
+          <t>The year 2025 marks another milestone for PMU Law with the approval of the postgraduate program</t>
         </is>
       </c>
       <c r="F106" s="9" t="inlineStr">
@@ -6518,12 +6526,12 @@
       </c>
       <c r="G106" s="9" t="inlineStr">
         <is>
-          <t>أساس الرسوم غير واضح</t>
+          <t>صياغة مرتبطة بتاريخ مضى</t>
         </is>
       </c>
       <c r="H106" s="9" t="inlineStr">
         <is>
-          <t>لا يبين الجدول الأول ما إذا كانت المبالغ عن البرنامج كاملًا أم عن سنة أم فصل، ولا تُنشر رسوم الدوام الجزئي رغم طرح ماجستير إدارة الأعمال بدوام جزئي، ويُقدَّم جدولا الرسوم بالساعة المعتمدة على أنهما تكلفة إعادة المقرر فقط.</t>
+          <t>تستخدم الفقرة التعريفية صياغة تفترض أن عام 2025 هو العام الجاري، وقد أصبحت قديمة.</t>
         </is>
       </c>
       <c r="I106" s="8" t="inlineStr">
@@ -6533,12 +6541,12 @@
       </c>
       <c r="J106" s="8" t="inlineStr">
         <is>
-          <t>متوسطة</t>
+          <t>منخفضة</t>
         </is>
       </c>
       <c r="K106" s="9" t="inlineStr">
         <is>
-          <t>تسمية العمود «إجمالي الرسوم الدراسية للبرنامج» مع بيان جدول السداد، ونشر رسوم الدوام الجزئي أو النص على تطبيق سعر الساعة المعتمدة، وتوضيح نطاق جدولي الساعة المعتمدة، بالتنسيق مع الإدارة المالية.</t>
+          <t>إعادة الصياغة بصيغة ثابتة، مثل: «In 2025, the Ministry of Education approved the Master of Arts (MA) in International Business Law…».</t>
         </is>
       </c>
       <c r="L106" s="9" t="inlineStr"/>
@@ -6549,42 +6557,42 @@
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>رسوم الدراسات العليا</t>
+          <t>ماجستير القانون التجاري الدولي MIBL</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/post_graduate_fees_tf_ro</t>
+          <t>https://pmu.edu.sa/admission/admissions_requirements_milbl_gdp</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>صفحة رسوم الدراسات العليا: جدولا الرسوم؛ وصفحة برامج الدراسات العليا: عناوين البرامج؛ وصفحتا متطلبات دكتوراه الهندسة الميكانيكية وماجستير التنمية البشرية</t>
+          <t>صفحة متطلبات القبول لماجستير القانون التجاري الدولي: الفقرة التعريفية</t>
         </is>
       </c>
       <c r="E107" s="7" t="inlineStr">
         <is>
-          <t>Master of Science in Human Development … Master of Science in Education and Human Development | 1,191 SAR /Credit hour … Doctoral program in Mechanical Engineering (72) … [Graduate Admissions] Doctorate in Mechanical Engineering Program … Admission to the Master of Human Development</t>
+          <t>admission on a part-time basis may be considered subject to the applicable regulation, delivered and facilitated by qualified and experienced academics in the respective areas.</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr">
         <is>
-          <t>الاتساق</t>
+          <t>لغوي ونحوي</t>
         </is>
       </c>
       <c r="G107" s="6" t="inlineStr">
         <is>
-          <t>عدم توحيد أسماء البرامج</t>
+          <t>جملة طويلة متداخلة</t>
         </is>
       </c>
       <c r="H107" s="6" t="inlineStr">
         <is>
-          <t>يرد البرنامج الواحد بأسماء مختلفة: دكتوراه الهندسة الميكانيكية باسم «Doctoral program» في صفحة الرسوم و«Doctorate» في صفحة البرامج و«PhD» في صفحة المتطلبات، وماجستير التنمية البشرية باسم «Human Development» و«Education and Human Development» في صفحة الرسوم نفسها و«Master of Human Development» في صفحة البرامج.</t>
+          <t>تدمج الجملة موضوع القبول بدوام جزئي مع موضوع تقديم البرنامج من قِبل أكاديميين مؤهلين في جملة واحدة، فيلتبس المعنى.</t>
         </is>
       </c>
       <c r="I107" s="5" t="inlineStr">
         <is>
-          <t>تصحيح مطلوب</t>
+          <t>توصية تحسين</t>
         </is>
       </c>
       <c r="J107" s="5" t="inlineStr">
@@ -6594,7 +6602,7 @@
       </c>
       <c r="K107" s="6" t="inlineStr">
         <is>
-          <t>اعتماد اسم رسمي واحد لكل برنامج من عمادة الدراسات العليا (مثل «PhD in Mechanical Engineering» و«Master of Science in Human Development») واستخدامه في جميع الصفحات وجداول الرسوم.</t>
+          <t>تقسيم الجملة إلى جملتين، مثل: «...subject to the applicable regulations. The program is delivered by qualified and experienced academics in the respective areas.»</t>
         </is>
       </c>
       <c r="L107" s="6" t="inlineStr"/>
@@ -6615,45 +6623,49 @@
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>صفحة رسوم الدراسات العليا: جدول الرسوم بالساعة المعتمدة</t>
+          <t>صفحة رسوم الدراسات العليا: جدول الرسوم الدراسية الكاملة؛ وصفحة قائمة التخصصات</t>
         </is>
       </c>
       <c r="E108" s="10" t="inlineStr">
         <is>
-          <t>2,083.3 SAR /Credit hour … 1,818.18 SAR /Credit hour … 1,191 SAR /Credit hour</t>
+          <t>Master of Engineering in Innovation, Sustainability, and Entrepreneurship (33) | SAR 80,000 | SAR 80,000 … PRE-Master for Master of Education | NA | SAR 30,000 … [List of Majors] Master of Science in Engineering Innovation, Sustainability, and Entrepreneurship</t>
         </is>
       </c>
       <c r="F108" s="9" t="inlineStr">
         <is>
-          <t>الاتساق</t>
+          <t>دقة المعلومات</t>
         </is>
       </c>
       <c r="G108" s="9" t="inlineStr">
         <is>
-          <t>تفاوت في دقة الأرقام</t>
+          <t>برامج مسعّرة دون صفحة قبول</t>
         </is>
       </c>
       <c r="H108" s="9" t="inlineStr">
         <is>
-          <t>تُعرض أسعار الساعة المعتمدة بدرجات دقة مختلفة (بلا كسور، وبمنزلة عشرية واحدة، وبمنزلتين).</t>
+          <t>يتضمن جدول رسوم الدراسات العليا رسومًا لبرنامج ماجستير الهندسة في الابتكار والاستدامة وريادة الأعمال ولبرنامج «ما قبل الماجستير لماجستير التربية»، ولا توجد لهما صفحة قبول ولا إدراج في صفحة برامج الدراسات العليا أو صفحة الدرجات والبرامج، كما يرد اسم الأول بصيغة مختلفة في قائمة التخصصات.</t>
         </is>
       </c>
       <c r="I108" s="8" t="inlineStr">
         <is>
-          <t>توصية تحسين</t>
+          <t>متابعة وتحقق</t>
         </is>
       </c>
       <c r="J108" s="8" t="inlineStr">
         <is>
-          <t>منخفضة</t>
+          <t>متوسطة</t>
         </is>
       </c>
       <c r="K108" s="9" t="inlineStr">
         <is>
-          <t>عرض جميع الأسعار بمنزلتين عشريتين (مثل: 2,083.33) بعد تأكيد القيم من الإدارة المالية.</t>
-        </is>
-      </c>
-      <c r="L108" s="9" t="inlineStr"/>
+          <t>تأكيد حالة طرح البرنامجين من عمادة الدراسات العليا والإدارة المالية، ثم إما إضافة صفحة قبول ورابط تقديم لكل برنامج مطروح، أو حذف صفّي الرسوم، مع توحيد الاسم الرسمي.</t>
+        </is>
+      </c>
+      <c r="L108" s="9" t="inlineStr">
+        <is>
+          <t>الجزء من الملاحظة الخاص باختلاف اسم برنامج التنمية البشرية مدرج في صف توحيد أسماء البرامج.</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="n">
@@ -6671,12 +6683,12 @@
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>صفحة رسوم الدراسات العليا: جدول رسوم الطلاب المستمرين</t>
+          <t>صفحة رسوم الدراسات العليا: عنوان الجدول الأول وتمهيد جدولي الرسوم بالساعة المعتمدة</t>
         </is>
       </c>
       <c r="E109" s="7" t="inlineStr">
         <is>
-          <t>EMBA - Continuing Students (Admitted before Fall Semester 2025/2026) | 1,334 SAR /Credit hour | 1,667 SAR /Credit hour … MBA - Continuing Students (Admitted before Fall Semester 2025/2026) | 1,354 SAR /Credit hour</t>
+          <t>Graduate FULL-TIME Students Tuition … EMBA | SAR 60,000 | SAR 75,000 … Not successfully completing a course in Graduate program for PMU Alumni and non-PMU alumni and having to repeat it will cost as per the credit hour fee as follows:</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr">
@@ -6686,27 +6698,27 @@
       </c>
       <c r="G109" s="6" t="inlineStr">
         <is>
-          <t>قيمة تحتاج إلى تأكيد</t>
+          <t>أساس الرسوم غير واضح</t>
         </is>
       </c>
       <c r="H109" s="6" t="inlineStr">
         <is>
-          <t>يختلف سعر الساعة لخريجي الجامعة المستمرين في ماجستير إدارة الأعمال التنفيذي (1,334 ريالًا) عنه في ماجستير إدارة الأعمال (1,354 ريالًا) بفارق 20 ريالًا، مع تطابق سعر غير الخريجين (1,667 ريالًا) في البرنامجين.</t>
+          <t>لا يبين الجدول الأول ما إذا كانت المبالغ عن البرنامج كاملًا أم عن سنة أم فصل، ولا تُنشر رسوم الدوام الجزئي رغم طرح ماجستير إدارة الأعمال بدوام جزئي، ويُقدَّم جدولا الرسوم بالساعة المعتمدة على أنهما تكلفة إعادة المقرر فقط.</t>
         </is>
       </c>
       <c r="I109" s="5" t="inlineStr">
         <is>
-          <t>متابعة وتحقق</t>
+          <t>توصية تحسين</t>
         </is>
       </c>
       <c r="J109" s="5" t="inlineStr">
         <is>
-          <t>منخفضة</t>
+          <t>متوسطة</t>
         </is>
       </c>
       <c r="K109" s="6" t="inlineStr">
         <is>
-          <t>تأكيد القيمتين من الإدارة المالية وتصحيح أيٍّ منهما إن كان الفارق خطأً مطبعيًا.</t>
+          <t>تسمية العمود «إجمالي الرسوم الدراسية للبرنامج» مع بيان جدول السداد، ونشر رسوم الدوام الجزئي أو النص على تطبيق سعر الساعة المعتمدة، وتوضيح نطاق جدولي الساعة المعتمدة، بالتنسيق مع الإدارة المالية.</t>
         </is>
       </c>
       <c r="L109" s="6" t="inlineStr"/>
@@ -6727,32 +6739,32 @@
       </c>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>صفحة رسوم الدراسات العليا: القائمة الجانبية (رسوم البكالوريوس وجداول السداد)</t>
+          <t>صفحة رسوم الدراسات العليا: جدولا الرسوم؛ وصفحة برامج الدراسات العليا: عناوين البرامج؛ وصفحتا متطلبات دكتوراه الهندسة الميكانيكية وماجستير التنمية البشرية</t>
         </is>
       </c>
       <c r="E110" s="10" t="inlineStr">
         <is>
-          <t>Undergraduate Fees for Continuing 2024-2025 … Payment Schedule … Spring Semester 2025/2026 … Summer Semester 2025/2026 … Fall Semester 2026/2027</t>
+          <t>Master of Science in Human Development … Master of Science in Education and Human Development | 1,191 SAR /Credit hour … Doctoral program in Mechanical Engineering (72) … [Graduate Admissions] Doctorate in Mechanical Engineering Program … Admission to the Master of Human Development</t>
         </is>
       </c>
       <c r="F110" s="9" t="inlineStr">
         <is>
-          <t>تنظيمي</t>
+          <t>الاتساق</t>
         </is>
       </c>
       <c r="G110" s="9" t="inlineStr">
         <is>
-          <t>روابط بتسميات قديمة</t>
+          <t>عدم توحيد أسماء البرامج</t>
         </is>
       </c>
       <c r="H110" s="9" t="inlineStr">
         <is>
-          <t>تعرض القائمة الجانبية جدولي سداد فصلي الربيع والصيف 2025/2026 اللذين انقضت مواعيدهما، إلى جانب جدول خريف 2026/2027، ويبدو عنوان رابط «Undergraduate Fees for Continuing 2024-2025» قديمًا مع أن الصفحة المرتبطة به تحدد الرسوم الحالية للطلاب المقبولين قبل خريف 2025/2026.</t>
+          <t>يرد البرنامج الواحد بأسماء مختلفة: دكتوراه الهندسة الميكانيكية باسم «Doctoral program» في صفحة الرسوم و«Doctorate» في صفحة البرامج و«PhD» في صفحة المتطلبات، وماجستير التنمية البشرية باسم «Human Development» و«Education and Human Development» في صفحة الرسوم نفسها و«Master of Human Development» في صفحة البرامج.</t>
         </is>
       </c>
       <c r="I110" s="8" t="inlineStr">
         <is>
-          <t>توصية تحسين</t>
+          <t>تصحيح مطلوب</t>
         </is>
       </c>
       <c r="J110" s="8" t="inlineStr">
@@ -6762,7 +6774,7 @@
       </c>
       <c r="K110" s="9" t="inlineStr">
         <is>
-          <t>أرشفة جدولي 2025/2026 المنقضيين أو إزالتهما وإضافة جداول 2026/2027 عند توفرها، وإعادة تسمية الرابط إلى «Undergraduate Fees – Continuing Students (admitted before Fall 2025/2026)».</t>
+          <t>اعتماد اسم رسمي واحد لكل برنامج من عمادة الدراسات العليا (مثل «PhD in Mechanical Engineering» و«Master of Science in Human Development») واستخدامه في جميع الصفحات وجداول الرسوم.</t>
         </is>
       </c>
       <c r="L110" s="9" t="inlineStr"/>
@@ -6773,37 +6785,37 @@
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>معلومات التواصل – الدراسات العليا</t>
+          <t>رسوم الدراسات العليا</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/admission_contact_gdp</t>
+          <t>https://pmu.edu.sa/admission/post_graduate_fees_tf_ro</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>صفحة معلومات التواصل للدراسات العليا: قسم «Contact Info»</t>
+          <t>صفحة رسوم الدراسات العليا: جدول الرسوم بالساعة المعتمدة</t>
         </is>
       </c>
       <c r="E111" s="7" t="inlineStr">
         <is>
-          <t>Graduate Study Admission Coordinator … Office: G-017 Admin Bld … Email: graduateadm@pmu.edu.sa</t>
+          <t>2,083.3 SAR /Credit hour … 1,818.18 SAR /Credit hour … 1,191 SAR /Credit hour</t>
         </is>
       </c>
       <c r="F111" s="6" t="inlineStr">
         <is>
-          <t>تجربة المستخدم</t>
+          <t>الاتساق</t>
         </is>
       </c>
       <c r="G111" s="6" t="inlineStr">
         <is>
-          <t>معلومات تواصل ناقصة</t>
+          <t>تفاوت في دقة الأرقام</t>
         </is>
       </c>
       <c r="H111" s="6" t="inlineStr">
         <is>
-          <t>تقتصر الصفحة على بريد إلكتروني ورقم مكتب مختصر، دون رقم هاتف أو ساعات عمل أو بيان الحرم (طلاب/طالبات) أو الاسم الكامل للمبنى.</t>
+          <t>تُعرض أسعار الساعة المعتمدة بدرجات دقة مختلفة (بلا كسور، وبمنزلة عشرية واحدة، وبمنزلتين).</t>
         </is>
       </c>
       <c r="I111" s="5" t="inlineStr">
@@ -6813,12 +6825,12 @@
       </c>
       <c r="J111" s="5" t="inlineStr">
         <is>
-          <t>متوسطة</t>
+          <t>منخفضة</t>
         </is>
       </c>
       <c r="K111" s="6" t="inlineStr">
         <is>
-          <t>إضافة رقم الهاتف وساعات العمل وبيانات الحرم والاسم الكامل للمبنى.</t>
+          <t>عرض جميع الأسعار بمنزلتين عشريتين (مثل: 2,083.33) بعد تأكيد القيم من الإدارة المالية.</t>
         </is>
       </c>
       <c r="L111" s="6" t="inlineStr"/>
@@ -6829,22 +6841,22 @@
       </c>
       <c r="B112" s="9" t="inlineStr">
         <is>
-          <t>رسوم البكالوريوس</t>
+          <t>رسوم الدراسات العليا</t>
         </is>
       </c>
       <c r="C112" s="10" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/fees_tf_ro</t>
+          <t>https://pmu.edu.sa/admission/post_graduate_fees_tf_ro</t>
         </is>
       </c>
       <c r="D112" s="9" t="inlineStr">
         <is>
-          <t>القائمة الجانبية – Payment Schedule</t>
+          <t>صفحة رسوم الدراسات العليا: جدول رسوم الطلاب المستمرين</t>
         </is>
       </c>
       <c r="E112" s="10" t="inlineStr">
         <is>
-          <t>Payment Schedule / Spring Semester 2025/2026 / Summer Semester 2025/2026 / Fall Semester 2026/2027</t>
+          <t>EMBA - Continuing Students (Admitted before Fall Semester 2025/2026) | 1,334 SAR /Credit hour | 1,667 SAR /Credit hour … MBA - Continuing Students (Admitted before Fall Semester 2025/2026) | 1,354 SAR /Credit hour</t>
         </is>
       </c>
       <c r="F112" s="9" t="inlineStr">
@@ -6854,34 +6866,30 @@
       </c>
       <c r="G112" s="9" t="inlineStr">
         <is>
-          <t>جداول سداد منتهية</t>
+          <t>قيمة تحتاج إلى تأكيد</t>
         </is>
       </c>
       <c r="H112" s="9" t="inlineStr">
         <is>
-          <t>لا تزال قائمة جداول السداد تعرض جدولي الفصل الثاني والفصل الصيفي للعام 2025/2026، وقد انقضت مواعيد أقساطهما (من مارس إلى مايو 2026 للفصل الثاني، ومن يوليو إلى أغسطس 2026 للفصل الصيفي).</t>
+          <t>يختلف سعر الساعة لخريجي الجامعة المستمرين في ماجستير إدارة الأعمال التنفيذي (1,334 ريالًا) عنه في ماجستير إدارة الأعمال (1,354 ريالًا) بفارق 20 ريالًا، مع تطابق سعر غير الخريجين (1,667 ريالًا) في البرنامجين.</t>
         </is>
       </c>
       <c r="I112" s="8" t="inlineStr">
         <is>
-          <t>تصحيح مطلوب</t>
+          <t>متابعة وتحقق</t>
         </is>
       </c>
       <c r="J112" s="8" t="inlineStr">
         <is>
-          <t>متوسطة</t>
+          <t>منخفضة</t>
         </is>
       </c>
       <c r="K112" s="9" t="inlineStr">
         <is>
-          <t>أرشفة هذين الرابطين أو استبدالهما بجدولي الفصل الثاني والفصل الصيفي للعام 2026/2027 فور اعتمادهما من الجهة المالكة.</t>
-        </is>
-      </c>
-      <c r="L112" s="9" t="inlineStr">
-        <is>
-          <t>تواريخ الفصل الصيفي (يوليو–أغسطس 2026) أُضيفت بعد التحقق من صفحة الجدول نفسها.</t>
-        </is>
-      </c>
+          <t>تأكيد القيمتين من الإدارة المالية وتصحيح أيٍّ منهما إن كان الفارق خطأً مطبعيًا.</t>
+        </is>
+      </c>
+      <c r="L112" s="9" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="5" t="n">
@@ -6889,37 +6897,37 @@
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>رسوم البكالوريوس</t>
+          <t>رسوم الدراسات العليا</t>
         </is>
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/fees_tf_ro</t>
+          <t>https://pmu.edu.sa/admission/post_graduate_fees_tf_ro</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr">
         <is>
-          <t>القائمة الجانبية لرسوم البكالوريوس وقائمة الروابط داخل الصفحة</t>
+          <t>صفحة رسوم الدراسات العليا: القائمة الجانبية (رسوم البكالوريوس وجداول السداد)</t>
         </is>
       </c>
       <c r="E113" s="7" t="inlineStr">
         <is>
-          <t>Undergraduate Fees for Continuing 2024-2025 … Continuing Students 2024–2025</t>
+          <t>Undergraduate Fees for Continuing 2024-2025 … Payment Schedule … Spring Semester 2025/2026 … Summer Semester 2025/2026 … Fall Semester 2026/2027</t>
         </is>
       </c>
       <c r="F113" s="6" t="inlineStr">
         <is>
-          <t>دقة المعلومات</t>
+          <t>تنظيمي</t>
         </is>
       </c>
       <c r="G113" s="6" t="inlineStr">
         <is>
-          <t>تسمية توحي بمعلومة قديمة</t>
+          <t>روابط بتسميات قديمة</t>
         </is>
       </c>
       <c r="H113" s="6" t="inlineStr">
         <is>
-          <t>يحمل رابط رسوم الطلاب المستمرين في القائمة الجانبية وفي قائمة الصفحة تسمية العام 2024–2025، في حين أن الصفحة المستهدفة تنص على أنها تخص الطلاب المقبولين قبل الفصل الدراسي الأول 2025/2026، مما يوحي للقارئ بأن جدول الرسوم منتهي الصلاحية.</t>
+          <t>تعرض القائمة الجانبية جدولي سداد فصلي الربيع والصيف 2025/2026 اللذين انقضت مواعيدهما، إلى جانب جدول خريف 2026/2027، ويبدو عنوان رابط «Undergraduate Fees for Continuing 2024-2025» قديمًا مع أن الصفحة المرتبطة به تحدد الرسوم الحالية للطلاب المقبولين قبل خريف 2025/2026.</t>
         </is>
       </c>
       <c r="I113" s="5" t="inlineStr">
@@ -6934,7 +6942,7 @@
       </c>
       <c r="K113" s="6" t="inlineStr">
         <is>
-          <t>تعديل التسمية في الموضعين لتصف الفئة المعنية (مثل: «Continuing Students admitted before Fall 2025/2026») أو استبدالها بجدول رسوم الطلاب المستمرين للعام الحالي، وذلك بعد تأكيد مكتب التسجيل.</t>
+          <t>أرشفة جدولي 2025/2026 المنقضيين أو إزالتهما وإضافة جداول 2026/2027 عند توفرها، وإعادة تسمية الرابط إلى «Undergraduate Fees – Continuing Students (admitted before Fall 2025/2026)».</t>
         </is>
       </c>
       <c r="L113" s="6" t="inlineStr"/>
@@ -6945,37 +6953,37 @@
       </c>
       <c r="B114" s="9" t="inlineStr">
         <is>
-          <t>رسوم البكالوريوس</t>
+          <t>معلومات التواصل – الدراسات العليا</t>
         </is>
       </c>
       <c r="C114" s="10" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/fees_tf_ro</t>
+          <t>https://pmu.edu.sa/admission/admission_contact_gdp</t>
         </is>
       </c>
       <c r="D114" s="9" t="inlineStr">
         <is>
-          <t>القائمة الجانبية وقائمة الروابط داخل صفحة رسوم البكالوريوس</t>
+          <t>صفحة معلومات التواصل للدراسات العليا: قسم «Contact Info»</t>
         </is>
       </c>
       <c r="E114" s="10" t="inlineStr">
         <is>
-          <t>Medical Program Studies / Undergraduate Fees Intake 2026/2027 … Undergraduate Fees for Continuing 2024-2025 … Payment Schedule … Fall Semester 2026/2027 … Medical Program Fees / Fall Semester 2026/2027 / Fall Semester 2025/2026 / Continuing Students 2024–2025</t>
+          <t>Graduate Study Admission Coordinator … Office: G-017 Admin Bld … Email: graduateadm@pmu.edu.sa</t>
         </is>
       </c>
       <c r="F114" s="9" t="inlineStr">
         <is>
-          <t>الاتساق</t>
+          <t>تجربة المستخدم</t>
         </is>
       </c>
       <c r="G114" s="9" t="inlineStr">
         <is>
-          <t>عدم اتساق التسميات</t>
+          <t>معلومات تواصل ناقصة</t>
         </is>
       </c>
       <c r="H114" s="9" t="inlineStr">
         <is>
-          <t>تختلف تسميات الروابط نفسها بين القائمة الجانبية وقائمة الصفحة: فرسوم الدفعة الجديدة تُسمّى «Undergraduate Fees Intake» في القائمة و«Fall Semester» في الصفحة (وهي التسمية ذاتها المستخدمة لجدول السداد)، ورسوم البرنامج الطبي تُسمّى «Medical Program Studies» مرة و«Medical Program Fees» مرة أخرى، كما يُكتب العام الدراسي بثلاث صيغ مختلفة (2024-2025 و2024–2025 و2026/2027).</t>
+          <t>تقتصر الصفحة على بريد إلكتروني ورقم مكتب مختصر، دون رقم هاتف أو ساعات عمل أو بيان الحرم (طلاب/طالبات) أو الاسم الكامل للمبنى.</t>
         </is>
       </c>
       <c r="I114" s="8" t="inlineStr">
@@ -6985,12 +6993,12 @@
       </c>
       <c r="J114" s="8" t="inlineStr">
         <is>
-          <t>منخفضة</t>
+          <t>متوسطة</t>
         </is>
       </c>
       <c r="K114" s="9" t="inlineStr">
         <is>
-          <t>توحيد التسميات: «Undergraduate Fees – Intake 2026/2027» و«Intake 2025/2026» لروابط الرسوم، وقصر «Fall Semester» على جداول السداد، واعتماد «Medical Program Fees» في الموضعين، وكتابة الأعوام الدراسية بصيغة واحدة مثل «2026/2027».</t>
+          <t>إضافة رقم الهاتف وساعات العمل وبيانات الحرم والاسم الكامل للمبنى.</t>
         </is>
       </c>
       <c r="L114" s="9" t="inlineStr"/>
@@ -7011,27 +7019,27 @@
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
-          <t>القائمة الجانبية – بند رسوم الدراسات العليا</t>
+          <t>القائمة الجانبية – Payment Schedule</t>
         </is>
       </c>
       <c r="E115" s="7" t="inlineStr">
         <is>
-          <t>Post Graduate Fees</t>
+          <t>Payment Schedule / Spring Semester 2025/2026 / Summer Semester 2025/2026 / Fall Semester 2026/2027</t>
         </is>
       </c>
       <c r="F115" s="6" t="inlineStr">
         <is>
-          <t>لغوي ونحوي</t>
+          <t>دقة المعلومات</t>
         </is>
       </c>
       <c r="G115" s="6" t="inlineStr">
         <is>
-          <t>صيغة كتابة غير قياسية</t>
+          <t>جداول سداد منتهية</t>
         </is>
       </c>
       <c r="H115" s="6" t="inlineStr">
         <is>
-          <t>يُكتب بند رسوم الدراسات العليا بصيغة «Post Graduate» المنفصلة، وهي صيغة غير قياسية.</t>
+          <t>لا تزال قائمة جداول السداد تعرض جدولي الفصل الثاني والفصل الصيفي للعام 2025/2026، وقد انقضت مواعيد أقساطهما (من مارس إلى مايو 2026 للفصل الثاني، ومن يوليو إلى أغسطس 2026 للفصل الصيفي).</t>
         </is>
       </c>
       <c r="I115" s="5" t="inlineStr">
@@ -7041,15 +7049,19 @@
       </c>
       <c r="J115" s="5" t="inlineStr">
         <is>
-          <t>منخفضة</t>
+          <t>متوسطة</t>
         </is>
       </c>
       <c r="K115" s="6" t="inlineStr">
         <is>
-          <t>تعديلها إلى «Postgraduate Fees» أو «Graduate Fees» اتساقًا مع تسمية «Graduate Admissions».</t>
-        </is>
-      </c>
-      <c r="L115" s="6" t="inlineStr"/>
+          <t>أرشفة هذين الرابطين أو استبدالهما بجدولي الفصل الثاني والفصل الصيفي للعام 2026/2027 فور اعتمادهما من الجهة المالكة.</t>
+        </is>
+      </c>
+      <c r="L115" s="6" t="inlineStr">
+        <is>
+          <t>تواريخ الفصل الصيفي (يوليو–أغسطس 2026) أُضيفت بعد التحقق من صفحة الجدول نفسها.</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="8" t="n">
@@ -7057,37 +7069,37 @@
       </c>
       <c r="B116" s="9" t="inlineStr">
         <is>
-          <t>اختبارات اللغة – نظرة عامة</t>
+          <t>رسوم البكالوريوس</t>
         </is>
       </c>
       <c r="C116" s="10" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/overview-undergraduate-placement-tests</t>
+          <t>https://pmu.edu.sa/admission/fees_tf_ro</t>
         </is>
       </c>
       <c r="D116" s="9" t="inlineStr">
         <is>
-          <t>فقرة «English Language Proficiency Tests»</t>
+          <t>القائمة الجانبية لرسوم البكالوريوس وقائمة الروابط داخل الصفحة</t>
         </is>
       </c>
       <c r="E116" s="10" t="inlineStr">
         <is>
-          <t>Candidates with PMU recognized proficiency English language test certificates can verify the admission requirements on the following links IELTS requirements and TOEFL requirements.</t>
+          <t>Undergraduate Fees for Continuing 2024-2025 … Continuing Students 2024–2025</t>
         </is>
       </c>
       <c r="F116" s="9" t="inlineStr">
         <is>
-          <t>تجربة المستخدم</t>
+          <t>دقة المعلومات</t>
         </is>
       </c>
       <c r="G116" s="9" t="inlineStr">
         <is>
-          <t>معلومة ناقصة</t>
+          <t>تسمية توحي بمعلومة قديمة</t>
         </is>
       </c>
       <c r="H116" s="9" t="inlineStr">
         <is>
-          <t>لا تقدم صفحة النظرة العامة على اختبارات اللغة أي ملخص للحد الأدنى من الدرجات أو مدة صلاحية النتائج أو آلية جدولة اختبار Aptis أو جهة تواصل في مكتب القبول، وتعتمد كليًا على الإحالة إلى صفحات الاختبارات المنفردة.</t>
+          <t>يحمل رابط رسوم الطلاب المستمرين في القائمة الجانبية وفي قائمة الصفحة تسمية العام 2024–2025، في حين أن الصفحة المستهدفة تنص على أنها تخص الطلاب المقبولين قبل الفصل الدراسي الأول 2025/2026، مما يوحي للقارئ بأن جدول الرسوم منتهي الصلاحية.</t>
         </is>
       </c>
       <c r="I116" s="8" t="inlineStr">
@@ -7102,7 +7114,7 @@
       </c>
       <c r="K116" s="9" t="inlineStr">
         <is>
-          <t>إضافة جدول مختصر (الاختبار، الحد الأدنى للالتحاق المباشر بالبرنامج الأساسي، مدة الصلاحية، طريقة تقديم النتيجة) مع بيانات التواصل مع مكتب القبول.</t>
+          <t>تعديل التسمية في الموضعين لتصف الفئة المعنية (مثل: «Continuing Students admitted before Fall 2025/2026») أو استبدالها بجدول رسوم الطلاب المستمرين للعام الحالي، وذلك بعد تأكيد مكتب التسجيل.</t>
         </is>
       </c>
       <c r="L116" s="9" t="inlineStr"/>
@@ -7113,42 +7125,42 @@
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>اختبارات اللغة – نظرة عامة</t>
+          <t>رسوم البكالوريوس</t>
         </is>
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/overview-undergraduate-placement-tests</t>
+          <t>https://pmu.edu.sa/admission/fees_tf_ro</t>
         </is>
       </c>
       <c r="D117" s="6" t="inlineStr">
         <is>
-          <t>فقرة «English Language Proficiency Tests»</t>
+          <t>القائمة الجانبية وقائمة الروابط داخل صفحة رسوم البكالوريوس</t>
         </is>
       </c>
       <c r="E117" s="7" t="inlineStr">
         <is>
-          <t>PMU has used international English language proficiency tests for admissions that ensure the accuracy of the outcomes.   Read more  about the current technology used for the English placement test Aptis.</t>
+          <t>Medical Program Studies / Undergraduate Fees Intake 2026/2027 … Undergraduate Fees for Continuing 2024-2025 … Payment Schedule … Fall Semester 2026/2027 … Medical Program Fees / Fall Semester 2026/2027 / Fall Semester 2025/2026 / Continuing Students 2024–2025</t>
         </is>
       </c>
       <c r="F117" s="6" t="inlineStr">
         <is>
-          <t>لغوي ونحوي</t>
+          <t>الاتساق</t>
         </is>
       </c>
       <c r="G117" s="6" t="inlineStr">
         <is>
-          <t>صياغة ركيكة</t>
+          <t>عدم اتساق التسميات</t>
         </is>
       </c>
       <c r="H117" s="6" t="inlineStr">
         <is>
-          <t>تستخدم الجملة الأولى زمنًا غير مناسب وصياغة ركيكة، وتصف الجملة الثانية اختبار Aptis بأنه «التقنية الحالية» لاختبار تحديد المستوى، وهو وصف غير دقيق.</t>
+          <t>تختلف تسميات الروابط نفسها بين القائمة الجانبية وقائمة الصفحة: فرسوم الدفعة الجديدة تُسمّى «Undergraduate Fees Intake» في القائمة و«Fall Semester» في الصفحة (وهي التسمية ذاتها المستخدمة لجدول السداد)، ورسوم البرنامج الطبي تُسمّى «Medical Program Studies» مرة و«Medical Program Fees» مرة أخرى، كما يُكتب العام الدراسي بثلاث صيغ مختلفة (2024-2025 و2024–2025 و2026/2027).</t>
         </is>
       </c>
       <c r="I117" s="5" t="inlineStr">
         <is>
-          <t>تصحيح مطلوب</t>
+          <t>توصية تحسين</t>
         </is>
       </c>
       <c r="J117" s="5" t="inlineStr">
@@ -7158,7 +7170,7 @@
       </c>
       <c r="K117" s="6" t="inlineStr">
         <is>
-          <t>إعادة الصياغة إلى: «PMU uses internationally recognised English proficiency tests to place candidates accurately.» و«Read more about Aptis, the English placement test used by PMU.»</t>
+          <t>توحيد التسميات: «Undergraduate Fees – Intake 2026/2027» و«Intake 2025/2026» لروابط الرسوم، وقصر «Fall Semester» على جداول السداد، واعتماد «Medical Program Fees» في الموضعين، وكتابة الأعوام الدراسية بصيغة واحدة مثل «2026/2027».</t>
         </is>
       </c>
       <c r="L117" s="6" t="inlineStr"/>
@@ -7169,37 +7181,37 @@
       </c>
       <c r="B118" s="9" t="inlineStr">
         <is>
-          <t>اختبار Aptis</t>
+          <t>رسوم البكالوريوس</t>
         </is>
       </c>
       <c r="C118" s="10" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/aptis-placement-test</t>
+          <t>https://pmu.edu.sa/admission/fees_tf_ro</t>
         </is>
       </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
-          <t>الفقرة الخاصة بالالتحاق المباشر بالبرنامج الأساسي (Core Program)</t>
+          <t>القائمة الجانبية – بند رسوم الدراسات العليا</t>
         </is>
       </c>
       <c r="E118" s="10" t="inlineStr">
         <is>
-          <t>If a candidate feels that he/she is eligible for direct entry into the Core Program, he/she will be required to take the IELTS through the PMU Testing Center or any other authorized testing center</t>
+          <t>Post Graduate Fees</t>
         </is>
       </c>
       <c r="F118" s="9" t="inlineStr">
         <is>
-          <t>دقة المعلومات</t>
+          <t>لغوي ونحوي</t>
         </is>
       </c>
       <c r="G118" s="9" t="inlineStr">
         <is>
-          <t>تعارض في الاختبارات المقبولة</t>
+          <t>صيغة كتابة غير قياسية</t>
         </is>
       </c>
       <c r="H118" s="9" t="inlineStr">
         <is>
-          <t>تشترط صفحة Aptis اختبار IELTS وحده للالتحاق المباشر بالبرنامج الأساسي، في حين تقبل صفحة TOEFL وصفحة التقديم (/apply) نتيجة TOEFL iBT أيضًا (83 إجمالًا و19 في الكتابة).</t>
+          <t>يُكتب بند رسوم الدراسات العليا بصيغة «Post Graduate» المنفصلة، وهي صيغة غير قياسية.</t>
         </is>
       </c>
       <c r="I118" s="8" t="inlineStr">
@@ -7209,12 +7221,12 @@
       </c>
       <c r="J118" s="8" t="inlineStr">
         <is>
-          <t>متوسطة</t>
+          <t>منخفضة</t>
         </is>
       </c>
       <c r="K118" s="9" t="inlineStr">
         <is>
-          <t>تعديل الجملة لتنص على قبول نتيجة سارية من IELTS Academic أو TOEFL iBT تستوفي الحد الأدنى للبرنامج الأساسي، مع الإحالة إلى صفحتي IELTS وTOEFL.</t>
+          <t>تعديلها إلى «Postgraduate Fees» أو «Graduate Fees» اتساقًا مع تسمية «Graduate Admissions».</t>
         </is>
       </c>
       <c r="L118" s="9" t="inlineStr"/>
@@ -7225,27 +7237,27 @@
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>اختبار Aptis</t>
+          <t>اختبارات اللغة – نظرة عامة</t>
         </is>
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/aptis-placement-test</t>
+          <t>https://pmu.edu.sa/admission/overview-undergraduate-placement-tests</t>
         </is>
       </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
-          <t>جدول المستويات بعد فقرة الإحالة إلى دليل المرشح</t>
+          <t>فقرة «English Language Proficiency Tests»</t>
         </is>
       </c>
       <c r="E119" s="7" t="inlineStr">
         <is>
-          <t>Based on candidates overall and writing scores, they will be placed on one of the following levels: … Level / Pre Beginner / Beginner / Intermediate / Advanced … direct entry into the Core Program</t>
+          <t>Candidates with PMU recognized proficiency English language test certificates can verify the admission requirements on the following links IELTS requirements and TOEFL requirements.</t>
         </is>
       </c>
       <c r="F119" s="6" t="inlineStr">
         <is>
-          <t>دقة المعلومات</t>
+          <t>تجربة المستخدم</t>
         </is>
       </c>
       <c r="G119" s="6" t="inlineStr">
@@ -7255,7 +7267,7 @@
       </c>
       <c r="H119" s="6" t="inlineStr">
         <is>
-          <t>تذكر الصفحة أن التسكين يعتمد على الدرجة الإجمالية ودرجة الكتابة، لكن جدول المستويات لا يتضمن أي درجات Aptis أو مستويات الإطار الأوروبي المرجعي (CEFR) المقابلة لكل مستوى، خلافًا لصفحتي IELTS وTOEFL، كما لا تشرح المقصود بـ«Core Program».</t>
+          <t>لا تقدم صفحة النظرة العامة على اختبارات اللغة أي ملخص للحد الأدنى من الدرجات أو مدة صلاحية النتائج أو آلية جدولة اختبار Aptis أو جهة تواصل في مكتب القبول، وتعتمد كليًا على الإحالة إلى صفحات الاختبارات المنفردة.</t>
         </is>
       </c>
       <c r="I119" s="5" t="inlineStr">
@@ -7265,19 +7277,15 @@
       </c>
       <c r="J119" s="5" t="inlineStr">
         <is>
-          <t>متوسطة</t>
+          <t>منخفضة</t>
         </is>
       </c>
       <c r="K119" s="6" t="inlineStr">
         <is>
-          <t>نشر نطاق الدرجة الإجمالية ودرجة الكتابة (أو مستوى CEFR) لكل مستوى كما يعتمده مكتب القبول، مع تعريف موجز بالبرنامج الأساسي.</t>
-        </is>
-      </c>
-      <c r="L119" s="6" t="inlineStr">
-        <is>
-          <t>الأولوية متوسطة وفق الملاحظة التفصيلية الأعلى أولوية ضمن العنصرين المدمجين؛ يتطلب نشر النطاقات اعتمادها من الجهة المالكة.</t>
-        </is>
-      </c>
+          <t>إضافة جدول مختصر (الاختبار، الحد الأدنى للالتحاق المباشر بالبرنامج الأساسي، مدة الصلاحية، طريقة تقديم النتيجة) مع بيانات التواصل مع مكتب القبول.</t>
+        </is>
+      </c>
+      <c r="L119" s="6" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="8" t="n">
@@ -7285,52 +7293,52 @@
       </c>
       <c r="B120" s="9" t="inlineStr">
         <is>
-          <t>اختبار Aptis</t>
+          <t>اختبارات اللغة – نظرة عامة</t>
         </is>
       </c>
       <c r="C120" s="10" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/aptis-placement-test</t>
+          <t>https://pmu.edu.sa/admission/overview-undergraduate-placement-tests</t>
         </is>
       </c>
       <c r="D120" s="9" t="inlineStr">
         <is>
-          <t>فقرة جدولة الاختبار ومدته</t>
+          <t>فقرة «English Language Proficiency Tests»</t>
         </is>
       </c>
       <c r="E120" s="10" t="inlineStr">
         <is>
-          <t>Once the candidates meet the admission’s general requirements, they will be scheduled to take Aptis test (visit Aptis webpage) … The duration of the placement test is approximately 4 hours.</t>
+          <t>PMU has used international English language proficiency tests for admissions that ensure the accuracy of the outcomes.   Read more  about the current technology used for the English placement test Aptis.</t>
         </is>
       </c>
       <c r="F120" s="9" t="inlineStr">
         <is>
-          <t>دقة المعلومات</t>
+          <t>لغوي ونحوي</t>
         </is>
       </c>
       <c r="G120" s="9" t="inlineStr">
         <is>
-          <t>معلومات إجرائية ناقصة</t>
+          <t>صياغة ركيكة</t>
         </is>
       </c>
       <c r="H120" s="9" t="inlineStr">
         <is>
-          <t>تكتفي الصفحة بذكر أن المتقدم «سيُجدول» لاختبار Aptis دون بيان آلية الجدولة أو رسوم الاختبار أو قواعد الإعادة أو مدة صلاحية النتيجة أو جهة التواصل، في حين تعرض صفحة الرسوم الأخرى «APTIS Exam Fees SAR 575»، والفترة الوحيدة المنشورة للاختبار في تقويم القبول (17 مايو – 5 يوليو 2026) قد انتهت.</t>
+          <t>تستخدم الجملة الأولى زمنًا غير مناسب وصياغة ركيكة، وتصف الجملة الثانية اختبار Aptis بأنه «التقنية الحالية» لاختبار تحديد المستوى، وهو وصف غير دقيق.</t>
         </is>
       </c>
       <c r="I120" s="8" t="inlineStr">
         <is>
-          <t>توصية تحسين</t>
+          <t>تصحيح مطلوب</t>
         </is>
       </c>
       <c r="J120" s="8" t="inlineStr">
         <is>
-          <t>متوسطة</t>
+          <t>منخفضة</t>
         </is>
       </c>
       <c r="K120" s="9" t="inlineStr">
         <is>
-          <t>إضافة آلية الجدولة ورسوم الاختبار المعتمدة (أو النص على عدم وجودها) وقواعد الإعادة ومدة الصلاحية وجهة التواصل والمواعيد القادمة، بعد تأكيد الرسوم من البرنامج التحضيري والإدارة المالية.</t>
+          <t>إعادة الصياغة إلى: «PMU uses internationally recognised English proficiency tests to place candidates accurately.» و«Read more about Aptis, the English placement test used by PMU.»</t>
         </is>
       </c>
       <c r="L120" s="9" t="inlineStr"/>
@@ -7351,27 +7359,27 @@
       </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
-          <t>فقرات الصفحة وجدول المستويات</t>
+          <t>الفقرة الخاصة بالالتحاق المباشر بالبرنامج الأساسي (Core Program)</t>
         </is>
       </c>
       <c r="E121" s="7" t="inlineStr">
         <is>
-          <t>Aptis is an English language test service provided by British Council … Once the candidates meet the admission’s general requirements, they will be scheduled to take Aptis test … to explore the Aptis before sitting for the test … Based on candidates overall and writing scores … Pre Beginner</t>
+          <t>If a candidate feels that he/she is eligible for direct entry into the Core Program, he/she will be required to take the IELTS through the PMU Testing Center or any other authorized testing center</t>
         </is>
       </c>
       <c r="F121" s="6" t="inlineStr">
         <is>
-          <t>لغوي ونحوي</t>
+          <t>دقة المعلومات</t>
         </is>
       </c>
       <c r="G121" s="6" t="inlineStr">
         <is>
-          <t>أخطاء لغوية متعددة</t>
+          <t>تعارض في الاختبارات المقبولة</t>
         </is>
       </c>
       <c r="H121" s="6" t="inlineStr">
         <is>
-          <t>تتضمن الصفحة عدة أخطاء لغوية: حذف أداة التعريف قبل «British Council» وقبل «Aptis test»، واستخدام ملكية غير صحيحة في «admission’s general requirements»، وصياغة ركيكة في «explore the Aptis»، وغياب علامة الملكية في «candidates»، وكتابة «Pre Beginner» بلا شرطة خلافًا لـ«Pre-Beginner» في صفحتي IELTS وTOEFL.</t>
+          <t>تشترط صفحة Aptis اختبار IELTS وحده للالتحاق المباشر بالبرنامج الأساسي، في حين تقبل صفحة TOEFL وصفحة التقديم (/apply) نتيجة TOEFL iBT أيضًا (83 إجمالًا و19 في الكتابة).</t>
         </is>
       </c>
       <c r="I121" s="5" t="inlineStr">
@@ -7381,12 +7389,12 @@
       </c>
       <c r="J121" s="5" t="inlineStr">
         <is>
-          <t>منخفضة</t>
+          <t>متوسطة</t>
         </is>
       </c>
       <c r="K121" s="6" t="inlineStr">
         <is>
-          <t>التعديل إلى: «provided by the British Council» و«Once candidates meet the general admission requirements, they will be scheduled to take the Aptis test» و«explore the Aptis test format before sitting the test» و«Based on candidates’ overall and writing scores» و«Pre-Beginner».</t>
+          <t>تعديل الجملة لتنص على قبول نتيجة سارية من IELTS Academic أو TOEFL iBT تستوفي الحد الأدنى للبرنامج الأساسي، مع الإحالة إلى صفحتي IELTS وTOEFL.</t>
         </is>
       </c>
       <c r="L121" s="6" t="inlineStr"/>
@@ -7407,12 +7415,12 @@
       </c>
       <c r="D122" s="9" t="inlineStr">
         <is>
-          <t>رابط «Aptis Candidate Guide (Click here)» – ملف PDF مرفق</t>
+          <t>جدول المستويات بعد فقرة الإحالة إلى دليل المرشح</t>
         </is>
       </c>
       <c r="E122" s="10" t="inlineStr">
         <is>
-          <t>Aptis Candidate Guide August 2017</t>
+          <t>Based on candidates overall and writing scores, they will be placed on one of the following levels: … Level / Pre Beginner / Beginner / Intermediate / Advanced … direct entry into the Core Program</t>
         </is>
       </c>
       <c r="F122" s="9" t="inlineStr">
@@ -7422,12 +7430,12 @@
       </c>
       <c r="G122" s="9" t="inlineStr">
         <is>
-          <t>مرجع خارجي قديم</t>
+          <t>معلومة ناقصة</t>
         </is>
       </c>
       <c r="H122" s="9" t="inlineStr">
         <is>
-          <t>تحيل الصفحة إلى نسخة مستضافة من دليل المرشح لاختبار Aptis صادرة في أغسطس 2017 (أُنشئ الملف عام 2017 وعُدّل آخر مرة في مارس 2019)، وقد لا تعكس النسخة الحالية للاختبار.</t>
+          <t>تذكر الصفحة أن التسكين يعتمد على الدرجة الإجمالية ودرجة الكتابة، لكن جدول المستويات لا يتضمن أي درجات Aptis أو مستويات الإطار الأوروبي المرجعي (CEFR) المقابلة لكل مستوى، خلافًا لصفحتي IELTS وTOEFL، كما لا تشرح المقصود بـ«Core Program».</t>
         </is>
       </c>
       <c r="I122" s="8" t="inlineStr">
@@ -7437,17 +7445,17 @@
       </c>
       <c r="J122" s="8" t="inlineStr">
         <is>
-          <t>منخفضة</t>
+          <t>متوسطة</t>
         </is>
       </c>
       <c r="K122" s="9" t="inlineStr">
         <is>
-          <t>استبدال الملف المستضاف برابط إلى موارد المرشحين الحالية على موقع المجلس الثقافي البريطاني بدلًا من استضافة إصدار 2017.</t>
+          <t>نشر نطاق الدرجة الإجمالية ودرجة الكتابة (أو مستوى CEFR) لكل مستوى كما يعتمده مكتب القبول، مع تعريف موجز بالبرنامج الأساسي.</t>
         </is>
       </c>
       <c r="L122" s="9" t="inlineStr">
         <is>
-          <t>بيانات إنشاء الملف وتعديله مأخوذة من خصائص ملف PDF.</t>
+          <t>الأولوية متوسطة وفق الملاحظة التفصيلية الأعلى أولوية ضمن العنصرين المدمجين؛ يتطلب نشر النطاقات اعتمادها من الجهة المالكة.</t>
         </is>
       </c>
     </row>
@@ -7457,22 +7465,22 @@
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>اختبار IELTS</t>
+          <t>اختبار Aptis</t>
         </is>
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/ielts-admission</t>
+          <t>https://pmu.edu.sa/admission/aptis-placement-test</t>
         </is>
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
-          <t>الفقرة التمهيدية وجدول المستويات</t>
+          <t>فقرة جدولة الاختبار ومدته</t>
         </is>
       </c>
       <c r="E123" s="7" t="inlineStr">
         <is>
-          <t>if the candidate provides a valid  IELTS  certificate (Academic version) … The validation of the IELTS certificate | Two years from the date of IELTS test</t>
+          <t>Once the candidates meet the admission’s general requirements, they will be scheduled to take Aptis test (visit Aptis webpage) … The duration of the placement test is approximately 4 hours.</t>
         </is>
       </c>
       <c r="F123" s="6" t="inlineStr">
@@ -7482,12 +7490,12 @@
       </c>
       <c r="G123" s="6" t="inlineStr">
         <is>
-          <t>معلومة ناقصة</t>
+          <t>معلومات إجرائية ناقصة</t>
         </is>
       </c>
       <c r="H123" s="6" t="inlineStr">
         <is>
-          <t>لا توضح صفحة IELTS طريقة تقديم النتيجة أو التحقق منها، ولا ما إذا كانت نتائج IELTS Online أو One Skill Retake مقبولة، في حين تحدد صفحة TOEFL هذه الجوانب («The original TOEFL iBT report has to be sent directly from ETS to PMU»).</t>
+          <t>تكتفي الصفحة بذكر أن المتقدم «سيُجدول» لاختبار Aptis دون بيان آلية الجدولة أو رسوم الاختبار أو قواعد الإعادة أو مدة صلاحية النتيجة أو جهة التواصل، في حين تعرض صفحة الرسوم الأخرى «APTIS Exam Fees SAR 575»، والفترة الوحيدة المنشورة للاختبار في تقويم القبول (17 مايو – 5 يوليو 2026) قد انتهت.</t>
         </is>
       </c>
       <c r="I123" s="5" t="inlineStr">
@@ -7502,14 +7510,10 @@
       </c>
       <c r="K123" s="6" t="inlineStr">
         <is>
-          <t>بيان طريقة تقديم نتيجة IELTS والتحقق منها (مثل رقم نموذج النتيجة أو الإرسال الإلكتروني إلى الجامعة) وصيغ الاختبار المقبولة، وفق ما يعتمده مكتب القبول.</t>
-        </is>
-      </c>
-      <c r="L123" s="6" t="inlineStr">
-        <is>
-          <t>قبول صيغ IELTS Online وOne Skill Retake قرار يعود إلى مكتب القبول.</t>
-        </is>
-      </c>
+          <t>إضافة آلية الجدولة ورسوم الاختبار المعتمدة (أو النص على عدم وجودها) وقواعد الإعادة ومدة الصلاحية وجهة التواصل والمواعيد القادمة، بعد تأكيد الرسوم من البرنامج التحضيري والإدارة المالية.</t>
+        </is>
+      </c>
+      <c r="L123" s="6" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="8" t="n">
@@ -7517,22 +7521,22 @@
       </c>
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>اختبار IELTS</t>
+          <t>اختبار Aptis</t>
         </is>
       </c>
       <c r="C124" s="10" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/ielts-admission</t>
+          <t>https://pmu.edu.sa/admission/aptis-placement-test</t>
         </is>
       </c>
       <c r="D124" s="9" t="inlineStr">
         <is>
-          <t>الفقرة التمهيدية وجدول المستويات (يتكرر النص نفسه في صفحة TOEFL – TOEFL)</t>
+          <t>فقرات الصفحة وجدول المستويات</t>
         </is>
       </c>
       <c r="E124" s="10" t="inlineStr">
         <is>
-          <t>might be admitted to different level in the Preparatory Program … successfully meets one of the below requirements of the categories below … The validation of the IELTS certificate | TOEFL: The validation of the TOEFL iBT report … one of the below minimum requirements of the categories below</t>
+          <t>Aptis is an English language test service provided by British Council … Once the candidates meet the admission’s general requirements, they will be scheduled to take Aptis test … to explore the Aptis before sitting for the test … Based on candidates overall and writing scores … Pre Beginner</t>
         </is>
       </c>
       <c r="F124" s="9" t="inlineStr">
@@ -7542,12 +7546,12 @@
       </c>
       <c r="G124" s="9" t="inlineStr">
         <is>
-          <t>أخطاء لغوية متكررة</t>
+          <t>أخطاء لغوية متعددة</t>
         </is>
       </c>
       <c r="H124" s="9" t="inlineStr">
         <is>
-          <t>في صفحتي IELTS وTOEFL تنقص أداة التنكير في «to different level»، وتتكرر كلمة «below» في الجملة نفسها، وتُستخدم «validation» بدلًا من «validity» في صف مدة الصلاحية.</t>
+          <t>تتضمن الصفحة عدة أخطاء لغوية: حذف أداة التعريف قبل «British Council» وقبل «Aptis test»، واستخدام ملكية غير صحيحة في «admission’s general requirements»، وصياغة ركيكة في «explore the Aptis»، وغياب علامة الملكية في «candidates»، وكتابة «Pre Beginner» بلا شرطة خلافًا لـ«Pre-Beginner» في صفحتي IELTS وTOEFL.</t>
         </is>
       </c>
       <c r="I124" s="8" t="inlineStr">
@@ -7562,7 +7566,7 @@
       </c>
       <c r="K124" s="9" t="inlineStr">
         <is>
-          <t>التعديل في الصفحتين إلى: «may be admitted to a different level … meets one of the (minimum) requirements below:» و«Validity of the IELTS certificate» و«Validity of the TOEFL iBT report».</t>
+          <t>التعديل إلى: «provided by the British Council» و«Once candidates meet the general admission requirements, they will be scheduled to take the Aptis test» و«explore the Aptis test format before sitting the test» و«Based on candidates’ overall and writing scores» و«Pre-Beginner».</t>
         </is>
       </c>
       <c r="L124" s="9" t="inlineStr"/>
@@ -7573,22 +7577,22 @@
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>اختبار TOEFL</t>
+          <t>اختبار Aptis</t>
         </is>
       </c>
       <c r="C125" s="7" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/toefl-admission</t>
+          <t>https://pmu.edu.sa/admission/aptis-placement-test</t>
         </is>
       </c>
       <c r="D125" s="6" t="inlineStr">
         <is>
-          <t>جدول مستويات TOEFL iBT (وجدول IELTS المقابل في صفحة IELTS)</t>
+          <t>رابط «Aptis Candidate Guide (Click here)» – ملف PDF مرفق</t>
         </is>
       </c>
       <c r="E125" s="7" t="inlineStr">
         <is>
-          <t>LEVEL | TOEFL iBT Overall | TOEFL iBT Writing … Core | 83 | 19</t>
+          <t>Aptis Candidate Guide August 2017</t>
         </is>
       </c>
       <c r="F125" s="6" t="inlineStr">
@@ -7598,32 +7602,32 @@
       </c>
       <c r="G125" s="6" t="inlineStr">
         <is>
-          <t>مقياس درجات قد يكون قديمًا</t>
+          <t>مرجع خارجي قديم</t>
         </is>
       </c>
       <c r="H125" s="6" t="inlineStr">
         <is>
-          <t>تُعرض متطلبات TOEFL iBT على مقياس 0–120 فقط، وتشير مصادر ثانوية إلى أن ETS بدأت في 21 يناير 2026 بإصدار النتائج على مقياس جديد من 1 إلى 6.</t>
+          <t>تحيل الصفحة إلى نسخة مستضافة من دليل المرشح لاختبار Aptis صادرة في أغسطس 2017 (أُنشئ الملف عام 2017 وعُدّل آخر مرة في مارس 2019)، وقد لا تعكس النسخة الحالية للاختبار.</t>
         </is>
       </c>
       <c r="I125" s="5" t="inlineStr">
         <is>
-          <t>متابعة وتحقق</t>
+          <t>توصية تحسين</t>
         </is>
       </c>
       <c r="J125" s="5" t="inlineStr">
         <is>
-          <t>متوسطة</t>
+          <t>منخفضة</t>
         </is>
       </c>
       <c r="K125" s="6" t="inlineStr">
         <is>
-          <t>التحقق من تغيير المقياس لدى ETS، ثم نشر جدول تعادل معتمد يتضمن المقياس الجديد بالتنسيق بين مكتب القبول ومركز الاختبارات.</t>
+          <t>استبدال الملف المستضاف برابط إلى موارد المرشحين الحالية على موقع المجلس الثقافي البريطاني بدلًا من استضافة إصدار 2017.</t>
         </is>
       </c>
       <c r="L125" s="6" t="inlineStr">
         <is>
-          <t>معلومة تغيير المقياس من مصدر ثانوي ولم يُتحقق منها من مصدر رسمي.</t>
+          <t>بيانات إنشاء الملف وتعديله مأخوذة من خصائص ملف PDF.</t>
         </is>
       </c>
     </row>
@@ -7633,37 +7637,37 @@
       </c>
       <c r="B126" s="9" t="inlineStr">
         <is>
-          <t>اختبار TOEFL</t>
+          <t>اختبار IELTS</t>
         </is>
       </c>
       <c r="C126" s="10" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/toefl-admission</t>
+          <t>https://pmu.edu.sa/admission/ielts-admission</t>
         </is>
       </c>
       <c r="D126" s="9" t="inlineStr">
         <is>
-          <t>أسفل جدول المستويات</t>
+          <t>الفقرة التمهيدية وجدول المستويات</t>
         </is>
       </c>
       <c r="E126" s="10" t="inlineStr">
         <is>
-          <t>(online or home edition is not accepted)</t>
+          <t>if the candidate provides a valid  IELTS  certificate (Academic version) … The validation of the IELTS certificate | Two years from the date of IELTS test</t>
         </is>
       </c>
       <c r="F126" s="9" t="inlineStr">
         <is>
-          <t>تجربة المستخدم</t>
+          <t>دقة المعلومات</t>
         </is>
       </c>
       <c r="G126" s="9" t="inlineStr">
         <is>
-          <t>ملاحظة غير واضحة الموضع</t>
+          <t>معلومة ناقصة</t>
         </is>
       </c>
       <c r="H126" s="9" t="inlineStr">
         <is>
-          <t>تظهر عبارة عدم قبول النسخة المنزلية بين قوسين مباشرة بعد صف مدة الصلاحية، منفصلة عن سياقها، ولا تستخدم الاسم الرسمي للمنتج.</t>
+          <t>لا توضح صفحة IELTS طريقة تقديم النتيجة أو التحقق منها، ولا ما إذا كانت نتائج IELTS Online أو One Skill Retake مقبولة، في حين تحدد صفحة TOEFL هذه الجوانب («The original TOEFL iBT report has to be sent directly from ETS to PMU»).</t>
         </is>
       </c>
       <c r="I126" s="8" t="inlineStr">
@@ -7673,15 +7677,19 @@
       </c>
       <c r="J126" s="8" t="inlineStr">
         <is>
-          <t>منخفضة</t>
+          <t>متوسطة</t>
         </is>
       </c>
       <c r="K126" s="9" t="inlineStr">
         <is>
-          <t>إفرادها في سطر مستقل بصيغة واضحة، مثل: «Not accepted: TOEFL iBT Home Edition.»</t>
-        </is>
-      </c>
-      <c r="L126" s="9" t="inlineStr"/>
+          <t>بيان طريقة تقديم نتيجة IELTS والتحقق منها (مثل رقم نموذج النتيجة أو الإرسال الإلكتروني إلى الجامعة) وصيغ الاختبار المقبولة، وفق ما يعتمده مكتب القبول.</t>
+        </is>
+      </c>
+      <c r="L126" s="9" t="inlineStr">
+        <is>
+          <t>قبول صيغ IELTS Online وOne Skill Retake قرار يعود إلى مكتب القبول.</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="n">
@@ -7689,37 +7697,37 @@
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>اختبار SAT</t>
+          <t>اختبار IELTS</t>
         </is>
       </c>
       <c r="C127" s="7" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/sat-admission</t>
+          <t>https://pmu.edu.sa/admission/ielts-admission</t>
         </is>
       </c>
       <c r="D127" s="6" t="inlineStr">
         <is>
-          <t>رابط «Tahseely» في الفقرة الأولى</t>
+          <t>الفقرة التمهيدية وجدول المستويات (يتكرر النص نفسه في صفحة TOEFL – TOEFL)</t>
         </is>
       </c>
       <c r="E127" s="7" t="inlineStr">
         <is>
-          <t>instead of Qudrat and Tahseely tests</t>
+          <t>might be admitted to different level in the Preparatory Program … successfully meets one of the below requirements of the categories below … The validation of the IELTS certificate | TOEFL: The validation of the TOEFL iBT report … one of the below minimum requirements of the categories below</t>
         </is>
       </c>
       <c r="F127" s="6" t="inlineStr">
         <is>
-          <t>وظيفي وتقني</t>
+          <t>لغوي ونحوي</t>
         </is>
       </c>
       <c r="G127" s="6" t="inlineStr">
         <is>
-          <t>رابط مضلل</t>
+          <t>أخطاء لغوية متكررة</t>
         </is>
       </c>
       <c r="H127" s="6" t="inlineStr">
         <is>
-          <t>يشير رابط «Tahseely»، الوارد في سياق تخصصات العلوم والهندسة، إلى صفحة المسار الإنساني على موقع هيئة تقويم التعليم والتدريب.</t>
+          <t>في صفحتي IELTS وTOEFL تنقص أداة التنكير في «to different level»، وتتكرر كلمة «below» في الجملة نفسها، وتُستخدم «validation» بدلًا من «validity» في صف مدة الصلاحية.</t>
         </is>
       </c>
       <c r="I127" s="5" t="inlineStr">
@@ -7729,19 +7737,15 @@
       </c>
       <c r="J127" s="5" t="inlineStr">
         <is>
-          <t>متوسطة</t>
+          <t>منخفضة</t>
         </is>
       </c>
       <c r="K127" s="6" t="inlineStr">
         <is>
-          <t>توجيه الرابط إلى صفحة اختبار التحصيلي للمسار العلمي أو إلى الصفحة العامة لاختبار التحصيلي.</t>
-        </is>
-      </c>
-      <c r="L127" s="6" t="inlineStr">
-        <is>
-          <t>وجهة الرابط: https://www.etec.gov.sa/en/service/theHumanitiesTrack/servicegoal</t>
-        </is>
-      </c>
+          <t>التعديل في الصفحتين إلى: «may be admitted to a different level … meets one of the (minimum) requirements below:» و«Validity of the IELTS certificate» و«Validity of the TOEFL iBT report».</t>
+        </is>
+      </c>
+      <c r="L127" s="6" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="8" t="n">
@@ -7749,22 +7753,22 @@
       </c>
       <c r="B128" s="9" t="inlineStr">
         <is>
-          <t>اختبار SAT</t>
+          <t>اختبار TOEFL</t>
         </is>
       </c>
       <c r="C128" s="10" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/sat-admission</t>
+          <t>https://pmu.edu.sa/admission/toefl-admission</t>
         </is>
       </c>
       <c r="D128" s="9" t="inlineStr">
         <is>
-          <t>الفقرة الأولى</t>
+          <t>جدول مستويات TOEFL iBT (وجدول IELTS المقابل في صفحة IELTS)</t>
         </is>
       </c>
       <c r="E128" s="10" t="inlineStr">
         <is>
-          <t>Students with international high school certificate might submit SAT with minimum score of 1200 instead of Qudrat and Tahseely tests.</t>
+          <t>LEVEL | TOEFL iBT Overall | TOEFL iBT Writing … Core | 83 | 19</t>
         </is>
       </c>
       <c r="F128" s="9" t="inlineStr">
@@ -7774,17 +7778,17 @@
       </c>
       <c r="G128" s="9" t="inlineStr">
         <is>
-          <t>معلومة ناقصة</t>
+          <t>مقياس درجات قد يكون قديمًا</t>
         </is>
       </c>
       <c r="H128" s="9" t="inlineStr">
         <is>
-          <t>تحدد الصفحة حدًا أدنى قدره 1200 درجة دون بيان مدة صلاحية النتيجة أو ما إذا كانت الدرجة المركبة من عدة جلسات (Superscore) مقبولة، في حين تنص صفحتا IELTS وTOEFL على صلاحية مدتها سنتان.</t>
+          <t>تُعرض متطلبات TOEFL iBT على مقياس 0–120 فقط، وتشير مصادر ثانوية إلى أن ETS بدأت في 21 يناير 2026 بإصدار النتائج على مقياس جديد من 1 إلى 6.</t>
         </is>
       </c>
       <c r="I128" s="8" t="inlineStr">
         <is>
-          <t>توصية تحسين</t>
+          <t>متابعة وتحقق</t>
         </is>
       </c>
       <c r="J128" s="8" t="inlineStr">
@@ -7794,10 +7798,14 @@
       </c>
       <c r="K128" s="9" t="inlineStr">
         <is>
-          <t>إضافة مدة صلاحية نتيجة SAT وقاعدة احتساب الدرجة (جلسة واحدة أو درجة مركبة) بعد اعتمادها من مكتب القبول.</t>
-        </is>
-      </c>
-      <c r="L128" s="9" t="inlineStr"/>
+          <t>التحقق من تغيير المقياس لدى ETS، ثم نشر جدول تعادل معتمد يتضمن المقياس الجديد بالتنسيق بين مكتب القبول ومركز الاختبارات.</t>
+        </is>
+      </c>
+      <c r="L128" s="9" t="inlineStr">
+        <is>
+          <t>معلومة تغيير المقياس من مصدر ثانوي ولم يُتحقق منها من مصدر رسمي.</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="n">
@@ -7805,42 +7813,42 @@
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>اختبار SAT</t>
+          <t>اختبار TOEFL</t>
         </is>
       </c>
       <c r="C129" s="7" t="inlineStr">
         <is>
-          <t>https://pmu.edu.sa/admission/sat-admission</t>
+          <t>https://pmu.edu.sa/admission/toefl-admission</t>
         </is>
       </c>
       <c r="D129" s="6" t="inlineStr">
         <is>
-          <t>الفقرة الأولى وجدول إعفاء مقررات الرياضيات (الجملة الأولى مكررة في الحاسب والهندسة)؛ وصفحة متطلبات تخصصات الحاسب والهندسة (فقرة الإعفاء من مقررات الرياضيات)</t>
+          <t>أسفل جدول المستويات</t>
         </is>
       </c>
       <c r="E129" s="7" t="inlineStr">
         <is>
-          <t>some majors require specific level of certain skills … may wave one or more of the mathematics courses … Introductory Algebra | Wave | Wave … Pre-Calculus | N/A | Wave</t>
+          <t>(online or home edition is not accepted)</t>
         </is>
       </c>
       <c r="F129" s="6" t="inlineStr">
         <is>
-          <t>لغوي ونحوي</t>
+          <t>تجربة المستخدم</t>
         </is>
       </c>
       <c r="G129" s="6" t="inlineStr">
         <is>
-          <t>أخطاء إملائية ولغوية</t>
+          <t>ملاحظة غير واضحة الموضع</t>
         </is>
       </c>
       <c r="H129" s="6" t="inlineStr">
         <is>
-          <t>كُتبت كلمة «waive» (بمعنى الإعفاء) خطأً «wave» في صفحة اختبار SAT (مرة في النص وأربع مرات في الجدول) وفي صفحة متطلبات تخصصات الحاسب والهندسة، وتنقص أداة التعريف في موضع من صفحة SAT.</t>
+          <t>تظهر عبارة عدم قبول النسخة المنزلية بين قوسين مباشرة بعد صف مدة الصلاحية، منفصلة عن سياقها، ولا تستخدم الاسم الرسمي للمنتج.</t>
         </is>
       </c>
       <c r="I129" s="5" t="inlineStr">
         <is>
-          <t>تصحيح مطلوب</t>
+          <t>توصية تحسين</t>
         </is>
       </c>
       <c r="J129" s="5" t="inlineStr">
@@ -7850,7 +7858,7 @@
       </c>
       <c r="K129" s="6" t="inlineStr">
         <is>
-          <t>تصحيح «wave» إلى «waive» في النص و«Waived» في الجدول، وتعديل العبارة إلى «require a specific level» في الصفحتين.</t>
+          <t>إفرادها في سطر مستقل بصيغة واضحة، مثل: «Not accepted: TOEFL iBT Home Edition.»</t>
         </is>
       </c>
       <c r="L129" s="6" t="inlineStr"/>
@@ -7871,47 +7879,47 @@
       </c>
       <c r="D130" s="9" t="inlineStr">
         <is>
-          <t>عنوان الصفحة ومسار التنقل (مقارنة بصفحة متطلبات تخصصات الحاسب والهندسة الحاسب والهندسة وصفحة التقديم)</t>
+          <t>رابط «Tahseely» في الفقرة الأولى</t>
         </is>
       </c>
       <c r="E130" s="10" t="inlineStr">
         <is>
-          <t>Scholastic Aptitude Test (SAT) | الحاسب والهندسة: (SAT 1) | /apply: Qudrat / SAT 1</t>
+          <t>instead of Qudrat and Tahseely tests</t>
         </is>
       </c>
       <c r="F130" s="9" t="inlineStr">
         <is>
-          <t>الاتساق</t>
+          <t>وظيفي وتقني</t>
         </is>
       </c>
       <c r="G130" s="9" t="inlineStr">
         <is>
-          <t>عدم اتساق التسمية</t>
+          <t>رابط مضلل</t>
         </is>
       </c>
       <c r="H130" s="9" t="inlineStr">
         <is>
-          <t>يُسمّى الاختبار «Scholastic Aptitude Test (SAT)» في صفحة SAT و«SAT 1» في صفحة المتطلبات وصفحة التقديم، في حين أن الاسم المعتمد حاليًا هو «SAT» فقط.</t>
+          <t>يشير رابط «Tahseely»، الوارد في سياق تخصصات العلوم والهندسة، إلى صفحة المسار الإنساني على موقع هيئة تقويم التعليم والتدريب.</t>
         </is>
       </c>
       <c r="I130" s="8" t="inlineStr">
         <is>
-          <t>توصية تحسين</t>
+          <t>تصحيح مطلوب</t>
         </is>
       </c>
       <c r="J130" s="8" t="inlineStr">
         <is>
-          <t>منخفضة</t>
+          <t>متوسطة</t>
         </is>
       </c>
       <c r="K130" s="9" t="inlineStr">
         <is>
-          <t>توحيد التسمية إلى «SAT» في صفحة SAT وصفحة متطلبات تخصصات الحاسب والهندسة وصفحة التقديم وصفحة القبول الرئيسية.</t>
+          <t>توجيه الرابط إلى صفحة اختبار التحصيلي للمسار العلمي أو إلى الصفحة العامة لاختبار التحصيلي.</t>
         </is>
       </c>
       <c r="L130" s="9" t="inlineStr">
         <is>
-          <t>الاسم الحالي للاختبار لدى College Board معلومة خارجية تستحسن مراجعتها.</t>
+          <t>وجهة الرابط: https://www.etec.gov.sa/en/service/theHumanitiesTrack/servicegoal</t>
         </is>
       </c>
     </row>
@@ -7931,49 +7939,221 @@
       </c>
       <c r="D131" s="6" t="inlineStr">
         <is>
+          <t>الفقرة الأولى</t>
+        </is>
+      </c>
+      <c r="E131" s="7" t="inlineStr">
+        <is>
+          <t>Students with international high school certificate might submit SAT with minimum score of 1200 instead of Qudrat and Tahseely tests.</t>
+        </is>
+      </c>
+      <c r="F131" s="6" t="inlineStr">
+        <is>
+          <t>دقة المعلومات</t>
+        </is>
+      </c>
+      <c r="G131" s="6" t="inlineStr">
+        <is>
+          <t>معلومة ناقصة</t>
+        </is>
+      </c>
+      <c r="H131" s="6" t="inlineStr">
+        <is>
+          <t>تحدد الصفحة حدًا أدنى قدره 1200 درجة دون بيان مدة صلاحية النتيجة أو ما إذا كانت الدرجة المركبة من عدة جلسات (Superscore) مقبولة، في حين تنص صفحتا IELTS وTOEFL على صلاحية مدتها سنتان.</t>
+        </is>
+      </c>
+      <c r="I131" s="5" t="inlineStr">
+        <is>
+          <t>توصية تحسين</t>
+        </is>
+      </c>
+      <c r="J131" s="5" t="inlineStr">
+        <is>
+          <t>متوسطة</t>
+        </is>
+      </c>
+      <c r="K131" s="6" t="inlineStr">
+        <is>
+          <t>إضافة مدة صلاحية نتيجة SAT وقاعدة احتساب الدرجة (جلسة واحدة أو درجة مركبة) بعد اعتمادها من مكتب القبول.</t>
+        </is>
+      </c>
+      <c r="L131" s="6" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="8" t="n">
+        <v>128</v>
+      </c>
+      <c r="B132" s="9" t="inlineStr">
+        <is>
+          <t>اختبار SAT</t>
+        </is>
+      </c>
+      <c r="C132" s="10" t="inlineStr">
+        <is>
+          <t>https://pmu.edu.sa/admission/sat-admission</t>
+        </is>
+      </c>
+      <c r="D132" s="9" t="inlineStr">
+        <is>
+          <t>الفقرة الأولى وجدول إعفاء مقررات الرياضيات (الجملة الأولى مكررة في الحاسب والهندسة)؛ وصفحة متطلبات تخصصات الحاسب والهندسة (فقرة الإعفاء من مقررات الرياضيات)</t>
+        </is>
+      </c>
+      <c r="E132" s="10" t="inlineStr">
+        <is>
+          <t>some majors require specific level of certain skills … may wave one or more of the mathematics courses … Introductory Algebra | Wave | Wave … Pre-Calculus | N/A | Wave</t>
+        </is>
+      </c>
+      <c r="F132" s="9" t="inlineStr">
+        <is>
+          <t>لغوي ونحوي</t>
+        </is>
+      </c>
+      <c r="G132" s="9" t="inlineStr">
+        <is>
+          <t>أخطاء إملائية ولغوية</t>
+        </is>
+      </c>
+      <c r="H132" s="9" t="inlineStr">
+        <is>
+          <t>كُتبت كلمة «waive» (بمعنى الإعفاء) خطأً «wave» في صفحة اختبار SAT (مرة في النص وأربع مرات في الجدول) وفي صفحة متطلبات تخصصات الحاسب والهندسة، وتنقص أداة التعريف في موضع من صفحة SAT.</t>
+        </is>
+      </c>
+      <c r="I132" s="8" t="inlineStr">
+        <is>
+          <t>تصحيح مطلوب</t>
+        </is>
+      </c>
+      <c r="J132" s="8" t="inlineStr">
+        <is>
+          <t>منخفضة</t>
+        </is>
+      </c>
+      <c r="K132" s="9" t="inlineStr">
+        <is>
+          <t>تصحيح «wave» إلى «waive» في النص و«Waived» في الجدول، وتعديل العبارة إلى «require a specific level» في الصفحتين.</t>
+        </is>
+      </c>
+      <c r="L132" s="9" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="n">
+        <v>129</v>
+      </c>
+      <c r="B133" s="6" t="inlineStr">
+        <is>
+          <t>اختبار SAT</t>
+        </is>
+      </c>
+      <c r="C133" s="7" t="inlineStr">
+        <is>
+          <t>https://pmu.edu.sa/admission/sat-admission</t>
+        </is>
+      </c>
+      <c r="D133" s="6" t="inlineStr">
+        <is>
+          <t>عنوان الصفحة ومسار التنقل (مقارنة بصفحة متطلبات تخصصات الحاسب والهندسة الحاسب والهندسة وصفحة التقديم)</t>
+        </is>
+      </c>
+      <c r="E133" s="7" t="inlineStr">
+        <is>
+          <t>Scholastic Aptitude Test (SAT) | الحاسب والهندسة: (SAT 1) | /apply: Qudrat / SAT 1</t>
+        </is>
+      </c>
+      <c r="F133" s="6" t="inlineStr">
+        <is>
+          <t>الاتساق</t>
+        </is>
+      </c>
+      <c r="G133" s="6" t="inlineStr">
+        <is>
+          <t>عدم اتساق التسمية</t>
+        </is>
+      </c>
+      <c r="H133" s="6" t="inlineStr">
+        <is>
+          <t>يُسمّى الاختبار «Scholastic Aptitude Test (SAT)» في صفحة SAT و«SAT 1» في صفحة المتطلبات وصفحة التقديم، في حين أن الاسم المعتمد حاليًا هو «SAT» فقط.</t>
+        </is>
+      </c>
+      <c r="I133" s="5" t="inlineStr">
+        <is>
+          <t>توصية تحسين</t>
+        </is>
+      </c>
+      <c r="J133" s="5" t="inlineStr">
+        <is>
+          <t>منخفضة</t>
+        </is>
+      </c>
+      <c r="K133" s="6" t="inlineStr">
+        <is>
+          <t>توحيد التسمية إلى «SAT» في صفحة SAT وصفحة متطلبات تخصصات الحاسب والهندسة وصفحة التقديم وصفحة القبول الرئيسية.</t>
+        </is>
+      </c>
+      <c r="L133" s="6" t="inlineStr">
+        <is>
+          <t>الاسم الحالي للاختبار لدى College Board معلومة خارجية تستحسن مراجعتها.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="8" t="n">
+        <v>130</v>
+      </c>
+      <c r="B134" s="9" t="inlineStr">
+        <is>
+          <t>اختبار SAT</t>
+        </is>
+      </c>
+      <c r="C134" s="10" t="inlineStr">
+        <is>
+          <t>https://pmu.edu.sa/admission/sat-admission</t>
+        </is>
+      </c>
+      <c r="D134" s="9" t="inlineStr">
+        <is>
           <t>جدول إعفاء مقررات الرياضيات</t>
         </is>
       </c>
-      <c r="E131" s="7" t="inlineStr">
+      <c r="E134" s="10" t="inlineStr">
         <is>
           <t>Introductory Algebra | Wave | Wave / Intermediate Algebra | N/A | Wave / Pre-Calculus | N/A | Wave</t>
         </is>
       </c>
-      <c r="F131" s="6" t="inlineStr">
+      <c r="F134" s="9" t="inlineStr">
         <is>
           <t>الاتساق</t>
         </is>
       </c>
-      <c r="G131" s="6" t="inlineStr">
+      <c r="G134" s="9" t="inlineStr">
         <is>
           <t>غياب رموز المقررات</t>
         </is>
       </c>
-      <c r="H131" s="6" t="inlineStr">
+      <c r="H134" s="9" t="inlineStr">
         <is>
           <t>يذكر جدول الإعفاء أسماء مقررات الرياضيات دون رموزها المستخدمة في صفحة الانتقال من البرنامج التحضيري إلى البكالوريوس (مثل «PRPM 0011 – Introductory Algebra»).</t>
         </is>
       </c>
-      <c r="I131" s="5" t="inlineStr">
+      <c r="I134" s="8" t="inlineStr">
         <is>
           <t>توصية تحسين</t>
         </is>
       </c>
-      <c r="J131" s="5" t="inlineStr">
+      <c r="J134" s="8" t="inlineStr">
         <is>
           <t>منخفضة</t>
         </is>
       </c>
-      <c r="K131" s="6" t="inlineStr">
+      <c r="K134" s="9" t="inlineStr">
         <is>
           <t>إضافة رموز المقررات إلى الجدول، مثل «PRPM 0011 Introductory Algebra».</t>
         </is>
       </c>
-      <c r="L131" s="6" t="inlineStr"/>
+      <c r="L134" s="9" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:L131"/>
-  <conditionalFormatting sqref="J5:J131">
+  <autoFilter ref="A4:L134"/>
+  <conditionalFormatting sqref="J5:J134">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>J5="عالية"</formula>
     </cfRule>
@@ -8024,7 +8204,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>العدد الإجمالي: 127 ملاحظة (مطابق لعدد صفوف السجل). المجاميع أدناه محسوبة بمعادلات من ورقة السجل.</t>
+          <t>العدد الإجمالي: 130 ملاحظة (مطابق لعدد صفوف السجل). المجاميع أدناه محسوبة بمعادلات من ورقة السجل.</t>
         </is>
       </c>
     </row>
